--- a/aht/August-AHT-Analysis.xlsx
+++ b/aht/August-AHT-Analysis.xlsx
@@ -707,7 +707,6 @@
       </c>
       <c r="C6" s="5">
         <f>'Checks'!C8</f>
-        <v/>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -723,7 +722,6 @@
       </c>
       <c r="C7" s="5">
         <f>'Checks'!C7</f>
-        <v/>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
@@ -739,7 +737,6 @@
       </c>
       <c r="C8" s="7">
         <f>'Checks'!C8*Assumptions!C10</f>
-        <v/>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
@@ -755,7 +752,6 @@
       </c>
       <c r="C9" s="5">
         <f>Assumptions!C9</f>
-        <v/>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -771,7 +767,6 @@
       </c>
       <c r="C10" s="7">
         <f>Assumptions!C9*Assumptions!C10</f>
-        <v/>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -1227,7 +1222,7 @@
       </c>
       <c r="C8" s="16">
         <f>C6/C7</f>
-        <v/>
+        <v>0.4531170519414458</v>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
@@ -1243,7 +1238,7 @@
       </c>
       <c r="C9" s="17">
         <f>C7/'Checks'!C6</f>
-        <v/>
+        <v>1.961529933481153</v>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="G2" s="24">
         <f>D2*H2</f>
-        <v/>
+        <v>20.88</v>
       </c>
       <c r="H2" s="25" t="n">
         <v>150</v>
@@ -1465,7 +1460,7 @@
       </c>
       <c r="G3" s="24">
         <f>D3*H3</f>
-        <v/>
+        <v>2.745</v>
       </c>
       <c r="H3" s="25" t="n">
         <v>150</v>
@@ -1498,7 +1493,7 @@
       </c>
       <c r="G4" s="24">
         <f>D4*H4</f>
-        <v/>
+        <v>2.97</v>
       </c>
       <c r="H4" s="25" t="n">
         <v>150</v>
@@ -1531,7 +1526,7 @@
       </c>
       <c r="G5" s="24">
         <f>D5*H5</f>
-        <v/>
+        <v>3.21</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>150</v>
@@ -1564,7 +1559,7 @@
       </c>
       <c r="G6" s="24">
         <f>D6*H6</f>
-        <v/>
+        <v>3.7199999999999998</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>150</v>
@@ -1597,7 +1592,7 @@
       </c>
       <c r="G7" s="24">
         <f>D7*H7</f>
-        <v/>
+        <v>4.335</v>
       </c>
       <c r="H7" s="25" t="n">
         <v>150</v>
@@ -1630,7 +1625,7 @@
       </c>
       <c r="G8" s="24">
         <f>D8*H8</f>
-        <v/>
+        <v>5.114999999999999</v>
       </c>
       <c r="H8" s="25" t="n">
         <v>150</v>
@@ -1663,7 +1658,7 @@
       </c>
       <c r="G9" s="24">
         <f>D9*H9</f>
-        <v/>
+        <v>5.145</v>
       </c>
       <c r="H9" s="25" t="n">
         <v>150</v>
@@ -1696,7 +1691,7 @@
       </c>
       <c r="G10" s="24">
         <f>D10*H10</f>
-        <v/>
+        <v>10.395</v>
       </c>
       <c r="H10" s="25" t="n">
         <v>150</v>
@@ -1729,7 +1724,7 @@
       </c>
       <c r="G11" s="24">
         <f>D11*H11</f>
-        <v/>
+        <v>14.445</v>
       </c>
       <c r="H11" s="25" t="n">
         <v>150</v>
@@ -1762,7 +1757,7 @@
       </c>
       <c r="G12" s="24">
         <f>D12*H12</f>
-        <v/>
+        <v>14.97</v>
       </c>
       <c r="H12" s="25" t="n">
         <v>150</v>
@@ -1795,7 +1790,7 @@
       </c>
       <c r="G13" s="24">
         <f>D13*H13</f>
-        <v/>
+        <v>17.385</v>
       </c>
       <c r="H13" s="25" t="n">
         <v>150</v>
@@ -1828,7 +1823,7 @@
       </c>
       <c r="G14" s="24">
         <f>D14*H14</f>
-        <v/>
+        <v>19.305</v>
       </c>
       <c r="H14" s="25" t="n">
         <v>150</v>
@@ -1861,7 +1856,7 @@
       </c>
       <c r="G15" s="24">
         <f>D15*H15</f>
-        <v/>
+        <v>25.92</v>
       </c>
       <c r="H15" s="25" t="n">
         <v>150</v>
@@ -1894,7 +1889,7 @@
       </c>
       <c r="G16" s="24">
         <f>D16*H16</f>
-        <v/>
+        <v>33.405</v>
       </c>
       <c r="H16" s="25" t="n">
         <v>150</v>
@@ -1927,7 +1922,7 @@
       </c>
       <c r="G17" s="24">
         <f>D17*H17</f>
-        <v/>
+        <v>40.515</v>
       </c>
       <c r="H17" s="25" t="n">
         <v>150</v>
@@ -1960,7 +1955,7 @@
       </c>
       <c r="G18" s="24">
         <f>D18*H18</f>
-        <v/>
+        <v>46.05</v>
       </c>
       <c r="H18" s="25" t="n">
         <v>150</v>
@@ -1993,7 +1988,7 @@
       </c>
       <c r="G19" s="24">
         <f>D19*H19</f>
-        <v/>
+        <v>96.105</v>
       </c>
       <c r="H19" s="25" t="n">
         <v>150</v>
@@ -2026,7 +2021,7 @@
       </c>
       <c r="G20" s="24">
         <f>D20*H20</f>
-        <v/>
+        <v>137.655</v>
       </c>
       <c r="H20" s="25" t="n">
         <v>150</v>
@@ -2059,7 +2054,7 @@
       </c>
       <c r="G21" s="24">
         <f>D21*H21</f>
-        <v/>
+        <v>138.81</v>
       </c>
       <c r="H21" s="25" t="n">
         <v>150</v>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="G22" s="24">
         <f>D22*H22</f>
-        <v/>
+        <v>161.86499999999998</v>
       </c>
       <c r="H22" s="25" t="n">
         <v>150</v>
@@ -2125,7 +2120,7 @@
       </c>
       <c r="G23" s="24">
         <f>D23*H23</f>
-        <v/>
+        <v>219.345</v>
       </c>
       <c r="H23" s="25" t="n">
         <v>150</v>
@@ -2158,7 +2153,7 @@
       </c>
       <c r="G24" s="24">
         <f>D24*H24</f>
-        <v/>
+        <v>284.61</v>
       </c>
       <c r="H24" s="25" t="n">
         <v>150</v>
@@ -2191,7 +2186,7 @@
       </c>
       <c r="G25" s="24">
         <f>D25*H25</f>
-        <v/>
+        <v>288.06</v>
       </c>
       <c r="H25" s="25" t="n">
         <v>150</v>
@@ -2224,7 +2219,7 @@
       </c>
       <c r="G26" s="24">
         <f>D26*H26</f>
-        <v/>
+        <v>378.9</v>
       </c>
       <c r="H26" s="25" t="n">
         <v>150</v>
@@ -2257,7 +2252,7 @@
       </c>
       <c r="G27" s="24">
         <f>D27*H27</f>
-        <v/>
+        <v>470.28000000000003</v>
       </c>
       <c r="H27" s="25" t="n">
         <v>150</v>
@@ -2290,7 +2285,7 @@
       </c>
       <c r="G28" s="24">
         <f>D28*H28</f>
-        <v/>
+        <v>602.025</v>
       </c>
       <c r="H28" s="25" t="n">
         <v>150</v>
@@ -2323,7 +2318,7 @@
       </c>
       <c r="G29" s="24">
         <f>D29*H29</f>
-        <v/>
+        <v>910.26</v>
       </c>
       <c r="H29" s="25" t="n">
         <v>150</v>
@@ -2356,7 +2351,7 @@
       </c>
       <c r="G30" s="24">
         <f>D30*H30</f>
-        <v/>
+        <v>5.16</v>
       </c>
       <c r="H30" s="25" t="n">
         <v>200</v>
@@ -2389,7 +2384,7 @@
       </c>
       <c r="G31" s="24">
         <f>D31*H31</f>
-        <v/>
+        <v>6.419999999999999</v>
       </c>
       <c r="H31" s="25" t="n">
         <v>200</v>
@@ -2422,7 +2417,7 @@
       </c>
       <c r="G32" s="24">
         <f>D32*H32</f>
-        <v/>
+        <v>8.06</v>
       </c>
       <c r="H32" s="25" t="n">
         <v>200</v>
@@ -2455,7 +2450,7 @@
       </c>
       <c r="G33" s="24">
         <f>D33*H33</f>
-        <v/>
+        <v>9.16</v>
       </c>
       <c r="H33" s="25" t="n">
         <v>200</v>
@@ -2488,7 +2483,7 @@
       </c>
       <c r="G34" s="24">
         <f>D34*H34</f>
-        <v/>
+        <v>12.42</v>
       </c>
       <c r="H34" s="25" t="n">
         <v>200</v>
@@ -2521,7 +2516,7 @@
       </c>
       <c r="G35" s="24">
         <f>D35*H35</f>
-        <v/>
+        <v>16.32</v>
       </c>
       <c r="H35" s="25" t="n">
         <v>200</v>
@@ -2554,7 +2549,7 @@
       </c>
       <c r="G36" s="24">
         <f>D36*H36</f>
-        <v/>
+        <v>18.04</v>
       </c>
       <c r="H36" s="25" t="n">
         <v>200</v>
@@ -2587,7 +2582,7 @@
       </c>
       <c r="G37" s="24">
         <f>D37*H37</f>
-        <v/>
+        <v>19.28</v>
       </c>
       <c r="H37" s="25" t="n">
         <v>200</v>
@@ -2620,7 +2615,7 @@
       </c>
       <c r="G38" s="24">
         <f>D38*H38</f>
-        <v/>
+        <v>19.400000000000002</v>
       </c>
       <c r="H38" s="25" t="n">
         <v>200</v>
@@ -2653,7 +2648,7 @@
       </c>
       <c r="G39" s="24">
         <f>D39*H39</f>
-        <v/>
+        <v>20.66</v>
       </c>
       <c r="H39" s="25" t="n">
         <v>200</v>
@@ -2686,7 +2681,7 @@
       </c>
       <c r="G40" s="24">
         <f>D40*H40</f>
-        <v/>
+        <v>20.7</v>
       </c>
       <c r="H40" s="25" t="n">
         <v>200</v>
@@ -2719,7 +2714,7 @@
       </c>
       <c r="G41" s="24">
         <f>D41*H41</f>
-        <v/>
+        <v>20.78</v>
       </c>
       <c r="H41" s="25" t="n">
         <v>200</v>
@@ -2752,7 +2747,7 @@
       </c>
       <c r="G42" s="24">
         <f>D42*H42</f>
-        <v/>
+        <v>25.5</v>
       </c>
       <c r="H42" s="25" t="n">
         <v>200</v>
@@ -2785,7 +2780,7 @@
       </c>
       <c r="G43" s="24">
         <f>D43*H43</f>
-        <v/>
+        <v>29.7</v>
       </c>
       <c r="H43" s="25" t="n">
         <v>200</v>
@@ -2818,7 +2813,7 @@
       </c>
       <c r="G44" s="24">
         <f>D44*H44</f>
-        <v/>
+        <v>30.3</v>
       </c>
       <c r="H44" s="25" t="n">
         <v>200</v>
@@ -2851,7 +2846,7 @@
       </c>
       <c r="G45" s="24">
         <f>D45*H45</f>
-        <v/>
+        <v>33.44</v>
       </c>
       <c r="H45" s="25" t="n">
         <v>200</v>
@@ -2884,7 +2879,7 @@
       </c>
       <c r="G46" s="24">
         <f>D46*H46</f>
-        <v/>
+        <v>36.52</v>
       </c>
       <c r="H46" s="25" t="n">
         <v>200</v>
@@ -2917,7 +2912,7 @@
       </c>
       <c r="G47" s="24">
         <f>D47*H47</f>
-        <v/>
+        <v>39.660000000000004</v>
       </c>
       <c r="H47" s="25" t="n">
         <v>200</v>
@@ -2950,7 +2945,7 @@
       </c>
       <c r="G48" s="24">
         <f>D48*H48</f>
-        <v/>
+        <v>40.32</v>
       </c>
       <c r="H48" s="25" t="n">
         <v>200</v>
@@ -2983,7 +2978,7 @@
       </c>
       <c r="G49" s="24">
         <f>D49*H49</f>
-        <v/>
+        <v>43.26</v>
       </c>
       <c r="H49" s="25" t="n">
         <v>200</v>
@@ -3016,7 +3011,7 @@
       </c>
       <c r="G50" s="24">
         <f>D50*H50</f>
-        <v/>
+        <v>47.56</v>
       </c>
       <c r="H50" s="25" t="n">
         <v>200</v>
@@ -3049,7 +3044,7 @@
       </c>
       <c r="G51" s="24">
         <f>D51*H51</f>
-        <v/>
+        <v>48.620000000000005</v>
       </c>
       <c r="H51" s="25" t="n">
         <v>200</v>
@@ -3082,7 +3077,7 @@
       </c>
       <c r="G52" s="24">
         <f>D52*H52</f>
-        <v/>
+        <v>52.739999999999995</v>
       </c>
       <c r="H52" s="25" t="n">
         <v>200</v>
@@ -3115,7 +3110,7 @@
       </c>
       <c r="G53" s="24">
         <f>D53*H53</f>
-        <v/>
+        <v>55.76</v>
       </c>
       <c r="H53" s="25" t="n">
         <v>200</v>
@@ -3148,7 +3143,7 @@
       </c>
       <c r="G54" s="24">
         <f>D54*H54</f>
-        <v/>
+        <v>59.36</v>
       </c>
       <c r="H54" s="25" t="n">
         <v>200</v>
@@ -3181,7 +3176,7 @@
       </c>
       <c r="G55" s="24">
         <f>D55*H55</f>
-        <v/>
+        <v>71.86</v>
       </c>
       <c r="H55" s="25" t="n">
         <v>200</v>
@@ -3214,7 +3209,7 @@
       </c>
       <c r="G56" s="24">
         <f>D56*H56</f>
-        <v/>
+        <v>84.14</v>
       </c>
       <c r="H56" s="25" t="n">
         <v>200</v>
@@ -3247,7 +3242,7 @@
       </c>
       <c r="G57" s="24">
         <f>D57*H57</f>
-        <v/>
+        <v>84.89999999999999</v>
       </c>
       <c r="H57" s="25" t="n">
         <v>200</v>
@@ -3280,7 +3275,7 @@
       </c>
       <c r="G58" s="24">
         <f>D58*H58</f>
-        <v/>
+        <v>86.24000000000001</v>
       </c>
       <c r="H58" s="25" t="n">
         <v>200</v>
@@ -3313,7 +3308,7 @@
       </c>
       <c r="G59" s="24">
         <f>D59*H59</f>
-        <v/>
+        <v>89.66</v>
       </c>
       <c r="H59" s="25" t="n">
         <v>200</v>
@@ -3346,7 +3341,7 @@
       </c>
       <c r="G60" s="24">
         <f>D60*H60</f>
-        <v/>
+        <v>90.06</v>
       </c>
       <c r="H60" s="25" t="n">
         <v>200</v>
@@ -3379,7 +3374,7 @@
       </c>
       <c r="G61" s="24">
         <f>D61*H61</f>
-        <v/>
+        <v>115.6</v>
       </c>
       <c r="H61" s="25" t="n">
         <v>200</v>
@@ -3412,7 +3407,7 @@
       </c>
       <c r="G62" s="24">
         <f>D62*H62</f>
-        <v/>
+        <v>120.74000000000001</v>
       </c>
       <c r="H62" s="25" t="n">
         <v>200</v>
@@ -3445,7 +3440,7 @@
       </c>
       <c r="G63" s="24">
         <f>D63*H63</f>
-        <v/>
+        <v>172.62</v>
       </c>
       <c r="H63" s="25" t="n">
         <v>200</v>
@@ -3478,7 +3473,7 @@
       </c>
       <c r="G64" s="24">
         <f>D64*H64</f>
-        <v/>
+        <v>194.70000000000002</v>
       </c>
       <c r="H64" s="25" t="n">
         <v>200</v>
@@ -3511,7 +3506,7 @@
       </c>
       <c r="G65" s="24">
         <f>D65*H65</f>
-        <v/>
+        <v>267.28000000000003</v>
       </c>
       <c r="H65" s="25" t="n">
         <v>200</v>
@@ -3544,7 +3539,7 @@
       </c>
       <c r="G66" s="24">
         <f>D66*H66</f>
-        <v/>
+        <v>274.76</v>
       </c>
       <c r="H66" s="25" t="n">
         <v>200</v>
@@ -3577,7 +3572,7 @@
       </c>
       <c r="G67" s="24">
         <f>D67*H67</f>
-        <v/>
+        <v>292.42</v>
       </c>
       <c r="H67" s="25" t="n">
         <v>200</v>
@@ -3610,7 +3605,7 @@
       </c>
       <c r="G68" s="24">
         <f>D68*H68</f>
-        <v/>
+        <v>350.28000000000003</v>
       </c>
       <c r="H68" s="25" t="n">
         <v>200</v>
@@ -3643,7 +3638,7 @@
       </c>
       <c r="G69" s="24">
         <f>D69*H69</f>
-        <v/>
+        <v>352.44</v>
       </c>
       <c r="H69" s="25" t="n">
         <v>200</v>
@@ -3676,7 +3671,7 @@
       </c>
       <c r="G70" s="24">
         <f>D70*H70</f>
-        <v/>
+        <v>437.7</v>
       </c>
       <c r="H70" s="25" t="n">
         <v>200</v>
@@ -3709,7 +3704,7 @@
       </c>
       <c r="G71" s="24">
         <f>D71*H71</f>
-        <v/>
+        <v>681.06</v>
       </c>
       <c r="H71" s="25" t="n">
         <v>200</v>
@@ -3742,7 +3737,7 @@
       </c>
       <c r="G72" s="24">
         <f>D72*H72</f>
-        <v/>
+        <v>20.775000000000002</v>
       </c>
       <c r="H72" s="25" t="n">
         <v>150</v>
@@ -3775,7 +3770,7 @@
       </c>
       <c r="G73" s="24">
         <f>D73*H73</f>
-        <v/>
+        <v>58.95</v>
       </c>
       <c r="H73" s="25" t="n">
         <v>150</v>
@@ -3808,7 +3803,7 @@
       </c>
       <c r="G74" s="24">
         <f>D74*H74</f>
-        <v/>
+        <v>3.495</v>
       </c>
       <c r="H74" s="25" t="n">
         <v>150</v>
@@ -3841,7 +3836,7 @@
       </c>
       <c r="G75" s="24">
         <f>D75*H75</f>
-        <v/>
+        <v>3.93</v>
       </c>
       <c r="H75" s="25" t="n">
         <v>150</v>
@@ -3874,7 +3869,7 @@
       </c>
       <c r="G76" s="24">
         <f>D76*H76</f>
-        <v/>
+        <v>4.905</v>
       </c>
       <c r="H76" s="25" t="n">
         <v>150</v>
@@ -3907,7 +3902,7 @@
       </c>
       <c r="G77" s="24">
         <f>D77*H77</f>
-        <v/>
+        <v>5.385</v>
       </c>
       <c r="H77" s="25" t="n">
         <v>150</v>
@@ -3940,7 +3935,7 @@
       </c>
       <c r="G78" s="24">
         <f>D78*H78</f>
-        <v/>
+        <v>11.19</v>
       </c>
       <c r="H78" s="25" t="n">
         <v>150</v>
@@ -3973,7 +3968,7 @@
       </c>
       <c r="G79" s="24">
         <f>D79*H79</f>
-        <v/>
+        <v>14.069999999999999</v>
       </c>
       <c r="H79" s="25" t="n">
         <v>150</v>
@@ -4006,7 +4001,7 @@
       </c>
       <c r="G80" s="24">
         <f>D80*H80</f>
-        <v/>
+        <v>16.86</v>
       </c>
       <c r="H80" s="25" t="n">
         <v>150</v>
@@ -4039,7 +4034,7 @@
       </c>
       <c r="G81" s="24">
         <f>D81*H81</f>
-        <v/>
+        <v>20.85</v>
       </c>
       <c r="H81" s="25" t="n">
         <v>150</v>
@@ -4072,7 +4067,7 @@
       </c>
       <c r="G82" s="24">
         <f>D82*H82</f>
-        <v/>
+        <v>23.04</v>
       </c>
       <c r="H82" s="25" t="n">
         <v>150</v>
@@ -4105,7 +4100,7 @@
       </c>
       <c r="G83" s="24">
         <f>D83*H83</f>
-        <v/>
+        <v>24.87</v>
       </c>
       <c r="H83" s="25" t="n">
         <v>150</v>
@@ -4138,7 +4133,7 @@
       </c>
       <c r="G84" s="24">
         <f>D84*H84</f>
-        <v/>
+        <v>28.919999999999998</v>
       </c>
       <c r="H84" s="25" t="n">
         <v>150</v>
@@ -4171,7 +4166,7 @@
       </c>
       <c r="G85" s="24">
         <f>D85*H85</f>
-        <v/>
+        <v>29.084999999999997</v>
       </c>
       <c r="H85" s="25" t="n">
         <v>150</v>
@@ -4204,7 +4199,7 @@
       </c>
       <c r="G86" s="24">
         <f>D86*H86</f>
-        <v/>
+        <v>30.54</v>
       </c>
       <c r="H86" s="25" t="n">
         <v>150</v>
@@ -4237,7 +4232,7 @@
       </c>
       <c r="G87" s="24">
         <f>D87*H87</f>
-        <v/>
+        <v>32.505</v>
       </c>
       <c r="H87" s="25" t="n">
         <v>150</v>
@@ -4270,7 +4265,7 @@
       </c>
       <c r="G88" s="24">
         <f>D88*H88</f>
-        <v/>
+        <v>41.055</v>
       </c>
       <c r="H88" s="25" t="n">
         <v>150</v>
@@ -4303,7 +4298,7 @@
       </c>
       <c r="G89" s="24">
         <f>D89*H89</f>
-        <v/>
+        <v>45.54</v>
       </c>
       <c r="H89" s="25" t="n">
         <v>150</v>
@@ -4336,7 +4331,7 @@
       </c>
       <c r="G90" s="24">
         <f>D90*H90</f>
-        <v/>
+        <v>60.495</v>
       </c>
       <c r="H90" s="25" t="n">
         <v>150</v>
@@ -4369,7 +4364,7 @@
       </c>
       <c r="G91" s="24">
         <f>D91*H91</f>
-        <v/>
+        <v>61.275</v>
       </c>
       <c r="H91" s="25" t="n">
         <v>150</v>
@@ -4402,7 +4397,7 @@
       </c>
       <c r="G92" s="24">
         <f>D92*H92</f>
-        <v/>
+        <v>74.235</v>
       </c>
       <c r="H92" s="25" t="n">
         <v>150</v>
@@ -4435,7 +4430,7 @@
       </c>
       <c r="G93" s="24">
         <f>D93*H93</f>
-        <v/>
+        <v>74.7</v>
       </c>
       <c r="H93" s="25" t="n">
         <v>150</v>
@@ -4468,7 +4463,7 @@
       </c>
       <c r="G94" s="24">
         <f>D94*H94</f>
-        <v/>
+        <v>90.525</v>
       </c>
       <c r="H94" s="25" t="n">
         <v>150</v>
@@ -4501,7 +4496,7 @@
       </c>
       <c r="G95" s="24">
         <f>D95*H95</f>
-        <v/>
+        <v>183.54</v>
       </c>
       <c r="H95" s="25" t="n">
         <v>150</v>
@@ -4534,7 +4529,7 @@
       </c>
       <c r="G96" s="24">
         <f>D96*H96</f>
-        <v/>
+        <v>220.335</v>
       </c>
       <c r="H96" s="25" t="n">
         <v>150</v>
@@ -4567,7 +4562,7 @@
       </c>
       <c r="G97" s="24">
         <f>D97*H97</f>
-        <v/>
+        <v>290.20500000000004</v>
       </c>
       <c r="H97" s="25" t="n">
         <v>150</v>
@@ -4600,7 +4595,7 @@
       </c>
       <c r="G98" s="24">
         <f>D98*H98</f>
-        <v/>
+        <v>301.97999999999996</v>
       </c>
       <c r="H98" s="25" t="n">
         <v>150</v>
@@ -4633,7 +4628,7 @@
       </c>
       <c r="G99" s="24">
         <f>D99*H99</f>
-        <v/>
+        <v>313.86</v>
       </c>
       <c r="H99" s="25" t="n">
         <v>150</v>
@@ -4666,7 +4661,7 @@
       </c>
       <c r="G100" s="24">
         <f>D100*H100</f>
-        <v/>
+        <v>354.28499999999997</v>
       </c>
       <c r="H100" s="25" t="n">
         <v>150</v>
@@ -4699,7 +4694,7 @@
       </c>
       <c r="G101" s="24">
         <f>D101*H101</f>
-        <v/>
+        <v>442.96500000000003</v>
       </c>
       <c r="H101" s="25" t="n">
         <v>150</v>
@@ -4732,7 +4727,7 @@
       </c>
       <c r="G102" s="24">
         <f>D102*H102</f>
-        <v/>
+        <v>701.0849999999999</v>
       </c>
       <c r="H102" s="25" t="n">
         <v>150</v>
@@ -4765,7 +4760,7 @@
       </c>
       <c r="G103" s="24">
         <f>D103*H103</f>
-        <v/>
+        <v>886.6949999999999</v>
       </c>
       <c r="H103" s="25" t="n">
         <v>150</v>
@@ -4798,7 +4793,7 @@
       </c>
       <c r="G104" s="24">
         <f>D104*H104</f>
-        <v/>
+        <v>1613.6999999999998</v>
       </c>
       <c r="H104" s="25" t="n">
         <v>150</v>
@@ -4831,7 +4826,7 @@
       </c>
       <c r="G105" s="24">
         <f>D105*H105</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H105" s="25" t="n">
         <v>150</v>
@@ -4864,7 +4859,7 @@
       </c>
       <c r="G106" s="24">
         <f>D106*H106</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H106" s="25" t="n">
         <v>150</v>
@@ -4897,7 +4892,7 @@
       </c>
       <c r="G107" s="24">
         <f>D107*H107</f>
-        <v/>
+        <v>4.38</v>
       </c>
       <c r="H107" s="25" t="n">
         <v>150</v>
@@ -4930,7 +4925,7 @@
       </c>
       <c r="G108" s="24">
         <f>D108*H108</f>
-        <v/>
+        <v>35.01</v>
       </c>
       <c r="H108" s="25" t="n">
         <v>150</v>
@@ -4963,7 +4958,7 @@
       </c>
       <c r="G109" s="24">
         <f>D109*H109</f>
-        <v/>
+        <v>49.875</v>
       </c>
       <c r="H109" s="25" t="n">
         <v>150</v>
@@ -4996,7 +4991,7 @@
       </c>
       <c r="G110" s="24">
         <f>D110*H110</f>
-        <v/>
+        <v>55.754999999999995</v>
       </c>
       <c r="H110" s="25" t="n">
         <v>150</v>
@@ -5029,7 +5024,7 @@
       </c>
       <c r="G111" s="24">
         <f>D111*H111</f>
-        <v/>
+        <v>58.754999999999995</v>
       </c>
       <c r="H111" s="25" t="n">
         <v>150</v>
@@ -5062,7 +5057,7 @@
       </c>
       <c r="G112" s="24">
         <f>D112*H112</f>
-        <v/>
+        <v>65.52000000000001</v>
       </c>
       <c r="H112" s="25" t="n">
         <v>150</v>
@@ -5095,7 +5090,7 @@
       </c>
       <c r="G113" s="24">
         <f>D113*H113</f>
-        <v/>
+        <v>123.99</v>
       </c>
       <c r="H113" s="25" t="n">
         <v>150</v>
@@ -5128,7 +5123,7 @@
       </c>
       <c r="G114" s="24">
         <f>D114*H114</f>
-        <v/>
+        <v>168.52499999999998</v>
       </c>
       <c r="H114" s="25" t="n">
         <v>150</v>
@@ -5161,7 +5156,7 @@
       </c>
       <c r="G115" s="24">
         <f>D115*H115</f>
-        <v/>
+        <v>0.495</v>
       </c>
       <c r="H115" s="25" t="n">
         <v>150</v>
@@ -5194,7 +5189,7 @@
       </c>
       <c r="G116" s="24">
         <f>D116*H116</f>
-        <v/>
+        <v>0.7050000000000001</v>
       </c>
       <c r="H116" s="25" t="n">
         <v>150</v>
@@ -5227,7 +5222,7 @@
       </c>
       <c r="G117" s="24">
         <f>D117*H117</f>
-        <v/>
+        <v>1.7850000000000001</v>
       </c>
       <c r="H117" s="25" t="n">
         <v>150</v>
@@ -5260,7 +5255,7 @@
       </c>
       <c r="G118" s="24">
         <f>D118*H118</f>
-        <v/>
+        <v>2.085</v>
       </c>
       <c r="H118" s="25" t="n">
         <v>150</v>
@@ -5293,7 +5288,7 @@
       </c>
       <c r="G119" s="24">
         <f>D119*H119</f>
-        <v/>
+        <v>2.28</v>
       </c>
       <c r="H119" s="25" t="n">
         <v>150</v>
@@ -5326,7 +5321,7 @@
       </c>
       <c r="G120" s="24">
         <f>D120*H120</f>
-        <v/>
+        <v>2.9850000000000003</v>
       </c>
       <c r="H120" s="25" t="n">
         <v>150</v>
@@ -5359,7 +5354,7 @@
       </c>
       <c r="G121" s="24">
         <f>D121*H121</f>
-        <v/>
+        <v>3.015</v>
       </c>
       <c r="H121" s="25" t="n">
         <v>150</v>
@@ -5392,7 +5387,7 @@
       </c>
       <c r="G122" s="24">
         <f>D122*H122</f>
-        <v/>
+        <v>3.015</v>
       </c>
       <c r="H122" s="25" t="n">
         <v>150</v>
@@ -5425,7 +5420,7 @@
       </c>
       <c r="G123" s="24">
         <f>D123*H123</f>
-        <v/>
+        <v>3.36</v>
       </c>
       <c r="H123" s="25" t="n">
         <v>150</v>
@@ -5458,7 +5453,7 @@
       </c>
       <c r="G124" s="24">
         <f>D124*H124</f>
-        <v/>
+        <v>3.75</v>
       </c>
       <c r="H124" s="25" t="n">
         <v>150</v>
@@ -5491,7 +5486,7 @@
       </c>
       <c r="G125" s="24">
         <f>D125*H125</f>
-        <v/>
+        <v>4.335</v>
       </c>
       <c r="H125" s="25" t="n">
         <v>150</v>
@@ -5524,7 +5519,7 @@
       </c>
       <c r="G126" s="24">
         <f>D126*H126</f>
-        <v/>
+        <v>4.965</v>
       </c>
       <c r="H126" s="25" t="n">
         <v>150</v>
@@ -5557,7 +5552,7 @@
       </c>
       <c r="G127" s="24">
         <f>D127*H127</f>
-        <v/>
+        <v>5.22</v>
       </c>
       <c r="H127" s="25" t="n">
         <v>150</v>
@@ -5590,7 +5585,7 @@
       </c>
       <c r="G128" s="24">
         <f>D128*H128</f>
-        <v/>
+        <v>12.09</v>
       </c>
       <c r="H128" s="25" t="n">
         <v>150</v>
@@ -5623,7 +5618,7 @@
       </c>
       <c r="G129" s="24">
         <f>D129*H129</f>
-        <v/>
+        <v>17.37</v>
       </c>
       <c r="H129" s="25" t="n">
         <v>150</v>
@@ -5656,7 +5651,7 @@
       </c>
       <c r="G130" s="24">
         <f>D130*H130</f>
-        <v/>
+        <v>19.305</v>
       </c>
       <c r="H130" s="25" t="n">
         <v>150</v>
@@ -5689,7 +5684,7 @@
       </c>
       <c r="G131" s="24">
         <f>D131*H131</f>
-        <v/>
+        <v>49.125</v>
       </c>
       <c r="H131" s="25" t="n">
         <v>150</v>
@@ -5722,7 +5717,7 @@
       </c>
       <c r="G132" s="24">
         <f>D132*H132</f>
-        <v/>
+        <v>55.67999999999999</v>
       </c>
       <c r="H132" s="25" t="n">
         <v>150</v>
@@ -5755,7 +5750,7 @@
       </c>
       <c r="G133" s="24">
         <f>D133*H133</f>
-        <v/>
+        <v>67.695</v>
       </c>
       <c r="H133" s="25" t="n">
         <v>150</v>
@@ -5788,7 +5783,7 @@
       </c>
       <c r="G134" s="24">
         <f>D134*H134</f>
-        <v/>
+        <v>76.62</v>
       </c>
       <c r="H134" s="25" t="n">
         <v>150</v>
@@ -5821,7 +5816,7 @@
       </c>
       <c r="G135" s="24">
         <f>D135*H135</f>
-        <v/>
+        <v>95.865</v>
       </c>
       <c r="H135" s="25" t="n">
         <v>150</v>
@@ -5854,7 +5849,7 @@
       </c>
       <c r="G136" s="24">
         <f>D136*H136</f>
-        <v/>
+        <v>99.53999999999999</v>
       </c>
       <c r="H136" s="25" t="n">
         <v>150</v>
@@ -5887,7 +5882,7 @@
       </c>
       <c r="G137" s="24">
         <f>D137*H137</f>
-        <v/>
+        <v>121.35000000000001</v>
       </c>
       <c r="H137" s="25" t="n">
         <v>150</v>
@@ -5920,7 +5915,7 @@
       </c>
       <c r="G138" s="24">
         <f>D138*H138</f>
-        <v/>
+        <v>123.675</v>
       </c>
       <c r="H138" s="25" t="n">
         <v>150</v>
@@ -5953,7 +5948,7 @@
       </c>
       <c r="G139" s="24">
         <f>D139*H139</f>
-        <v/>
+        <v>124.66499999999999</v>
       </c>
       <c r="H139" s="25" t="n">
         <v>150</v>
@@ -5986,7 +5981,7 @@
       </c>
       <c r="G140" s="24">
         <f>D140*H140</f>
-        <v/>
+        <v>126.21000000000001</v>
       </c>
       <c r="H140" s="25" t="n">
         <v>150</v>
@@ -6019,7 +6014,7 @@
       </c>
       <c r="G141" s="24">
         <f>D141*H141</f>
-        <v/>
+        <v>134.34</v>
       </c>
       <c r="H141" s="25" t="n">
         <v>150</v>
@@ -6052,7 +6047,7 @@
       </c>
       <c r="G142" s="24">
         <f>D142*H142</f>
-        <v/>
+        <v>138.285</v>
       </c>
       <c r="H142" s="25" t="n">
         <v>150</v>
@@ -6085,7 +6080,7 @@
       </c>
       <c r="G143" s="24">
         <f>D143*H143</f>
-        <v/>
+        <v>142.92</v>
       </c>
       <c r="H143" s="25" t="n">
         <v>150</v>
@@ -6118,7 +6113,7 @@
       </c>
       <c r="G144" s="24">
         <f>D144*H144</f>
-        <v/>
+        <v>143.43</v>
       </c>
       <c r="H144" s="25" t="n">
         <v>150</v>
@@ -6151,7 +6146,7 @@
       </c>
       <c r="G145" s="24">
         <f>D145*H145</f>
-        <v/>
+        <v>152.94</v>
       </c>
       <c r="H145" s="25" t="n">
         <v>150</v>
@@ -6184,7 +6179,7 @@
       </c>
       <c r="G146" s="24">
         <f>D146*H146</f>
-        <v/>
+        <v>169.965</v>
       </c>
       <c r="H146" s="25" t="n">
         <v>150</v>
@@ -6217,7 +6212,7 @@
       </c>
       <c r="G147" s="24">
         <f>D147*H147</f>
-        <v/>
+        <v>177.37500000000003</v>
       </c>
       <c r="H147" s="25" t="n">
         <v>150</v>
@@ -6250,7 +6245,7 @@
       </c>
       <c r="G148" s="24">
         <f>D148*H148</f>
-        <v/>
+        <v>199.65</v>
       </c>
       <c r="H148" s="25" t="n">
         <v>150</v>
@@ -6283,7 +6278,7 @@
       </c>
       <c r="G149" s="24">
         <f>D149*H149</f>
-        <v/>
+        <v>222.81</v>
       </c>
       <c r="H149" s="25" t="n">
         <v>150</v>
@@ -6316,7 +6311,7 @@
       </c>
       <c r="G150" s="24">
         <f>D150*H150</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H150" s="25" t="n">
         <v>150</v>
@@ -6349,7 +6344,7 @@
       </c>
       <c r="G151" s="24">
         <f>D151*H151</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H151" s="25" t="n">
         <v>150</v>
@@ -6382,7 +6377,7 @@
       </c>
       <c r="G152" s="24">
         <f>D152*H152</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H152" s="25" t="n">
         <v>150</v>
@@ -6415,7 +6410,7 @@
       </c>
       <c r="G153" s="24">
         <f>D153*H153</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H153" s="25" t="n">
         <v>150</v>
@@ -6448,7 +6443,7 @@
       </c>
       <c r="G154" s="24">
         <f>D154*H154</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H154" s="25" t="n">
         <v>150</v>
@@ -6481,7 +6476,7 @@
       </c>
       <c r="G155" s="24">
         <f>D155*H155</f>
-        <v/>
+        <v>9.18</v>
       </c>
       <c r="H155" s="25" t="n">
         <v>150</v>
@@ -6514,7 +6509,7 @@
       </c>
       <c r="G156" s="24">
         <f>D156*H156</f>
-        <v/>
+        <v>35.955</v>
       </c>
       <c r="H156" s="25" t="n">
         <v>150</v>
@@ -6547,7 +6542,7 @@
       </c>
       <c r="G157" s="24">
         <f>D157*H157</f>
-        <v/>
+        <v>52.08</v>
       </c>
       <c r="H157" s="25" t="n">
         <v>150</v>
@@ -6580,7 +6575,7 @@
       </c>
       <c r="G158" s="24">
         <f>D158*H158</f>
-        <v/>
+        <v>61.14</v>
       </c>
       <c r="H158" s="25" t="n">
         <v>150</v>
@@ -6613,7 +6608,7 @@
       </c>
       <c r="G159" s="24">
         <f>D159*H159</f>
-        <v/>
+        <v>66.48</v>
       </c>
       <c r="H159" s="25" t="n">
         <v>150</v>
@@ -6646,7 +6641,7 @@
       </c>
       <c r="G160" s="24">
         <f>D160*H160</f>
-        <v/>
+        <v>71.745</v>
       </c>
       <c r="H160" s="25" t="n">
         <v>150</v>
@@ -6679,7 +6674,7 @@
       </c>
       <c r="G161" s="24">
         <f>D161*H161</f>
-        <v/>
+        <v>74.89500000000001</v>
       </c>
       <c r="H161" s="25" t="n">
         <v>150</v>
@@ -6712,7 +6707,7 @@
       </c>
       <c r="G162" s="24">
         <f>D162*H162</f>
-        <v/>
+        <v>94.57499999999999</v>
       </c>
       <c r="H162" s="25" t="n">
         <v>150</v>
@@ -6745,7 +6740,7 @@
       </c>
       <c r="G163" s="24">
         <f>D163*H163</f>
-        <v/>
+        <v>98.415</v>
       </c>
       <c r="H163" s="25" t="n">
         <v>150</v>
@@ -6778,7 +6773,7 @@
       </c>
       <c r="G164" s="24">
         <f>D164*H164</f>
-        <v/>
+        <v>163.245</v>
       </c>
       <c r="H164" s="25" t="n">
         <v>150</v>
@@ -6811,7 +6806,7 @@
       </c>
       <c r="G165" s="24">
         <f>D165*H165</f>
-        <v/>
+        <v>204.72</v>
       </c>
       <c r="H165" s="25" t="n">
         <v>150</v>
@@ -6844,7 +6839,7 @@
       </c>
       <c r="G166" s="24">
         <f>D166*H166</f>
-        <v/>
+        <v>9.36</v>
       </c>
       <c r="H166" s="25" t="n">
         <v>150</v>
@@ -6877,7 +6872,7 @@
       </c>
       <c r="G167" s="24">
         <f>D167*H167</f>
-        <v/>
+        <v>11.25</v>
       </c>
       <c r="H167" s="25" t="n">
         <v>150</v>
@@ -6910,7 +6905,7 @@
       </c>
       <c r="G168" s="24">
         <f>D168*H168</f>
-        <v/>
+        <v>11.475</v>
       </c>
       <c r="H168" s="25" t="n">
         <v>150</v>
@@ -6943,7 +6938,7 @@
       </c>
       <c r="G169" s="24">
         <f>D169*H169</f>
-        <v/>
+        <v>12.254999999999999</v>
       </c>
       <c r="H169" s="25" t="n">
         <v>150</v>
@@ -6976,7 +6971,7 @@
       </c>
       <c r="G170" s="24">
         <f>D170*H170</f>
-        <v/>
+        <v>12.525</v>
       </c>
       <c r="H170" s="25" t="n">
         <v>150</v>
@@ -7009,7 +7004,7 @@
       </c>
       <c r="G171" s="24">
         <f>D171*H171</f>
-        <v/>
+        <v>14.97</v>
       </c>
       <c r="H171" s="25" t="n">
         <v>150</v>
@@ -7042,7 +7037,7 @@
       </c>
       <c r="G172" s="24">
         <f>D172*H172</f>
-        <v/>
+        <v>17.985</v>
       </c>
       <c r="H172" s="25" t="n">
         <v>150</v>
@@ -7075,7 +7070,7 @@
       </c>
       <c r="G173" s="24">
         <f>D173*H173</f>
-        <v/>
+        <v>35.46</v>
       </c>
       <c r="H173" s="25" t="n">
         <v>150</v>
@@ -7108,7 +7103,7 @@
       </c>
       <c r="G174" s="24">
         <f>D174*H174</f>
-        <v/>
+        <v>37.185</v>
       </c>
       <c r="H174" s="25" t="n">
         <v>150</v>
@@ -7141,7 +7136,7 @@
       </c>
       <c r="G175" s="24">
         <f>D175*H175</f>
-        <v/>
+        <v>44.31</v>
       </c>
       <c r="H175" s="25" t="n">
         <v>150</v>
@@ -7174,7 +7169,7 @@
       </c>
       <c r="G176" s="24">
         <f>D176*H176</f>
-        <v/>
+        <v>45.795</v>
       </c>
       <c r="H176" s="25" t="n">
         <v>150</v>
@@ -7207,7 +7202,7 @@
       </c>
       <c r="G177" s="24">
         <f>D177*H177</f>
-        <v/>
+        <v>47.985</v>
       </c>
       <c r="H177" s="25" t="n">
         <v>150</v>
@@ -7240,7 +7235,7 @@
       </c>
       <c r="G178" s="24">
         <f>D178*H178</f>
-        <v/>
+        <v>49.23</v>
       </c>
       <c r="H178" s="25" t="n">
         <v>150</v>
@@ -7273,7 +7268,7 @@
       </c>
       <c r="G179" s="24">
         <f>D179*H179</f>
-        <v/>
+        <v>51.434999999999995</v>
       </c>
       <c r="H179" s="25" t="n">
         <v>150</v>
@@ -7306,7 +7301,7 @@
       </c>
       <c r="G180" s="24">
         <f>D180*H180</f>
-        <v/>
+        <v>53.580000000000005</v>
       </c>
       <c r="H180" s="25" t="n">
         <v>150</v>
@@ -7339,7 +7334,7 @@
       </c>
       <c r="G181" s="24">
         <f>D181*H181</f>
-        <v/>
+        <v>53.775</v>
       </c>
       <c r="H181" s="25" t="n">
         <v>150</v>
@@ -7372,7 +7367,7 @@
       </c>
       <c r="G182" s="24">
         <f>D182*H182</f>
-        <v/>
+        <v>57.105</v>
       </c>
       <c r="H182" s="25" t="n">
         <v>150</v>
@@ -7405,7 +7400,7 @@
       </c>
       <c r="G183" s="24">
         <f>D183*H183</f>
-        <v/>
+        <v>57.585</v>
       </c>
       <c r="H183" s="25" t="n">
         <v>150</v>
@@ -7438,7 +7433,7 @@
       </c>
       <c r="G184" s="24">
         <f>D184*H184</f>
-        <v/>
+        <v>60.045</v>
       </c>
       <c r="H184" s="25" t="n">
         <v>150</v>
@@ -7471,7 +7466,7 @@
       </c>
       <c r="G185" s="24">
         <f>D185*H185</f>
-        <v/>
+        <v>60.87</v>
       </c>
       <c r="H185" s="25" t="n">
         <v>150</v>
@@ -7504,7 +7499,7 @@
       </c>
       <c r="G186" s="24">
         <f>D186*H186</f>
-        <v/>
+        <v>62.085</v>
       </c>
       <c r="H186" s="25" t="n">
         <v>150</v>
@@ -7537,7 +7532,7 @@
       </c>
       <c r="G187" s="24">
         <f>D187*H187</f>
-        <v/>
+        <v>74.94</v>
       </c>
       <c r="H187" s="25" t="n">
         <v>150</v>
@@ -7570,7 +7565,7 @@
       </c>
       <c r="G188" s="24">
         <f>D188*H188</f>
-        <v/>
+        <v>77.97</v>
       </c>
       <c r="H188" s="25" t="n">
         <v>150</v>
@@ -7603,7 +7598,7 @@
       </c>
       <c r="G189" s="24">
         <f>D189*H189</f>
-        <v/>
+        <v>89.775</v>
       </c>
       <c r="H189" s="25" t="n">
         <v>150</v>
@@ -7636,7 +7631,7 @@
       </c>
       <c r="G190" s="24">
         <f>D190*H190</f>
-        <v/>
+        <v>92.805</v>
       </c>
       <c r="H190" s="25" t="n">
         <v>150</v>
@@ -7669,7 +7664,7 @@
       </c>
       <c r="G191" s="24">
         <f>D191*H191</f>
-        <v/>
+        <v>103.23</v>
       </c>
       <c r="H191" s="25" t="n">
         <v>150</v>
@@ -7702,7 +7697,7 @@
       </c>
       <c r="G192" s="24">
         <f>D192*H192</f>
-        <v/>
+        <v>112.22999999999999</v>
       </c>
       <c r="H192" s="25" t="n">
         <v>150</v>
@@ -7735,7 +7730,7 @@
       </c>
       <c r="G193" s="24">
         <f>D193*H193</f>
-        <v/>
+        <v>121.71000000000001</v>
       </c>
       <c r="H193" s="25" t="n">
         <v>150</v>
@@ -7768,7 +7763,7 @@
       </c>
       <c r="G194" s="24">
         <f>D194*H194</f>
-        <v/>
+        <v>138.42</v>
       </c>
       <c r="H194" s="25" t="n">
         <v>150</v>
@@ -7801,7 +7796,7 @@
       </c>
       <c r="G195" s="24">
         <f>D195*H195</f>
-        <v/>
+        <v>263.58000000000004</v>
       </c>
       <c r="H195" s="25" t="n">
         <v>150</v>
@@ -7834,7 +7829,7 @@
       </c>
       <c r="G196" s="24">
         <f>D196*H196</f>
-        <v/>
+        <v>289.665</v>
       </c>
       <c r="H196" s="25" t="n">
         <v>150</v>
@@ -7867,7 +7862,7 @@
       </c>
       <c r="G197" s="24">
         <f>D197*H197</f>
-        <v/>
+        <v>378.495</v>
       </c>
       <c r="H197" s="25" t="n">
         <v>150</v>
@@ -7900,7 +7895,7 @@
       </c>
       <c r="G198" s="24">
         <f>D198*H198</f>
-        <v/>
+        <v>447.36</v>
       </c>
       <c r="H198" s="25" t="n">
         <v>150</v>
@@ -7933,7 +7928,7 @@
       </c>
       <c r="G199" s="24">
         <f>D199*H199</f>
-        <v/>
+        <v>463.14000000000004</v>
       </c>
       <c r="H199" s="25" t="n">
         <v>150</v>
@@ -7966,7 +7961,7 @@
       </c>
       <c r="G200" s="24">
         <f>D200*H200</f>
-        <v/>
+        <v>1.38</v>
       </c>
       <c r="H200" s="25" t="n">
         <v>150</v>
@@ -7999,7 +7994,7 @@
       </c>
       <c r="G201" s="24">
         <f>D201*H201</f>
-        <v/>
+        <v>3.3150000000000004</v>
       </c>
       <c r="H201" s="25" t="n">
         <v>150</v>
@@ -8032,7 +8027,7 @@
       </c>
       <c r="G202" s="24">
         <f>D202*H202</f>
-        <v/>
+        <v>4.62</v>
       </c>
       <c r="H202" s="25" t="n">
         <v>150</v>
@@ -8065,7 +8060,7 @@
       </c>
       <c r="G203" s="24">
         <f>D203*H203</f>
-        <v/>
+        <v>53.415000000000006</v>
       </c>
       <c r="H203" s="25" t="n">
         <v>150</v>
@@ -8098,7 +8093,7 @@
       </c>
       <c r="G204" s="24">
         <f>D204*H204</f>
-        <v/>
+        <v>63.239999999999995</v>
       </c>
       <c r="H204" s="25" t="n">
         <v>150</v>
@@ -8131,7 +8126,7 @@
       </c>
       <c r="G205" s="24">
         <f>D205*H205</f>
-        <v/>
+        <v>117.85499999999999</v>
       </c>
       <c r="H205" s="25" t="n">
         <v>150</v>
@@ -8164,7 +8159,7 @@
       </c>
       <c r="G206" s="24">
         <f>D206*H206</f>
-        <v/>
+        <v>214.695</v>
       </c>
       <c r="H206" s="25" t="n">
         <v>150</v>
@@ -8197,7 +8192,7 @@
       </c>
       <c r="G207" s="24">
         <f>D207*H207</f>
-        <v/>
+        <v>243.97500000000002</v>
       </c>
       <c r="H207" s="25" t="n">
         <v>150</v>
@@ -8230,7 +8225,7 @@
       </c>
       <c r="G208" s="24">
         <f>D208*H208</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H208" s="25" t="n">
         <v>150</v>
@@ -8263,7 +8258,7 @@
       </c>
       <c r="G209" s="24">
         <f>D209*H209</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H209" s="25" t="n">
         <v>150</v>
@@ -8296,7 +8291,7 @@
       </c>
       <c r="G210" s="24">
         <f>D210*H210</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H210" s="25" t="n">
         <v>150</v>
@@ -8329,7 +8324,7 @@
       </c>
       <c r="G211" s="24">
         <f>D211*H211</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H211" s="25" t="n">
         <v>150</v>
@@ -8362,7 +8357,7 @@
       </c>
       <c r="G212" s="24">
         <f>D212*H212</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H212" s="25" t="n">
         <v>150</v>
@@ -8395,7 +8390,7 @@
       </c>
       <c r="G213" s="24">
         <f>D213*H213</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H213" s="25" t="n">
         <v>150</v>
@@ -8428,7 +8423,7 @@
       </c>
       <c r="G214" s="24">
         <f>D214*H214</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H214" s="25" t="n">
         <v>150</v>
@@ -8461,7 +8456,7 @@
       </c>
       <c r="G215" s="24">
         <f>D215*H215</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H215" s="25" t="n">
         <v>150</v>
@@ -8494,7 +8489,7 @@
       </c>
       <c r="G216" s="24">
         <f>D216*H216</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H216" s="25" t="n">
         <v>150</v>
@@ -8527,7 +8522,7 @@
       </c>
       <c r="G217" s="24">
         <f>D217*H217</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H217" s="25" t="n">
         <v>150</v>
@@ -8560,7 +8555,7 @@
       </c>
       <c r="G218" s="24">
         <f>D218*H218</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H218" s="25" t="n">
         <v>150</v>
@@ -8593,7 +8588,7 @@
       </c>
       <c r="G219" s="24">
         <f>D219*H219</f>
-        <v/>
+        <v>0.8699999999999999</v>
       </c>
       <c r="H219" s="25" t="n">
         <v>150</v>
@@ -8626,7 +8621,7 @@
       </c>
       <c r="G220" s="24">
         <f>D220*H220</f>
-        <v/>
+        <v>4.8149999999999995</v>
       </c>
       <c r="H220" s="25" t="n">
         <v>150</v>
@@ -8659,7 +8654,7 @@
       </c>
       <c r="G221" s="24">
         <f>D221*H221</f>
-        <v/>
+        <v>9.93</v>
       </c>
       <c r="H221" s="25" t="n">
         <v>150</v>
@@ -8692,7 +8687,7 @@
       </c>
       <c r="G222" s="24">
         <f>D222*H222</f>
-        <v/>
+        <v>11.07</v>
       </c>
       <c r="H222" s="25" t="n">
         <v>150</v>
@@ -8725,7 +8720,7 @@
       </c>
       <c r="G223" s="24">
         <f>D223*H223</f>
-        <v/>
+        <v>11.805000000000001</v>
       </c>
       <c r="H223" s="25" t="n">
         <v>150</v>
@@ -8758,7 +8753,7 @@
       </c>
       <c r="G224" s="24">
         <f>D224*H224</f>
-        <v/>
+        <v>17.400000000000002</v>
       </c>
       <c r="H224" s="25" t="n">
         <v>150</v>
@@ -8791,7 +8786,7 @@
       </c>
       <c r="G225" s="24">
         <f>D225*H225</f>
-        <v/>
+        <v>17.535</v>
       </c>
       <c r="H225" s="25" t="n">
         <v>150</v>
@@ -8824,7 +8819,7 @@
       </c>
       <c r="G226" s="24">
         <f>D226*H226</f>
-        <v/>
+        <v>17.625</v>
       </c>
       <c r="H226" s="25" t="n">
         <v>150</v>
@@ -8857,7 +8852,7 @@
       </c>
       <c r="G227" s="24">
         <f>D227*H227</f>
-        <v/>
+        <v>19.334999999999997</v>
       </c>
       <c r="H227" s="25" t="n">
         <v>150</v>
@@ -8890,7 +8885,7 @@
       </c>
       <c r="G228" s="24">
         <f>D228*H228</f>
-        <v/>
+        <v>20.37</v>
       </c>
       <c r="H228" s="25" t="n">
         <v>150</v>
@@ -8923,7 +8918,7 @@
       </c>
       <c r="G229" s="24">
         <f>D229*H229</f>
-        <v/>
+        <v>21.555</v>
       </c>
       <c r="H229" s="25" t="n">
         <v>150</v>
@@ -8956,7 +8951,7 @@
       </c>
       <c r="G230" s="24">
         <f>D230*H230</f>
-        <v/>
+        <v>22.155</v>
       </c>
       <c r="H230" s="25" t="n">
         <v>150</v>
@@ -8989,7 +8984,7 @@
       </c>
       <c r="G231" s="24">
         <f>D231*H231</f>
-        <v/>
+        <v>22.830000000000002</v>
       </c>
       <c r="H231" s="25" t="n">
         <v>150</v>
@@ -9022,7 +9017,7 @@
       </c>
       <c r="G232" s="24">
         <f>D232*H232</f>
-        <v/>
+        <v>23.82</v>
       </c>
       <c r="H232" s="25" t="n">
         <v>150</v>
@@ -9055,7 +9050,7 @@
       </c>
       <c r="G233" s="24">
         <f>D233*H233</f>
-        <v/>
+        <v>23.925</v>
       </c>
       <c r="H233" s="25" t="n">
         <v>150</v>
@@ -9088,7 +9083,7 @@
       </c>
       <c r="G234" s="24">
         <f>D234*H234</f>
-        <v/>
+        <v>24.195</v>
       </c>
       <c r="H234" s="25" t="n">
         <v>150</v>
@@ -9121,7 +9116,7 @@
       </c>
       <c r="G235" s="24">
         <f>D235*H235</f>
-        <v/>
+        <v>26.474999999999998</v>
       </c>
       <c r="H235" s="25" t="n">
         <v>150</v>
@@ -9154,7 +9149,7 @@
       </c>
       <c r="G236" s="24">
         <f>D236*H236</f>
-        <v/>
+        <v>28.02</v>
       </c>
       <c r="H236" s="25" t="n">
         <v>150</v>
@@ -9187,7 +9182,7 @@
       </c>
       <c r="G237" s="24">
         <f>D237*H237</f>
-        <v/>
+        <v>30.87</v>
       </c>
       <c r="H237" s="25" t="n">
         <v>150</v>
@@ -9220,7 +9215,7 @@
       </c>
       <c r="G238" s="24">
         <f>D238*H238</f>
-        <v/>
+        <v>31.605</v>
       </c>
       <c r="H238" s="25" t="n">
         <v>150</v>
@@ -9253,7 +9248,7 @@
       </c>
       <c r="G239" s="24">
         <f>D239*H239</f>
-        <v/>
+        <v>32.445</v>
       </c>
       <c r="H239" s="25" t="n">
         <v>150</v>
@@ -9286,7 +9281,7 @@
       </c>
       <c r="G240" s="24">
         <f>D240*H240</f>
-        <v/>
+        <v>34.935</v>
       </c>
       <c r="H240" s="25" t="n">
         <v>150</v>
@@ -9319,7 +9314,7 @@
       </c>
       <c r="G241" s="24">
         <f>D241*H241</f>
-        <v/>
+        <v>37.05</v>
       </c>
       <c r="H241" s="25" t="n">
         <v>150</v>
@@ -9352,7 +9347,7 @@
       </c>
       <c r="G242" s="24">
         <f>D242*H242</f>
-        <v/>
+        <v>37.35</v>
       </c>
       <c r="H242" s="25" t="n">
         <v>150</v>
@@ -9385,7 +9380,7 @@
       </c>
       <c r="G243" s="24">
         <f>D243*H243</f>
-        <v/>
+        <v>37.455</v>
       </c>
       <c r="H243" s="25" t="n">
         <v>150</v>
@@ -9418,7 +9413,7 @@
       </c>
       <c r="G244" s="24">
         <f>D244*H244</f>
-        <v/>
+        <v>38.355</v>
       </c>
       <c r="H244" s="25" t="n">
         <v>150</v>
@@ -9451,7 +9446,7 @@
       </c>
       <c r="G245" s="24">
         <f>D245*H245</f>
-        <v/>
+        <v>38.835</v>
       </c>
       <c r="H245" s="25" t="n">
         <v>150</v>
@@ -9484,7 +9479,7 @@
       </c>
       <c r="G246" s="24">
         <f>D246*H246</f>
-        <v/>
+        <v>42.33</v>
       </c>
       <c r="H246" s="25" t="n">
         <v>150</v>
@@ -9517,7 +9512,7 @@
       </c>
       <c r="G247" s="24">
         <f>D247*H247</f>
-        <v/>
+        <v>42.449999999999996</v>
       </c>
       <c r="H247" s="25" t="n">
         <v>150</v>
@@ -9550,7 +9545,7 @@
       </c>
       <c r="G248" s="24">
         <f>D248*H248</f>
-        <v/>
+        <v>44.445</v>
       </c>
       <c r="H248" s="25" t="n">
         <v>150</v>
@@ -9583,7 +9578,7 @@
       </c>
       <c r="G249" s="24">
         <f>D249*H249</f>
-        <v/>
+        <v>45.824999999999996</v>
       </c>
       <c r="H249" s="25" t="n">
         <v>150</v>
@@ -9616,7 +9611,7 @@
       </c>
       <c r="G250" s="24">
         <f>D250*H250</f>
-        <v/>
+        <v>52.695</v>
       </c>
       <c r="H250" s="25" t="n">
         <v>150</v>
@@ -9649,7 +9644,7 @@
       </c>
       <c r="G251" s="24">
         <f>D251*H251</f>
-        <v/>
+        <v>57.254999999999995</v>
       </c>
       <c r="H251" s="25" t="n">
         <v>150</v>
@@ -9682,7 +9677,7 @@
       </c>
       <c r="G252" s="24">
         <f>D252*H252</f>
-        <v/>
+        <v>59.144999999999996</v>
       </c>
       <c r="H252" s="25" t="n">
         <v>150</v>
@@ -9715,7 +9710,7 @@
       </c>
       <c r="G253" s="24">
         <f>D253*H253</f>
-        <v/>
+        <v>60.03</v>
       </c>
       <c r="H253" s="25" t="n">
         <v>150</v>
@@ -9748,7 +9743,7 @@
       </c>
       <c r="G254" s="24">
         <f>D254*H254</f>
-        <v/>
+        <v>60.075</v>
       </c>
       <c r="H254" s="25" t="n">
         <v>150</v>
@@ -9781,7 +9776,7 @@
       </c>
       <c r="G255" s="24">
         <f>D255*H255</f>
-        <v/>
+        <v>66.48</v>
       </c>
       <c r="H255" s="25" t="n">
         <v>150</v>
@@ -9814,7 +9809,7 @@
       </c>
       <c r="G256" s="24">
         <f>D256*H256</f>
-        <v/>
+        <v>67.26</v>
       </c>
       <c r="H256" s="25" t="n">
         <v>150</v>
@@ -9847,7 +9842,7 @@
       </c>
       <c r="G257" s="24">
         <f>D257*H257</f>
-        <v/>
+        <v>72.33</v>
       </c>
       <c r="H257" s="25" t="n">
         <v>150</v>
@@ -9880,7 +9875,7 @@
       </c>
       <c r="G258" s="24">
         <f>D258*H258</f>
-        <v/>
+        <v>76.185</v>
       </c>
       <c r="H258" s="25" t="n">
         <v>150</v>
@@ -9913,7 +9908,7 @@
       </c>
       <c r="G259" s="24">
         <f>D259*H259</f>
-        <v/>
+        <v>79.90499999999999</v>
       </c>
       <c r="H259" s="25" t="n">
         <v>150</v>
@@ -9946,7 +9941,7 @@
       </c>
       <c r="G260" s="24">
         <f>D260*H260</f>
-        <v/>
+        <v>82.08</v>
       </c>
       <c r="H260" s="25" t="n">
         <v>150</v>
@@ -9979,7 +9974,7 @@
       </c>
       <c r="G261" s="24">
         <f>D261*H261</f>
-        <v/>
+        <v>82.33500000000001</v>
       </c>
       <c r="H261" s="25" t="n">
         <v>150</v>
@@ -10012,7 +10007,7 @@
       </c>
       <c r="G262" s="24">
         <f>D262*H262</f>
-        <v/>
+        <v>85.28999999999999</v>
       </c>
       <c r="H262" s="25" t="n">
         <v>150</v>
@@ -10045,7 +10040,7 @@
       </c>
       <c r="G263" s="24">
         <f>D263*H263</f>
-        <v/>
+        <v>87.12</v>
       </c>
       <c r="H263" s="25" t="n">
         <v>150</v>
@@ -10078,7 +10073,7 @@
       </c>
       <c r="G264" s="24">
         <f>D264*H264</f>
-        <v/>
+        <v>88.05</v>
       </c>
       <c r="H264" s="25" t="n">
         <v>150</v>
@@ -10111,7 +10106,7 @@
       </c>
       <c r="G265" s="24">
         <f>D265*H265</f>
-        <v/>
+        <v>89.39999999999999</v>
       </c>
       <c r="H265" s="25" t="n">
         <v>150</v>
@@ -10144,7 +10139,7 @@
       </c>
       <c r="G266" s="24">
         <f>D266*H266</f>
-        <v/>
+        <v>97.965</v>
       </c>
       <c r="H266" s="25" t="n">
         <v>150</v>
@@ -10177,7 +10172,7 @@
       </c>
       <c r="G267" s="24">
         <f>D267*H267</f>
-        <v/>
+        <v>99.63</v>
       </c>
       <c r="H267" s="25" t="n">
         <v>150</v>
@@ -10210,7 +10205,7 @@
       </c>
       <c r="G268" s="24">
         <f>D268*H268</f>
-        <v/>
+        <v>100.215</v>
       </c>
       <c r="H268" s="25" t="n">
         <v>150</v>
@@ -10243,7 +10238,7 @@
       </c>
       <c r="G269" s="24">
         <f>D269*H269</f>
-        <v/>
+        <v>103.785</v>
       </c>
       <c r="H269" s="25" t="n">
         <v>150</v>
@@ -10276,7 +10271,7 @@
       </c>
       <c r="G270" s="24">
         <f>D270*H270</f>
-        <v/>
+        <v>105.6</v>
       </c>
       <c r="H270" s="25" t="n">
         <v>150</v>
@@ -10309,7 +10304,7 @@
       </c>
       <c r="G271" s="24">
         <f>D271*H271</f>
-        <v/>
+        <v>109.17</v>
       </c>
       <c r="H271" s="25" t="n">
         <v>150</v>
@@ -10342,7 +10337,7 @@
       </c>
       <c r="G272" s="24">
         <f>D272*H272</f>
-        <v/>
+        <v>109.875</v>
       </c>
       <c r="H272" s="25" t="n">
         <v>150</v>
@@ -10375,7 +10370,7 @@
       </c>
       <c r="G273" s="24">
         <f>D273*H273</f>
-        <v/>
+        <v>113.04</v>
       </c>
       <c r="H273" s="25" t="n">
         <v>150</v>
@@ -10408,7 +10403,7 @@
       </c>
       <c r="G274" s="24">
         <f>D274*H274</f>
-        <v/>
+        <v>115.78500000000001</v>
       </c>
       <c r="H274" s="25" t="n">
         <v>150</v>
@@ -10441,7 +10436,7 @@
       </c>
       <c r="G275" s="24">
         <f>D275*H275</f>
-        <v/>
+        <v>118.48500000000001</v>
       </c>
       <c r="H275" s="25" t="n">
         <v>150</v>
@@ -10474,7 +10469,7 @@
       </c>
       <c r="G276" s="24">
         <f>D276*H276</f>
-        <v/>
+        <v>124.32</v>
       </c>
       <c r="H276" s="25" t="n">
         <v>150</v>
@@ -10507,7 +10502,7 @@
       </c>
       <c r="G277" s="24">
         <f>D277*H277</f>
-        <v/>
+        <v>124.77</v>
       </c>
       <c r="H277" s="25" t="n">
         <v>150</v>
@@ -10540,7 +10535,7 @@
       </c>
       <c r="G278" s="24">
         <f>D278*H278</f>
-        <v/>
+        <v>132.3</v>
       </c>
       <c r="H278" s="25" t="n">
         <v>150</v>
@@ -10573,7 +10568,7 @@
       </c>
       <c r="G279" s="24">
         <f>D279*H279</f>
-        <v/>
+        <v>132.975</v>
       </c>
       <c r="H279" s="25" t="n">
         <v>150</v>
@@ -10606,7 +10601,7 @@
       </c>
       <c r="G280" s="24">
         <f>D280*H280</f>
-        <v/>
+        <v>138.225</v>
       </c>
       <c r="H280" s="25" t="n">
         <v>150</v>
@@ -10639,7 +10634,7 @@
       </c>
       <c r="G281" s="24">
         <f>D281*H281</f>
-        <v/>
+        <v>141.54</v>
       </c>
       <c r="H281" s="25" t="n">
         <v>150</v>
@@ -10672,7 +10667,7 @@
       </c>
       <c r="G282" s="24">
         <f>D282*H282</f>
-        <v/>
+        <v>169.695</v>
       </c>
       <c r="H282" s="25" t="n">
         <v>150</v>
@@ -10705,7 +10700,7 @@
       </c>
       <c r="G283" s="24">
         <f>D283*H283</f>
-        <v/>
+        <v>176.88</v>
       </c>
       <c r="H283" s="25" t="n">
         <v>150</v>
@@ -10738,7 +10733,7 @@
       </c>
       <c r="G284" s="24">
         <f>D284*H284</f>
-        <v/>
+        <v>187.035</v>
       </c>
       <c r="H284" s="25" t="n">
         <v>150</v>
@@ -10771,7 +10766,7 @@
       </c>
       <c r="G285" s="24">
         <f>D285*H285</f>
-        <v/>
+        <v>187.05</v>
       </c>
       <c r="H285" s="25" t="n">
         <v>150</v>
@@ -10804,7 +10799,7 @@
       </c>
       <c r="G286" s="24">
         <f>D286*H286</f>
-        <v/>
+        <v>197.57999999999998</v>
       </c>
       <c r="H286" s="25" t="n">
         <v>150</v>
@@ -10837,7 +10832,7 @@
       </c>
       <c r="G287" s="24">
         <f>D287*H287</f>
-        <v/>
+        <v>199.875</v>
       </c>
       <c r="H287" s="25" t="n">
         <v>150</v>
@@ -10870,7 +10865,7 @@
       </c>
       <c r="G288" s="24">
         <f>D288*H288</f>
-        <v/>
+        <v>216.495</v>
       </c>
       <c r="H288" s="25" t="n">
         <v>150</v>
@@ -10903,7 +10898,7 @@
       </c>
       <c r="G289" s="24">
         <f>D289*H289</f>
-        <v/>
+        <v>217.53</v>
       </c>
       <c r="H289" s="25" t="n">
         <v>150</v>
@@ -10936,7 +10931,7 @@
       </c>
       <c r="G290" s="24">
         <f>D290*H290</f>
-        <v/>
+        <v>240.795</v>
       </c>
       <c r="H290" s="25" t="n">
         <v>150</v>
@@ -10969,7 +10964,7 @@
       </c>
       <c r="G291" s="24">
         <f>D291*H291</f>
-        <v/>
+        <v>241.14</v>
       </c>
       <c r="H291" s="25" t="n">
         <v>150</v>
@@ -11002,7 +10997,7 @@
       </c>
       <c r="G292" s="24">
         <f>D292*H292</f>
-        <v/>
+        <v>247.875</v>
       </c>
       <c r="H292" s="25" t="n">
         <v>150</v>
@@ -11035,7 +11030,7 @@
       </c>
       <c r="G293" s="24">
         <f>D293*H293</f>
-        <v/>
+        <v>256.53</v>
       </c>
       <c r="H293" s="25" t="n">
         <v>150</v>
@@ -11068,7 +11063,7 @@
       </c>
       <c r="G294" s="24">
         <f>D294*H294</f>
-        <v/>
+        <v>258.075</v>
       </c>
       <c r="H294" s="25" t="n">
         <v>150</v>
@@ -11101,7 +11096,7 @@
       </c>
       <c r="G295" s="24">
         <f>D295*H295</f>
-        <v/>
+        <v>258.315</v>
       </c>
       <c r="H295" s="25" t="n">
         <v>150</v>
@@ -11134,7 +11129,7 @@
       </c>
       <c r="G296" s="24">
         <f>D296*H296</f>
-        <v/>
+        <v>260.055</v>
       </c>
       <c r="H296" s="25" t="n">
         <v>150</v>
@@ -11167,7 +11162,7 @@
       </c>
       <c r="G297" s="24">
         <f>D297*H297</f>
-        <v/>
+        <v>263.715</v>
       </c>
       <c r="H297" s="25" t="n">
         <v>150</v>
@@ -11200,7 +11195,7 @@
       </c>
       <c r="G298" s="24">
         <f>D298*H298</f>
-        <v/>
+        <v>269.55</v>
       </c>
       <c r="H298" s="25" t="n">
         <v>150</v>
@@ -11233,7 +11228,7 @@
       </c>
       <c r="G299" s="24">
         <f>D299*H299</f>
-        <v/>
+        <v>278.31</v>
       </c>
       <c r="H299" s="25" t="n">
         <v>150</v>
@@ -11266,7 +11261,7 @@
       </c>
       <c r="G300" s="24">
         <f>D300*H300</f>
-        <v/>
+        <v>342.555</v>
       </c>
       <c r="H300" s="25" t="n">
         <v>150</v>
@@ -11299,7 +11294,7 @@
       </c>
       <c r="G301" s="24">
         <f>D301*H301</f>
-        <v/>
+        <v>353.13</v>
       </c>
       <c r="H301" s="25" t="n">
         <v>150</v>
@@ -11332,7 +11327,7 @@
       </c>
       <c r="G302" s="24">
         <f>D302*H302</f>
-        <v/>
+        <v>477.975</v>
       </c>
       <c r="H302" s="25" t="n">
         <v>150</v>
@@ -11365,7 +11360,7 @@
       </c>
       <c r="G303" s="24">
         <f>D303*H303</f>
-        <v/>
+        <v>1.5750000000000002</v>
       </c>
       <c r="H303" s="25" t="n">
         <v>150</v>
@@ -11398,7 +11393,7 @@
       </c>
       <c r="G304" s="24">
         <f>D304*H304</f>
-        <v/>
+        <v>1.77</v>
       </c>
       <c r="H304" s="25" t="n">
         <v>150</v>
@@ -11431,7 +11426,7 @@
       </c>
       <c r="G305" s="24">
         <f>D305*H305</f>
-        <v/>
+        <v>3.135</v>
       </c>
       <c r="H305" s="25" t="n">
         <v>150</v>
@@ -11464,7 +11459,7 @@
       </c>
       <c r="G306" s="24">
         <f>D306*H306</f>
-        <v/>
+        <v>3.8400000000000003</v>
       </c>
       <c r="H306" s="25" t="n">
         <v>150</v>
@@ -11497,7 +11492,7 @@
       </c>
       <c r="G307" s="24">
         <f>D307*H307</f>
-        <v/>
+        <v>4.3500000000000005</v>
       </c>
       <c r="H307" s="25" t="n">
         <v>150</v>
@@ -11530,7 +11525,7 @@
       </c>
       <c r="G308" s="24">
         <f>D308*H308</f>
-        <v/>
+        <v>7.74</v>
       </c>
       <c r="H308" s="25" t="n">
         <v>150</v>
@@ -11563,7 +11558,7 @@
       </c>
       <c r="G309" s="24">
         <f>D309*H309</f>
-        <v/>
+        <v>7.83</v>
       </c>
       <c r="H309" s="25" t="n">
         <v>150</v>
@@ -11596,7 +11591,7 @@
       </c>
       <c r="G310" s="24">
         <f>D310*H310</f>
-        <v/>
+        <v>10.455</v>
       </c>
       <c r="H310" s="25" t="n">
         <v>150</v>
@@ -11629,7 +11624,7 @@
       </c>
       <c r="G311" s="24">
         <f>D311*H311</f>
-        <v/>
+        <v>11.43</v>
       </c>
       <c r="H311" s="25" t="n">
         <v>150</v>
@@ -11662,7 +11657,7 @@
       </c>
       <c r="G312" s="24">
         <f>D312*H312</f>
-        <v/>
+        <v>20.22</v>
       </c>
       <c r="H312" s="25" t="n">
         <v>150</v>
@@ -11695,7 +11690,7 @@
       </c>
       <c r="G313" s="24">
         <f>D313*H313</f>
-        <v/>
+        <v>29.07</v>
       </c>
       <c r="H313" s="25" t="n">
         <v>150</v>
@@ -11728,7 +11723,7 @@
       </c>
       <c r="G314" s="24">
         <f>D314*H314</f>
-        <v/>
+        <v>30.42</v>
       </c>
       <c r="H314" s="25" t="n">
         <v>150</v>
@@ -11761,7 +11756,7 @@
       </c>
       <c r="G315" s="24">
         <f>D315*H315</f>
-        <v/>
+        <v>32.82</v>
       </c>
       <c r="H315" s="25" t="n">
         <v>150</v>
@@ -11794,7 +11789,7 @@
       </c>
       <c r="G316" s="24">
         <f>D316*H316</f>
-        <v/>
+        <v>34.635</v>
       </c>
       <c r="H316" s="25" t="n">
         <v>150</v>
@@ -11827,7 +11822,7 @@
       </c>
       <c r="G317" s="24">
         <f>D317*H317</f>
-        <v/>
+        <v>35.88</v>
       </c>
       <c r="H317" s="25" t="n">
         <v>150</v>
@@ -11860,7 +11855,7 @@
       </c>
       <c r="G318" s="24">
         <f>D318*H318</f>
-        <v/>
+        <v>39.0</v>
       </c>
       <c r="H318" s="25" t="n">
         <v>150</v>
@@ -11893,7 +11888,7 @@
       </c>
       <c r="G319" s="24">
         <f>D319*H319</f>
-        <v/>
+        <v>40.185</v>
       </c>
       <c r="H319" s="25" t="n">
         <v>150</v>
@@ -11926,7 +11921,7 @@
       </c>
       <c r="G320" s="24">
         <f>D320*H320</f>
-        <v/>
+        <v>41.144999999999996</v>
       </c>
       <c r="H320" s="25" t="n">
         <v>150</v>
@@ -11959,7 +11954,7 @@
       </c>
       <c r="G321" s="24">
         <f>D321*H321</f>
-        <v/>
+        <v>43.755</v>
       </c>
       <c r="H321" s="25" t="n">
         <v>150</v>
@@ -11992,7 +11987,7 @@
       </c>
       <c r="G322" s="24">
         <f>D322*H322</f>
-        <v/>
+        <v>44.82</v>
       </c>
       <c r="H322" s="25" t="n">
         <v>150</v>
@@ -12025,7 +12020,7 @@
       </c>
       <c r="G323" s="24">
         <f>D323*H323</f>
-        <v/>
+        <v>47.04</v>
       </c>
       <c r="H323" s="25" t="n">
         <v>150</v>
@@ -12058,7 +12053,7 @@
       </c>
       <c r="G324" s="24">
         <f>D324*H324</f>
-        <v/>
+        <v>51.075</v>
       </c>
       <c r="H324" s="25" t="n">
         <v>150</v>
@@ -12091,7 +12086,7 @@
       </c>
       <c r="G325" s="24">
         <f>D325*H325</f>
-        <v/>
+        <v>52.980000000000004</v>
       </c>
       <c r="H325" s="25" t="n">
         <v>150</v>
@@ -12124,7 +12119,7 @@
       </c>
       <c r="G326" s="24">
         <f>D326*H326</f>
-        <v/>
+        <v>57.269999999999996</v>
       </c>
       <c r="H326" s="25" t="n">
         <v>150</v>
@@ -12157,7 +12152,7 @@
       </c>
       <c r="G327" s="24">
         <f>D327*H327</f>
-        <v/>
+        <v>60.24</v>
       </c>
       <c r="H327" s="25" t="n">
         <v>150</v>
@@ -12190,7 +12185,7 @@
       </c>
       <c r="G328" s="24">
         <f>D328*H328</f>
-        <v/>
+        <v>65.22</v>
       </c>
       <c r="H328" s="25" t="n">
         <v>150</v>
@@ -12223,7 +12218,7 @@
       </c>
       <c r="G329" s="24">
         <f>D329*H329</f>
-        <v/>
+        <v>65.42999999999999</v>
       </c>
       <c r="H329" s="25" t="n">
         <v>150</v>
@@ -12256,7 +12251,7 @@
       </c>
       <c r="G330" s="24">
         <f>D330*H330</f>
-        <v/>
+        <v>65.955</v>
       </c>
       <c r="H330" s="25" t="n">
         <v>150</v>
@@ -12289,7 +12284,7 @@
       </c>
       <c r="G331" s="24">
         <f>D331*H331</f>
-        <v/>
+        <v>70.2</v>
       </c>
       <c r="H331" s="25" t="n">
         <v>150</v>
@@ -12322,7 +12317,7 @@
       </c>
       <c r="G332" s="24">
         <f>D332*H332</f>
-        <v/>
+        <v>70.25999999999999</v>
       </c>
       <c r="H332" s="25" t="n">
         <v>150</v>
@@ -12355,7 +12350,7 @@
       </c>
       <c r="G333" s="24">
         <f>D333*H333</f>
-        <v/>
+        <v>72.855</v>
       </c>
       <c r="H333" s="25" t="n">
         <v>150</v>
@@ -12388,7 +12383,7 @@
       </c>
       <c r="G334" s="24">
         <f>D334*H334</f>
-        <v/>
+        <v>76.62</v>
       </c>
       <c r="H334" s="25" t="n">
         <v>150</v>
@@ -12421,7 +12416,7 @@
       </c>
       <c r="G335" s="24">
         <f>D335*H335</f>
-        <v/>
+        <v>77.745</v>
       </c>
       <c r="H335" s="25" t="n">
         <v>150</v>
@@ -12454,7 +12449,7 @@
       </c>
       <c r="G336" s="24">
         <f>D336*H336</f>
-        <v/>
+        <v>81.15</v>
       </c>
       <c r="H336" s="25" t="n">
         <v>150</v>
@@ -12487,7 +12482,7 @@
       </c>
       <c r="G337" s="24">
         <f>D337*H337</f>
-        <v/>
+        <v>90.75</v>
       </c>
       <c r="H337" s="25" t="n">
         <v>150</v>
@@ -12520,7 +12515,7 @@
       </c>
       <c r="G338" s="24">
         <f>D338*H338</f>
-        <v/>
+        <v>94.59</v>
       </c>
       <c r="H338" s="25" t="n">
         <v>150</v>
@@ -12553,7 +12548,7 @@
       </c>
       <c r="G339" s="24">
         <f>D339*H339</f>
-        <v/>
+        <v>107.79</v>
       </c>
       <c r="H339" s="25" t="n">
         <v>150</v>
@@ -12586,7 +12581,7 @@
       </c>
       <c r="G340" s="24">
         <f>D340*H340</f>
-        <v/>
+        <v>115.485</v>
       </c>
       <c r="H340" s="25" t="n">
         <v>150</v>
@@ -12619,7 +12614,7 @@
       </c>
       <c r="G341" s="24">
         <f>D341*H341</f>
-        <v/>
+        <v>119.22</v>
       </c>
       <c r="H341" s="25" t="n">
         <v>150</v>
@@ -12652,7 +12647,7 @@
       </c>
       <c r="G342" s="24">
         <f>D342*H342</f>
-        <v/>
+        <v>126.16499999999999</v>
       </c>
       <c r="H342" s="25" t="n">
         <v>150</v>
@@ -12685,7 +12680,7 @@
       </c>
       <c r="G343" s="24">
         <f>D343*H343</f>
-        <v/>
+        <v>128.265</v>
       </c>
       <c r="H343" s="25" t="n">
         <v>150</v>
@@ -12718,7 +12713,7 @@
       </c>
       <c r="G344" s="24">
         <f>D344*H344</f>
-        <v/>
+        <v>134.76</v>
       </c>
       <c r="H344" s="25" t="n">
         <v>150</v>
@@ -12751,7 +12746,7 @@
       </c>
       <c r="G345" s="24">
         <f>D345*H345</f>
-        <v/>
+        <v>152.745</v>
       </c>
       <c r="H345" s="25" t="n">
         <v>150</v>
@@ -12784,7 +12779,7 @@
       </c>
       <c r="G346" s="24">
         <f>D346*H346</f>
-        <v/>
+        <v>156.675</v>
       </c>
       <c r="H346" s="25" t="n">
         <v>150</v>
@@ -12817,7 +12812,7 @@
       </c>
       <c r="G347" s="24">
         <f>D347*H347</f>
-        <v/>
+        <v>162.73499999999999</v>
       </c>
       <c r="H347" s="25" t="n">
         <v>150</v>
@@ -12850,7 +12845,7 @@
       </c>
       <c r="G348" s="24">
         <f>D348*H348</f>
-        <v/>
+        <v>167.88</v>
       </c>
       <c r="H348" s="25" t="n">
         <v>150</v>
@@ -12883,7 +12878,7 @@
       </c>
       <c r="G349" s="24">
         <f>D349*H349</f>
-        <v/>
+        <v>181.095</v>
       </c>
       <c r="H349" s="25" t="n">
         <v>150</v>
@@ -12916,7 +12911,7 @@
       </c>
       <c r="G350" s="24">
         <f>D350*H350</f>
-        <v/>
+        <v>184.26</v>
       </c>
       <c r="H350" s="25" t="n">
         <v>150</v>
@@ -12949,7 +12944,7 @@
       </c>
       <c r="G351" s="24">
         <f>D351*H351</f>
-        <v/>
+        <v>186.57</v>
       </c>
       <c r="H351" s="25" t="n">
         <v>150</v>
@@ -12982,7 +12977,7 @@
       </c>
       <c r="G352" s="24">
         <f>D352*H352</f>
-        <v/>
+        <v>192.99</v>
       </c>
       <c r="H352" s="25" t="n">
         <v>150</v>
@@ -13015,7 +13010,7 @@
       </c>
       <c r="G353" s="24">
         <f>D353*H353</f>
-        <v/>
+        <v>193.035</v>
       </c>
       <c r="H353" s="25" t="n">
         <v>150</v>
@@ -13048,7 +13043,7 @@
       </c>
       <c r="G354" s="24">
         <f>D354*H354</f>
-        <v/>
+        <v>205.59</v>
       </c>
       <c r="H354" s="25" t="n">
         <v>150</v>
@@ -13081,7 +13076,7 @@
       </c>
       <c r="G355" s="24">
         <f>D355*H355</f>
-        <v/>
+        <v>258.765</v>
       </c>
       <c r="H355" s="25" t="n">
         <v>150</v>
@@ -13114,7 +13109,7 @@
       </c>
       <c r="G356" s="24">
         <f>D356*H356</f>
-        <v/>
+        <v>280.74</v>
       </c>
       <c r="H356" s="25" t="n">
         <v>150</v>
@@ -13147,7 +13142,7 @@
       </c>
       <c r="G357" s="24">
         <f>D357*H357</f>
-        <v/>
+        <v>358.44</v>
       </c>
       <c r="H357" s="25" t="n">
         <v>150</v>
@@ -13180,7 +13175,7 @@
       </c>
       <c r="G358" s="24">
         <f>D358*H358</f>
-        <v/>
+        <v>395.205</v>
       </c>
       <c r="H358" s="25" t="n">
         <v>150</v>
@@ -13213,7 +13208,7 @@
       </c>
       <c r="G359" s="24">
         <f>D359*H359</f>
-        <v/>
+        <v>540.915</v>
       </c>
       <c r="H359" s="25" t="n">
         <v>150</v>
@@ -13246,7 +13241,7 @@
       </c>
       <c r="G360" s="24">
         <f>D360*H360</f>
-        <v/>
+        <v>573.165</v>
       </c>
       <c r="H360" s="25" t="n">
         <v>150</v>
@@ -13279,7 +13274,7 @@
       </c>
       <c r="G361" s="24">
         <f>D361*H361</f>
-        <v/>
+        <v>2.58</v>
       </c>
       <c r="H361" s="25" t="n">
         <v>150</v>
@@ -13312,7 +13307,7 @@
       </c>
       <c r="G362" s="24">
         <f>D362*H362</f>
-        <v/>
+        <v>11.1</v>
       </c>
       <c r="H362" s="25" t="n">
         <v>150</v>
@@ -13345,7 +13340,7 @@
       </c>
       <c r="G363" s="24">
         <f>D363*H363</f>
-        <v/>
+        <v>14.879999999999999</v>
       </c>
       <c r="H363" s="25" t="n">
         <v>150</v>
@@ -13378,7 +13373,7 @@
       </c>
       <c r="G364" s="24">
         <f>D364*H364</f>
-        <v/>
+        <v>24.255000000000003</v>
       </c>
       <c r="H364" s="25" t="n">
         <v>150</v>
@@ -13411,7 +13406,7 @@
       </c>
       <c r="G365" s="24">
         <f>D365*H365</f>
-        <v/>
+        <v>28.245</v>
       </c>
       <c r="H365" s="25" t="n">
         <v>150</v>
@@ -13444,7 +13439,7 @@
       </c>
       <c r="G366" s="24">
         <f>D366*H366</f>
-        <v/>
+        <v>32.43</v>
       </c>
       <c r="H366" s="25" t="n">
         <v>150</v>
@@ -13477,7 +13472,7 @@
       </c>
       <c r="G367" s="24">
         <f>D367*H367</f>
-        <v/>
+        <v>45.255</v>
       </c>
       <c r="H367" s="25" t="n">
         <v>150</v>
@@ -13510,7 +13505,7 @@
       </c>
       <c r="G368" s="24">
         <f>D368*H368</f>
-        <v/>
+        <v>50.7</v>
       </c>
       <c r="H368" s="25" t="n">
         <v>150</v>
@@ -13543,7 +13538,7 @@
       </c>
       <c r="G369" s="24">
         <f>D369*H369</f>
-        <v/>
+        <v>54.225</v>
       </c>
       <c r="H369" s="25" t="n">
         <v>150</v>
@@ -13576,7 +13571,7 @@
       </c>
       <c r="G370" s="24">
         <f>D370*H370</f>
-        <v/>
+        <v>60.24</v>
       </c>
       <c r="H370" s="25" t="n">
         <v>150</v>
@@ -13609,7 +13604,7 @@
       </c>
       <c r="G371" s="24">
         <f>D371*H371</f>
-        <v/>
+        <v>63.96</v>
       </c>
       <c r="H371" s="25" t="n">
         <v>150</v>
@@ -13642,7 +13637,7 @@
       </c>
       <c r="G372" s="24">
         <f>D372*H372</f>
-        <v/>
+        <v>69.9</v>
       </c>
       <c r="H372" s="25" t="n">
         <v>150</v>
@@ -13675,7 +13670,7 @@
       </c>
       <c r="G373" s="24">
         <f>D373*H373</f>
-        <v/>
+        <v>70.35</v>
       </c>
       <c r="H373" s="25" t="n">
         <v>150</v>
@@ -13708,7 +13703,7 @@
       </c>
       <c r="G374" s="24">
         <f>D374*H374</f>
-        <v/>
+        <v>71.02499999999999</v>
       </c>
       <c r="H374" s="25" t="n">
         <v>150</v>
@@ -13741,7 +13736,7 @@
       </c>
       <c r="G375" s="24">
         <f>D375*H375</f>
-        <v/>
+        <v>72.94500000000001</v>
       </c>
       <c r="H375" s="25" t="n">
         <v>150</v>
@@ -13774,7 +13769,7 @@
       </c>
       <c r="G376" s="24">
         <f>D376*H376</f>
-        <v/>
+        <v>75.855</v>
       </c>
       <c r="H376" s="25" t="n">
         <v>150</v>
@@ -13807,7 +13802,7 @@
       </c>
       <c r="G377" s="24">
         <f>D377*H377</f>
-        <v/>
+        <v>81.795</v>
       </c>
       <c r="H377" s="25" t="n">
         <v>150</v>
@@ -13840,7 +13835,7 @@
       </c>
       <c r="G378" s="24">
         <f>D378*H378</f>
-        <v/>
+        <v>83.03999999999999</v>
       </c>
       <c r="H378" s="25" t="n">
         <v>150</v>
@@ -13873,7 +13868,7 @@
       </c>
       <c r="G379" s="24">
         <f>D379*H379</f>
-        <v/>
+        <v>99.55499999999999</v>
       </c>
       <c r="H379" s="25" t="n">
         <v>150</v>
@@ -13906,7 +13901,7 @@
       </c>
       <c r="G380" s="24">
         <f>D380*H380</f>
-        <v/>
+        <v>102.30000000000001</v>
       </c>
       <c r="H380" s="25" t="n">
         <v>150</v>
@@ -13939,7 +13934,7 @@
       </c>
       <c r="G381" s="24">
         <f>D381*H381</f>
-        <v/>
+        <v>109.02</v>
       </c>
       <c r="H381" s="25" t="n">
         <v>150</v>
@@ -13972,7 +13967,7 @@
       </c>
       <c r="G382" s="24">
         <f>D382*H382</f>
-        <v/>
+        <v>127.22999999999999</v>
       </c>
       <c r="H382" s="25" t="n">
         <v>150</v>
@@ -14005,7 +14000,7 @@
       </c>
       <c r="G383" s="24">
         <f>D383*H383</f>
-        <v/>
+        <v>190.185</v>
       </c>
       <c r="H383" s="25" t="n">
         <v>150</v>
@@ -14038,7 +14033,7 @@
       </c>
       <c r="G384" s="24">
         <f>D384*H384</f>
-        <v/>
+        <v>218.26500000000001</v>
       </c>
       <c r="H384" s="25" t="n">
         <v>150</v>
@@ -14071,7 +14066,7 @@
       </c>
       <c r="G385" s="24">
         <f>D385*H385</f>
-        <v/>
+        <v>255.03</v>
       </c>
       <c r="H385" s="25" t="n">
         <v>150</v>
@@ -14104,7 +14099,7 @@
       </c>
       <c r="G386" s="24">
         <f>D386*H386</f>
-        <v/>
+        <v>390.375</v>
       </c>
       <c r="H386" s="25" t="n">
         <v>150</v>
@@ -14137,7 +14132,7 @@
       </c>
       <c r="G387" s="24">
         <f>D387*H387</f>
-        <v/>
+        <v>41.309999999999995</v>
       </c>
       <c r="H387" s="25" t="n">
         <v>150</v>
@@ -14170,7 +14165,7 @@
       </c>
       <c r="G388" s="24">
         <f>D388*H388</f>
-        <v/>
+        <v>45.135</v>
       </c>
       <c r="H388" s="25" t="n">
         <v>150</v>
@@ -14203,7 +14198,7 @@
       </c>
       <c r="G389" s="24">
         <f>D389*H389</f>
-        <v/>
+        <v>46.695</v>
       </c>
       <c r="H389" s="25" t="n">
         <v>150</v>
@@ -14236,7 +14231,7 @@
       </c>
       <c r="G390" s="24">
         <f>D390*H390</f>
-        <v/>
+        <v>66.03</v>
       </c>
       <c r="H390" s="25" t="n">
         <v>150</v>
@@ -14269,7 +14264,7 @@
       </c>
       <c r="G391" s="24">
         <f>D391*H391</f>
-        <v/>
+        <v>76.485</v>
       </c>
       <c r="H391" s="25" t="n">
         <v>150</v>
@@ -14302,7 +14297,7 @@
       </c>
       <c r="G392" s="24">
         <f>D392*H392</f>
-        <v/>
+        <v>139.035</v>
       </c>
       <c r="H392" s="25" t="n">
         <v>150</v>
@@ -14335,7 +14330,7 @@
       </c>
       <c r="G393" s="24">
         <f>D393*H393</f>
-        <v/>
+        <v>144.29999999999998</v>
       </c>
       <c r="H393" s="25" t="n">
         <v>150</v>
@@ -14368,7 +14363,7 @@
       </c>
       <c r="G394" s="24">
         <f>D394*H394</f>
-        <v/>
+        <v>149.085</v>
       </c>
       <c r="H394" s="25" t="n">
         <v>150</v>
@@ -14401,7 +14396,7 @@
       </c>
       <c r="G395" s="24">
         <f>D395*H395</f>
-        <v/>
+        <v>2.3</v>
       </c>
       <c r="H395" s="25" t="n">
         <v>200</v>
@@ -14434,7 +14429,7 @@
       </c>
       <c r="G396" s="24">
         <f>D396*H396</f>
-        <v/>
+        <v>3.2</v>
       </c>
       <c r="H396" s="25" t="n">
         <v>200</v>
@@ -14467,7 +14462,7 @@
       </c>
       <c r="G397" s="24">
         <f>D397*H397</f>
-        <v/>
+        <v>4.96</v>
       </c>
       <c r="H397" s="25" t="n">
         <v>200</v>
@@ -14500,7 +14495,7 @@
       </c>
       <c r="G398" s="24">
         <f>D398*H398</f>
-        <v/>
+        <v>7.88</v>
       </c>
       <c r="H398" s="25" t="n">
         <v>200</v>
@@ -14533,7 +14528,7 @@
       </c>
       <c r="G399" s="24">
         <f>D399*H399</f>
-        <v/>
+        <v>17.16</v>
       </c>
       <c r="H399" s="25" t="n">
         <v>200</v>
@@ -14566,7 +14561,7 @@
       </c>
       <c r="G400" s="24">
         <f>D400*H400</f>
-        <v/>
+        <v>19.72</v>
       </c>
       <c r="H400" s="25" t="n">
         <v>200</v>
@@ -14599,7 +14594,7 @@
       </c>
       <c r="G401" s="24">
         <f>D401*H401</f>
-        <v/>
+        <v>22.18</v>
       </c>
       <c r="H401" s="25" t="n">
         <v>200</v>
@@ -14632,7 +14627,7 @@
       </c>
       <c r="G402" s="24">
         <f>D402*H402</f>
-        <v/>
+        <v>25.019999999999996</v>
       </c>
       <c r="H402" s="25" t="n">
         <v>200</v>
@@ -14665,7 +14660,7 @@
       </c>
       <c r="G403" s="24">
         <f>D403*H403</f>
-        <v/>
+        <v>27.939999999999998</v>
       </c>
       <c r="H403" s="25" t="n">
         <v>200</v>
@@ -14698,7 +14693,7 @@
       </c>
       <c r="G404" s="24">
         <f>D404*H404</f>
-        <v/>
+        <v>29.160000000000004</v>
       </c>
       <c r="H404" s="25" t="n">
         <v>200</v>
@@ -14731,7 +14726,7 @@
       </c>
       <c r="G405" s="24">
         <f>D405*H405</f>
-        <v/>
+        <v>32.98</v>
       </c>
       <c r="H405" s="25" t="n">
         <v>200</v>
@@ -14764,7 +14759,7 @@
       </c>
       <c r="G406" s="24">
         <f>D406*H406</f>
-        <v/>
+        <v>33.64</v>
       </c>
       <c r="H406" s="25" t="n">
         <v>200</v>
@@ -14797,7 +14792,7 @@
       </c>
       <c r="G407" s="24">
         <f>D407*H407</f>
-        <v/>
+        <v>36.28</v>
       </c>
       <c r="H407" s="25" t="n">
         <v>200</v>
@@ -14830,7 +14825,7 @@
       </c>
       <c r="G408" s="24">
         <f>D408*H408</f>
-        <v/>
+        <v>38.0</v>
       </c>
       <c r="H408" s="25" t="n">
         <v>200</v>
@@ -14863,7 +14858,7 @@
       </c>
       <c r="G409" s="24">
         <f>D409*H409</f>
-        <v/>
+        <v>38.12</v>
       </c>
       <c r="H409" s="25" t="n">
         <v>200</v>
@@ -14896,7 +14891,7 @@
       </c>
       <c r="G410" s="24">
         <f>D410*H410</f>
-        <v/>
+        <v>41.980000000000004</v>
       </c>
       <c r="H410" s="25" t="n">
         <v>200</v>
@@ -14929,7 +14924,7 @@
       </c>
       <c r="G411" s="24">
         <f>D411*H411</f>
-        <v/>
+        <v>43.66</v>
       </c>
       <c r="H411" s="25" t="n">
         <v>200</v>
@@ -14962,7 +14957,7 @@
       </c>
       <c r="G412" s="24">
         <f>D412*H412</f>
-        <v/>
+        <v>47.339999999999996</v>
       </c>
       <c r="H412" s="25" t="n">
         <v>200</v>
@@ -14995,7 +14990,7 @@
       </c>
       <c r="G413" s="24">
         <f>D413*H413</f>
-        <v/>
+        <v>48.36</v>
       </c>
       <c r="H413" s="25" t="n">
         <v>200</v>
@@ -15028,7 +15023,7 @@
       </c>
       <c r="G414" s="24">
         <f>D414*H414</f>
-        <v/>
+        <v>48.74</v>
       </c>
       <c r="H414" s="25" t="n">
         <v>200</v>
@@ -15061,7 +15056,7 @@
       </c>
       <c r="G415" s="24">
         <f>D415*H415</f>
-        <v/>
+        <v>49.559999999999995</v>
       </c>
       <c r="H415" s="25" t="n">
         <v>200</v>
@@ -15094,7 +15089,7 @@
       </c>
       <c r="G416" s="24">
         <f>D416*H416</f>
-        <v/>
+        <v>54.26</v>
       </c>
       <c r="H416" s="25" t="n">
         <v>200</v>
@@ -15127,7 +15122,7 @@
       </c>
       <c r="G417" s="24">
         <f>D417*H417</f>
-        <v/>
+        <v>55.58</v>
       </c>
       <c r="H417" s="25" t="n">
         <v>200</v>
@@ -15160,7 +15155,7 @@
       </c>
       <c r="G418" s="24">
         <f>D418*H418</f>
-        <v/>
+        <v>59.019999999999996</v>
       </c>
       <c r="H418" s="25" t="n">
         <v>200</v>
@@ -15193,7 +15188,7 @@
       </c>
       <c r="G419" s="24">
         <f>D419*H419</f>
-        <v/>
+        <v>60.36</v>
       </c>
       <c r="H419" s="25" t="n">
         <v>200</v>
@@ -15226,7 +15221,7 @@
       </c>
       <c r="G420" s="24">
         <f>D420*H420</f>
-        <v/>
+        <v>63.5</v>
       </c>
       <c r="H420" s="25" t="n">
         <v>200</v>
@@ -15259,7 +15254,7 @@
       </c>
       <c r="G421" s="24">
         <f>D421*H421</f>
-        <v/>
+        <v>63.6</v>
       </c>
       <c r="H421" s="25" t="n">
         <v>200</v>
@@ -15292,7 +15287,7 @@
       </c>
       <c r="G422" s="24">
         <f>D422*H422</f>
-        <v/>
+        <v>68.5</v>
       </c>
       <c r="H422" s="25" t="n">
         <v>200</v>
@@ -15325,7 +15320,7 @@
       </c>
       <c r="G423" s="24">
         <f>D423*H423</f>
-        <v/>
+        <v>68.92</v>
       </c>
       <c r="H423" s="25" t="n">
         <v>200</v>
@@ -15358,7 +15353,7 @@
       </c>
       <c r="G424" s="24">
         <f>D424*H424</f>
-        <v/>
+        <v>70.52000000000001</v>
       </c>
       <c r="H424" s="25" t="n">
         <v>200</v>
@@ -15391,7 +15386,7 @@
       </c>
       <c r="G425" s="24">
         <f>D425*H425</f>
-        <v/>
+        <v>74.68</v>
       </c>
       <c r="H425" s="25" t="n">
         <v>200</v>
@@ -15424,7 +15419,7 @@
       </c>
       <c r="G426" s="24">
         <f>D426*H426</f>
-        <v/>
+        <v>80.25999999999999</v>
       </c>
       <c r="H426" s="25" t="n">
         <v>200</v>
@@ -15457,7 +15452,7 @@
       </c>
       <c r="G427" s="24">
         <f>D427*H427</f>
-        <v/>
+        <v>84.11999999999999</v>
       </c>
       <c r="H427" s="25" t="n">
         <v>200</v>
@@ -15490,7 +15485,7 @@
       </c>
       <c r="G428" s="24">
         <f>D428*H428</f>
-        <v/>
+        <v>85.86</v>
       </c>
       <c r="H428" s="25" t="n">
         <v>200</v>
@@ -15523,7 +15518,7 @@
       </c>
       <c r="G429" s="24">
         <f>D429*H429</f>
-        <v/>
+        <v>88.5</v>
       </c>
       <c r="H429" s="25" t="n">
         <v>200</v>
@@ -15556,7 +15551,7 @@
       </c>
       <c r="G430" s="24">
         <f>D430*H430</f>
-        <v/>
+        <v>89.0</v>
       </c>
       <c r="H430" s="25" t="n">
         <v>200</v>
@@ -15589,7 +15584,7 @@
       </c>
       <c r="G431" s="24">
         <f>D431*H431</f>
-        <v/>
+        <v>95.66</v>
       </c>
       <c r="H431" s="25" t="n">
         <v>200</v>
@@ -15622,7 +15617,7 @@
       </c>
       <c r="G432" s="24">
         <f>D432*H432</f>
-        <v/>
+        <v>98.16</v>
       </c>
       <c r="H432" s="25" t="n">
         <v>200</v>
@@ -15655,7 +15650,7 @@
       </c>
       <c r="G433" s="24">
         <f>D433*H433</f>
-        <v/>
+        <v>98.22</v>
       </c>
       <c r="H433" s="25" t="n">
         <v>200</v>
@@ -15688,7 +15683,7 @@
       </c>
       <c r="G434" s="24">
         <f>D434*H434</f>
-        <v/>
+        <v>102.67999999999999</v>
       </c>
       <c r="H434" s="25" t="n">
         <v>200</v>
@@ -15721,7 +15716,7 @@
       </c>
       <c r="G435" s="24">
         <f>D435*H435</f>
-        <v/>
+        <v>104.66</v>
       </c>
       <c r="H435" s="25" t="n">
         <v>200</v>
@@ -15754,7 +15749,7 @@
       </c>
       <c r="G436" s="24">
         <f>D436*H436</f>
-        <v/>
+        <v>118.17999999999999</v>
       </c>
       <c r="H436" s="25" t="n">
         <v>200</v>
@@ -15787,7 +15782,7 @@
       </c>
       <c r="G437" s="24">
         <f>D437*H437</f>
-        <v/>
+        <v>119.28</v>
       </c>
       <c r="H437" s="25" t="n">
         <v>200</v>
@@ -15820,7 +15815,7 @@
       </c>
       <c r="G438" s="24">
         <f>D438*H438</f>
-        <v/>
+        <v>119.88000000000001</v>
       </c>
       <c r="H438" s="25" t="n">
         <v>200</v>
@@ -15853,7 +15848,7 @@
       </c>
       <c r="G439" s="24">
         <f>D439*H439</f>
-        <v/>
+        <v>121.0</v>
       </c>
       <c r="H439" s="25" t="n">
         <v>200</v>
@@ -15886,7 +15881,7 @@
       </c>
       <c r="G440" s="24">
         <f>D440*H440</f>
-        <v/>
+        <v>126.38000000000001</v>
       </c>
       <c r="H440" s="25" t="n">
         <v>200</v>
@@ -15919,7 +15914,7 @@
       </c>
       <c r="G441" s="24">
         <f>D441*H441</f>
-        <v/>
+        <v>141.6</v>
       </c>
       <c r="H441" s="25" t="n">
         <v>200</v>
@@ -15952,7 +15947,7 @@
       </c>
       <c r="G442" s="24">
         <f>D442*H442</f>
-        <v/>
+        <v>141.64000000000001</v>
       </c>
       <c r="H442" s="25" t="n">
         <v>200</v>
@@ -15985,7 +15980,7 @@
       </c>
       <c r="G443" s="24">
         <f>D443*H443</f>
-        <v/>
+        <v>142.16</v>
       </c>
       <c r="H443" s="25" t="n">
         <v>200</v>
@@ -16018,7 +16013,7 @@
       </c>
       <c r="G444" s="24">
         <f>D444*H444</f>
-        <v/>
+        <v>142.74</v>
       </c>
       <c r="H444" s="25" t="n">
         <v>200</v>
@@ -16051,7 +16046,7 @@
       </c>
       <c r="G445" s="24">
         <f>D445*H445</f>
-        <v/>
+        <v>146.28</v>
       </c>
       <c r="H445" s="25" t="n">
         <v>200</v>
@@ -16084,7 +16079,7 @@
       </c>
       <c r="G446" s="24">
         <f>D446*H446</f>
-        <v/>
+        <v>150.58</v>
       </c>
       <c r="H446" s="25" t="n">
         <v>200</v>
@@ -16117,7 +16112,7 @@
       </c>
       <c r="G447" s="24">
         <f>D447*H447</f>
-        <v/>
+        <v>153.76000000000002</v>
       </c>
       <c r="H447" s="25" t="n">
         <v>200</v>
@@ -16150,7 +16145,7 @@
       </c>
       <c r="G448" s="24">
         <f>D448*H448</f>
-        <v/>
+        <v>162.7</v>
       </c>
       <c r="H448" s="25" t="n">
         <v>200</v>
@@ -16183,7 +16178,7 @@
       </c>
       <c r="G449" s="24">
         <f>D449*H449</f>
-        <v/>
+        <v>164.66</v>
       </c>
       <c r="H449" s="25" t="n">
         <v>200</v>
@@ -16216,7 +16211,7 @@
       </c>
       <c r="G450" s="24">
         <f>D450*H450</f>
-        <v/>
+        <v>166.44</v>
       </c>
       <c r="H450" s="25" t="n">
         <v>200</v>
@@ -16249,7 +16244,7 @@
       </c>
       <c r="G451" s="24">
         <f>D451*H451</f>
-        <v/>
+        <v>178.51999999999998</v>
       </c>
       <c r="H451" s="25" t="n">
         <v>200</v>
@@ -16282,7 +16277,7 @@
       </c>
       <c r="G452" s="24">
         <f>D452*H452</f>
-        <v/>
+        <v>193.16</v>
       </c>
       <c r="H452" s="25" t="n">
         <v>200</v>
@@ -16315,7 +16310,7 @@
       </c>
       <c r="G453" s="24">
         <f>D453*H453</f>
-        <v/>
+        <v>212.8</v>
       </c>
       <c r="H453" s="25" t="n">
         <v>200</v>
@@ -16348,7 +16343,7 @@
       </c>
       <c r="G454" s="24">
         <f>D454*H454</f>
-        <v/>
+        <v>215.83999999999997</v>
       </c>
       <c r="H454" s="25" t="n">
         <v>200</v>
@@ -16381,7 +16376,7 @@
       </c>
       <c r="G455" s="24">
         <f>D455*H455</f>
-        <v/>
+        <v>218.06</v>
       </c>
       <c r="H455" s="25" t="n">
         <v>200</v>
@@ -16414,7 +16409,7 @@
       </c>
       <c r="G456" s="24">
         <f>D456*H456</f>
-        <v/>
+        <v>222.56</v>
       </c>
       <c r="H456" s="25" t="n">
         <v>200</v>
@@ -16447,7 +16442,7 @@
       </c>
       <c r="G457" s="24">
         <f>D457*H457</f>
-        <v/>
+        <v>224.6</v>
       </c>
       <c r="H457" s="25" t="n">
         <v>200</v>
@@ -16480,7 +16475,7 @@
       </c>
       <c r="G458" s="24">
         <f>D458*H458</f>
-        <v/>
+        <v>231.86</v>
       </c>
       <c r="H458" s="25" t="n">
         <v>200</v>
@@ -16513,7 +16508,7 @@
       </c>
       <c r="G459" s="24">
         <f>D459*H459</f>
-        <v/>
+        <v>237.8</v>
       </c>
       <c r="H459" s="25" t="n">
         <v>200</v>
@@ -16546,7 +16541,7 @@
       </c>
       <c r="G460" s="24">
         <f>D460*H460</f>
-        <v/>
+        <v>249.98</v>
       </c>
       <c r="H460" s="25" t="n">
         <v>200</v>
@@ -16579,7 +16574,7 @@
       </c>
       <c r="G461" s="24">
         <f>D461*H461</f>
-        <v/>
+        <v>252.07999999999998</v>
       </c>
       <c r="H461" s="25" t="n">
         <v>200</v>
@@ -16612,7 +16607,7 @@
       </c>
       <c r="G462" s="24">
         <f>D462*H462</f>
-        <v/>
+        <v>261.52000000000004</v>
       </c>
       <c r="H462" s="25" t="n">
         <v>200</v>
@@ -16645,7 +16640,7 @@
       </c>
       <c r="G463" s="24">
         <f>D463*H463</f>
-        <v/>
+        <v>279.42</v>
       </c>
       <c r="H463" s="25" t="n">
         <v>200</v>
@@ -16678,7 +16673,7 @@
       </c>
       <c r="G464" s="24">
         <f>D464*H464</f>
-        <v/>
+        <v>328.7</v>
       </c>
       <c r="H464" s="25" t="n">
         <v>200</v>
@@ -16711,7 +16706,7 @@
       </c>
       <c r="G465" s="24">
         <f>D465*H465</f>
-        <v/>
+        <v>343.82</v>
       </c>
       <c r="H465" s="25" t="n">
         <v>200</v>
@@ -16744,7 +16739,7 @@
       </c>
       <c r="G466" s="24">
         <f>D466*H466</f>
-        <v/>
+        <v>372.2</v>
       </c>
       <c r="H466" s="25" t="n">
         <v>200</v>
@@ -16777,7 +16772,7 @@
       </c>
       <c r="G467" s="24">
         <f>D467*H467</f>
-        <v/>
+        <v>383.84000000000003</v>
       </c>
       <c r="H467" s="25" t="n">
         <v>200</v>
@@ -16810,7 +16805,7 @@
       </c>
       <c r="G468" s="24">
         <f>D468*H468</f>
-        <v/>
+        <v>387.56</v>
       </c>
       <c r="H468" s="25" t="n">
         <v>200</v>
@@ -16843,7 +16838,7 @@
       </c>
       <c r="G469" s="24">
         <f>D469*H469</f>
-        <v/>
+        <v>405.84</v>
       </c>
       <c r="H469" s="25" t="n">
         <v>200</v>
@@ -16876,7 +16871,7 @@
       </c>
       <c r="G470" s="24">
         <f>D470*H470</f>
-        <v/>
+        <v>420.02</v>
       </c>
       <c r="H470" s="25" t="n">
         <v>200</v>
@@ -16909,7 +16904,7 @@
       </c>
       <c r="G471" s="24">
         <f>D471*H471</f>
-        <v/>
+        <v>498.62</v>
       </c>
       <c r="H471" s="25" t="n">
         <v>200</v>
@@ -16942,7 +16937,7 @@
       </c>
       <c r="G472" s="24">
         <f>D472*H472</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="H472" s="25" t="n">
         <v>200</v>
@@ -16975,7 +16970,7 @@
       </c>
       <c r="G473" s="24">
         <f>D473*H473</f>
-        <v/>
+        <v>3.6799999999999997</v>
       </c>
       <c r="H473" s="25" t="n">
         <v>200</v>
@@ -17008,7 +17003,7 @@
       </c>
       <c r="G474" s="24">
         <f>D474*H474</f>
-        <v/>
+        <v>14.56</v>
       </c>
       <c r="H474" s="25" t="n">
         <v>200</v>
@@ -17041,7 +17036,7 @@
       </c>
       <c r="G475" s="24">
         <f>D475*H475</f>
-        <v/>
+        <v>22.720000000000002</v>
       </c>
       <c r="H475" s="25" t="n">
         <v>200</v>
@@ -17074,7 +17069,7 @@
       </c>
       <c r="G476" s="24">
         <f>D476*H476</f>
-        <v/>
+        <v>24.98</v>
       </c>
       <c r="H476" s="25" t="n">
         <v>200</v>
@@ -17107,7 +17102,7 @@
       </c>
       <c r="G477" s="24">
         <f>D477*H477</f>
-        <v/>
+        <v>36.559999999999995</v>
       </c>
       <c r="H477" s="25" t="n">
         <v>200</v>
@@ -17140,7 +17135,7 @@
       </c>
       <c r="G478" s="24">
         <f>D478*H478</f>
-        <v/>
+        <v>48.54</v>
       </c>
       <c r="H478" s="25" t="n">
         <v>200</v>
@@ -17173,7 +17168,7 @@
       </c>
       <c r="G479" s="24">
         <f>D479*H479</f>
-        <v/>
+        <v>59.62</v>
       </c>
       <c r="H479" s="25" t="n">
         <v>200</v>
@@ -17206,7 +17201,7 @@
       </c>
       <c r="G480" s="24">
         <f>D480*H480</f>
-        <v/>
+        <v>65.9</v>
       </c>
       <c r="H480" s="25" t="n">
         <v>200</v>
@@ -17239,7 +17234,7 @@
       </c>
       <c r="G481" s="24">
         <f>D481*H481</f>
-        <v/>
+        <v>72.44</v>
       </c>
       <c r="H481" s="25" t="n">
         <v>200</v>
@@ -17272,7 +17267,7 @@
       </c>
       <c r="G482" s="24">
         <f>D482*H482</f>
-        <v/>
+        <v>72.5</v>
       </c>
       <c r="H482" s="25" t="n">
         <v>200</v>
@@ -17305,7 +17300,7 @@
       </c>
       <c r="G483" s="24">
         <f>D483*H483</f>
-        <v/>
+        <v>74.36</v>
       </c>
       <c r="H483" s="25" t="n">
         <v>200</v>
@@ -17338,7 +17333,7 @@
       </c>
       <c r="G484" s="24">
         <f>D484*H484</f>
-        <v/>
+        <v>92.54</v>
       </c>
       <c r="H484" s="25" t="n">
         <v>200</v>
@@ -17371,7 +17366,7 @@
       </c>
       <c r="G485" s="24">
         <f>D485*H485</f>
-        <v/>
+        <v>95.78</v>
       </c>
       <c r="H485" s="25" t="n">
         <v>200</v>
@@ -17404,7 +17399,7 @@
       </c>
       <c r="G486" s="24">
         <f>D486*H486</f>
-        <v/>
+        <v>96.06</v>
       </c>
       <c r="H486" s="25" t="n">
         <v>200</v>
@@ -17437,7 +17432,7 @@
       </c>
       <c r="G487" s="24">
         <f>D487*H487</f>
-        <v/>
+        <v>107.38000000000001</v>
       </c>
       <c r="H487" s="25" t="n">
         <v>200</v>
@@ -17470,7 +17465,7 @@
       </c>
       <c r="G488" s="24">
         <f>D488*H488</f>
-        <v/>
+        <v>116.14</v>
       </c>
       <c r="H488" s="25" t="n">
         <v>200</v>
@@ -17503,7 +17498,7 @@
       </c>
       <c r="G489" s="24">
         <f>D489*H489</f>
-        <v/>
+        <v>118.68</v>
       </c>
       <c r="H489" s="25" t="n">
         <v>200</v>
@@ -17536,7 +17531,7 @@
       </c>
       <c r="G490" s="24">
         <f>D490*H490</f>
-        <v/>
+        <v>120.8</v>
       </c>
       <c r="H490" s="25" t="n">
         <v>200</v>
@@ -17569,7 +17564,7 @@
       </c>
       <c r="G491" s="24">
         <f>D491*H491</f>
-        <v/>
+        <v>129.07999999999998</v>
       </c>
       <c r="H491" s="25" t="n">
         <v>200</v>
@@ -17602,7 +17597,7 @@
       </c>
       <c r="G492" s="24">
         <f>D492*H492</f>
-        <v/>
+        <v>130.16</v>
       </c>
       <c r="H492" s="25" t="n">
         <v>200</v>
@@ -17635,7 +17630,7 @@
       </c>
       <c r="G493" s="24">
         <f>D493*H493</f>
-        <v/>
+        <v>135.12</v>
       </c>
       <c r="H493" s="25" t="n">
         <v>200</v>
@@ -17668,7 +17663,7 @@
       </c>
       <c r="G494" s="24">
         <f>D494*H494</f>
-        <v/>
+        <v>163.04000000000002</v>
       </c>
       <c r="H494" s="25" t="n">
         <v>200</v>
@@ -17701,7 +17696,7 @@
       </c>
       <c r="G495" s="24">
         <f>D495*H495</f>
-        <v/>
+        <v>195.64</v>
       </c>
       <c r="H495" s="25" t="n">
         <v>200</v>
@@ -17734,7 +17729,7 @@
       </c>
       <c r="G496" s="24">
         <f>D496*H496</f>
-        <v/>
+        <v>216.71999999999997</v>
       </c>
       <c r="H496" s="25" t="n">
         <v>200</v>
@@ -17767,7 +17762,7 @@
       </c>
       <c r="G497" s="24">
         <f>D497*H497</f>
-        <v/>
+        <v>219.1</v>
       </c>
       <c r="H497" s="25" t="n">
         <v>200</v>
@@ -17800,7 +17795,7 @@
       </c>
       <c r="G498" s="24">
         <f>D498*H498</f>
-        <v/>
+        <v>222.84</v>
       </c>
       <c r="H498" s="25" t="n">
         <v>200</v>
@@ -17833,7 +17828,7 @@
       </c>
       <c r="G499" s="24">
         <f>D499*H499</f>
-        <v/>
+        <v>225.57999999999998</v>
       </c>
       <c r="H499" s="25" t="n">
         <v>200</v>
@@ -17866,7 +17861,7 @@
       </c>
       <c r="G500" s="24">
         <f>D500*H500</f>
-        <v/>
+        <v>360.15999999999997</v>
       </c>
       <c r="H500" s="25" t="n">
         <v>200</v>
@@ -17899,7 +17894,7 @@
       </c>
       <c r="G501" s="24">
         <f>D501*H501</f>
-        <v/>
+        <v>568.8399999999999</v>
       </c>
       <c r="H501" s="25" t="n">
         <v>200</v>
@@ -17932,7 +17927,7 @@
       </c>
       <c r="G502" s="24">
         <f>D502*H502</f>
-        <v/>
+        <v>16.485</v>
       </c>
       <c r="H502" s="25" t="n">
         <v>150</v>
@@ -17965,7 +17960,7 @@
       </c>
       <c r="G503" s="24">
         <f>D503*H503</f>
-        <v/>
+        <v>17.07</v>
       </c>
       <c r="H503" s="25" t="n">
         <v>150</v>
@@ -17998,7 +17993,7 @@
       </c>
       <c r="G504" s="24">
         <f>D504*H504</f>
-        <v/>
+        <v>23.535</v>
       </c>
       <c r="H504" s="25" t="n">
         <v>150</v>
@@ -18031,7 +18026,7 @@
       </c>
       <c r="G505" s="24">
         <f>D505*H505</f>
-        <v/>
+        <v>24.435</v>
       </c>
       <c r="H505" s="25" t="n">
         <v>150</v>
@@ -18064,7 +18059,7 @@
       </c>
       <c r="G506" s="24">
         <f>D506*H506</f>
-        <v/>
+        <v>29.505000000000003</v>
       </c>
       <c r="H506" s="25" t="n">
         <v>150</v>
@@ -18097,7 +18092,7 @@
       </c>
       <c r="G507" s="24">
         <f>D507*H507</f>
-        <v/>
+        <v>67.065</v>
       </c>
       <c r="H507" s="25" t="n">
         <v>150</v>
@@ -18130,7 +18125,7 @@
       </c>
       <c r="G508" s="24">
         <f>D508*H508</f>
-        <v/>
+        <v>70.62</v>
       </c>
       <c r="H508" s="25" t="n">
         <v>150</v>
@@ -18163,7 +18158,7 @@
       </c>
       <c r="G509" s="24">
         <f>D509*H509</f>
-        <v/>
+        <v>76.965</v>
       </c>
       <c r="H509" s="25" t="n">
         <v>150</v>
@@ -18196,7 +18191,7 @@
       </c>
       <c r="G510" s="24">
         <f>D510*H510</f>
-        <v/>
+        <v>82.38000000000001</v>
       </c>
       <c r="H510" s="25" t="n">
         <v>150</v>
@@ -18225,7 +18220,6 @@
       <c r="F511" s="23" t="n"/>
       <c r="G511" s="24">
         <f>D511*H511</f>
-        <v/>
       </c>
       <c r="H511" s="25" t="n">
         <v>150</v>
@@ -18258,7 +18252,7 @@
       </c>
       <c r="G512" s="24">
         <f>D512*H512</f>
-        <v/>
+        <v>119.98500000000001</v>
       </c>
       <c r="H512" s="25" t="n">
         <v>150</v>
@@ -18291,7 +18285,7 @@
       </c>
       <c r="G513" s="24">
         <f>D513*H513</f>
-        <v/>
+        <v>167.92499999999998</v>
       </c>
       <c r="H513" s="25" t="n">
         <v>150</v>
@@ -18324,7 +18318,7 @@
       </c>
       <c r="G514" s="24">
         <f>D514*H514</f>
-        <v/>
+        <v>182.22000000000003</v>
       </c>
       <c r="H514" s="25" t="n">
         <v>150</v>
@@ -18357,7 +18351,7 @@
       </c>
       <c r="G515" s="24">
         <f>D515*H515</f>
-        <v/>
+        <v>226.32</v>
       </c>
       <c r="H515" s="25" t="n">
         <v>150</v>
@@ -18390,7 +18384,7 @@
       </c>
       <c r="G516" s="24">
         <f>D516*H516</f>
-        <v/>
+        <v>298.365</v>
       </c>
       <c r="H516" s="25" t="n">
         <v>150</v>
@@ -18423,7 +18417,7 @@
       </c>
       <c r="G517" s="24">
         <f>D517*H517</f>
-        <v/>
+        <v>436.60499999999996</v>
       </c>
       <c r="H517" s="25" t="n">
         <v>150</v>
@@ -18456,7 +18450,7 @@
       </c>
       <c r="G518" s="24">
         <f>D518*H518</f>
-        <v/>
+        <v>777.075</v>
       </c>
       <c r="H518" s="25" t="n">
         <v>150</v>
@@ -18489,7 +18483,7 @@
       </c>
       <c r="G519" s="24">
         <f>D519*H519</f>
-        <v/>
+        <v>2.16</v>
       </c>
       <c r="H519" s="25" t="n">
         <v>200</v>
@@ -18522,7 +18516,7 @@
       </c>
       <c r="G520" s="24">
         <f>D520*H520</f>
-        <v/>
+        <v>4.9399999999999995</v>
       </c>
       <c r="H520" s="25" t="n">
         <v>200</v>
@@ -18555,7 +18549,7 @@
       </c>
       <c r="G521" s="24">
         <f>D521*H521</f>
-        <v/>
+        <v>6.279999999999999</v>
       </c>
       <c r="H521" s="25" t="n">
         <v>200</v>
@@ -18588,7 +18582,7 @@
       </c>
       <c r="G522" s="24">
         <f>D522*H522</f>
-        <v/>
+        <v>6.9</v>
       </c>
       <c r="H522" s="25" t="n">
         <v>200</v>
@@ -18621,7 +18615,7 @@
       </c>
       <c r="G523" s="24">
         <f>D523*H523</f>
-        <v/>
+        <v>10.8</v>
       </c>
       <c r="H523" s="25" t="n">
         <v>200</v>
@@ -18654,7 +18648,7 @@
       </c>
       <c r="G524" s="24">
         <f>D524*H524</f>
-        <v/>
+        <v>13.459999999999999</v>
       </c>
       <c r="H524" s="25" t="n">
         <v>200</v>
@@ -18687,7 +18681,7 @@
       </c>
       <c r="G525" s="24">
         <f>D525*H525</f>
-        <v/>
+        <v>13.86</v>
       </c>
       <c r="H525" s="25" t="n">
         <v>200</v>
@@ -18720,7 +18714,7 @@
       </c>
       <c r="G526" s="24">
         <f>D526*H526</f>
-        <v/>
+        <v>14.34</v>
       </c>
       <c r="H526" s="25" t="n">
         <v>200</v>
@@ -18753,7 +18747,7 @@
       </c>
       <c r="G527" s="24">
         <f>D527*H527</f>
-        <v/>
+        <v>20.16</v>
       </c>
       <c r="H527" s="25" t="n">
         <v>200</v>
@@ -18786,7 +18780,7 @@
       </c>
       <c r="G528" s="24">
         <f>D528*H528</f>
-        <v/>
+        <v>22.900000000000002</v>
       </c>
       <c r="H528" s="25" t="n">
         <v>200</v>
@@ -18819,7 +18813,7 @@
       </c>
       <c r="G529" s="24">
         <f>D529*H529</f>
-        <v/>
+        <v>23.28</v>
       </c>
       <c r="H529" s="25" t="n">
         <v>200</v>
@@ -18852,7 +18846,7 @@
       </c>
       <c r="G530" s="24">
         <f>D530*H530</f>
-        <v/>
+        <v>41.120000000000005</v>
       </c>
       <c r="H530" s="25" t="n">
         <v>200</v>
@@ -18885,7 +18879,7 @@
       </c>
       <c r="G531" s="24">
         <f>D531*H531</f>
-        <v/>
+        <v>41.82</v>
       </c>
       <c r="H531" s="25" t="n">
         <v>200</v>
@@ -18918,7 +18912,7 @@
       </c>
       <c r="G532" s="24">
         <f>D532*H532</f>
-        <v/>
+        <v>52.1</v>
       </c>
       <c r="H532" s="25" t="n">
         <v>200</v>
@@ -18951,7 +18945,7 @@
       </c>
       <c r="G533" s="24">
         <f>D533*H533</f>
-        <v/>
+        <v>57.68</v>
       </c>
       <c r="H533" s="25" t="n">
         <v>200</v>
@@ -18984,7 +18978,7 @@
       </c>
       <c r="G534" s="24">
         <f>D534*H534</f>
-        <v/>
+        <v>69.96</v>
       </c>
       <c r="H534" s="25" t="n">
         <v>200</v>
@@ -19017,7 +19011,7 @@
       </c>
       <c r="G535" s="24">
         <f>D535*H535</f>
-        <v/>
+        <v>72.3</v>
       </c>
       <c r="H535" s="25" t="n">
         <v>200</v>
@@ -19050,7 +19044,7 @@
       </c>
       <c r="G536" s="24">
         <f>D536*H536</f>
-        <v/>
+        <v>74.62</v>
       </c>
       <c r="H536" s="25" t="n">
         <v>200</v>
@@ -19083,7 +19077,7 @@
       </c>
       <c r="G537" s="24">
         <f>D537*H537</f>
-        <v/>
+        <v>79.36</v>
       </c>
       <c r="H537" s="25" t="n">
         <v>200</v>
@@ -19116,7 +19110,7 @@
       </c>
       <c r="G538" s="24">
         <f>D538*H538</f>
-        <v/>
+        <v>106.84</v>
       </c>
       <c r="H538" s="25" t="n">
         <v>200</v>
@@ -19149,7 +19143,7 @@
       </c>
       <c r="G539" s="24">
         <f>D539*H539</f>
-        <v/>
+        <v>112.62</v>
       </c>
       <c r="H539" s="25" t="n">
         <v>200</v>
@@ -19182,7 +19176,7 @@
       </c>
       <c r="G540" s="24">
         <f>D540*H540</f>
-        <v/>
+        <v>113.28</v>
       </c>
       <c r="H540" s="25" t="n">
         <v>200</v>
@@ -19215,7 +19209,7 @@
       </c>
       <c r="G541" s="24">
         <f>D541*H541</f>
-        <v/>
+        <v>134.54</v>
       </c>
       <c r="H541" s="25" t="n">
         <v>200</v>
@@ -19248,7 +19242,7 @@
       </c>
       <c r="G542" s="24">
         <f>D542*H542</f>
-        <v/>
+        <v>141.74</v>
       </c>
       <c r="H542" s="25" t="n">
         <v>200</v>
@@ -19281,7 +19275,7 @@
       </c>
       <c r="G543" s="24">
         <f>D543*H543</f>
-        <v/>
+        <v>142.48000000000002</v>
       </c>
       <c r="H543" s="25" t="n">
         <v>200</v>
@@ -19314,7 +19308,7 @@
       </c>
       <c r="G544" s="24">
         <f>D544*H544</f>
-        <v/>
+        <v>150.85999999999999</v>
       </c>
       <c r="H544" s="25" t="n">
         <v>200</v>
@@ -19347,7 +19341,7 @@
       </c>
       <c r="G545" s="24">
         <f>D545*H545</f>
-        <v/>
+        <v>151.32000000000002</v>
       </c>
       <c r="H545" s="25" t="n">
         <v>200</v>
@@ -19380,7 +19374,7 @@
       </c>
       <c r="G546" s="24">
         <f>D546*H546</f>
-        <v/>
+        <v>165.38</v>
       </c>
       <c r="H546" s="25" t="n">
         <v>200</v>
@@ -19413,7 +19407,7 @@
       </c>
       <c r="G547" s="24">
         <f>D547*H547</f>
-        <v/>
+        <v>179.8</v>
       </c>
       <c r="H547" s="25" t="n">
         <v>200</v>
@@ -19446,7 +19440,7 @@
       </c>
       <c r="G548" s="24">
         <f>D548*H548</f>
-        <v/>
+        <v>181.6</v>
       </c>
       <c r="H548" s="25" t="n">
         <v>200</v>
@@ -19479,7 +19473,7 @@
       </c>
       <c r="G549" s="24">
         <f>D549*H549</f>
-        <v/>
+        <v>185.68</v>
       </c>
       <c r="H549" s="25" t="n">
         <v>200</v>
@@ -19512,7 +19506,7 @@
       </c>
       <c r="G550" s="24">
         <f>D550*H550</f>
-        <v/>
+        <v>191.44</v>
       </c>
       <c r="H550" s="25" t="n">
         <v>200</v>
@@ -19545,7 +19539,7 @@
       </c>
       <c r="G551" s="24">
         <f>D551*H551</f>
-        <v/>
+        <v>212.56</v>
       </c>
       <c r="H551" s="25" t="n">
         <v>200</v>
@@ -19578,7 +19572,7 @@
       </c>
       <c r="G552" s="24">
         <f>D552*H552</f>
-        <v/>
+        <v>213.68</v>
       </c>
       <c r="H552" s="25" t="n">
         <v>200</v>
@@ -19611,7 +19605,7 @@
       </c>
       <c r="G553" s="24">
         <f>D553*H553</f>
-        <v/>
+        <v>214.82000000000002</v>
       </c>
       <c r="H553" s="25" t="n">
         <v>200</v>
@@ -19644,7 +19638,7 @@
       </c>
       <c r="G554" s="24">
         <f>D554*H554</f>
-        <v/>
+        <v>220.18</v>
       </c>
       <c r="H554" s="25" t="n">
         <v>200</v>
@@ -19677,7 +19671,7 @@
       </c>
       <c r="G555" s="24">
         <f>D555*H555</f>
-        <v/>
+        <v>288.18</v>
       </c>
       <c r="H555" s="25" t="n">
         <v>200</v>
@@ -19710,7 +19704,7 @@
       </c>
       <c r="G556" s="24">
         <f>D556*H556</f>
-        <v/>
+        <v>298.53999999999996</v>
       </c>
       <c r="H556" s="25" t="n">
         <v>200</v>
@@ -19743,7 +19737,7 @@
       </c>
       <c r="G557" s="24">
         <f>D557*H557</f>
-        <v/>
+        <v>339.96</v>
       </c>
       <c r="H557" s="25" t="n">
         <v>200</v>
@@ -19776,7 +19770,7 @@
       </c>
       <c r="G558" s="24">
         <f>D558*H558</f>
-        <v/>
+        <v>342.26</v>
       </c>
       <c r="H558" s="25" t="n">
         <v>200</v>
@@ -19809,7 +19803,7 @@
       </c>
       <c r="G559" s="24">
         <f>D559*H559</f>
-        <v/>
+        <v>1160.9199999999998</v>
       </c>
       <c r="H559" s="25" t="n">
         <v>200</v>
@@ -19842,7 +19836,7 @@
       </c>
       <c r="G560" s="24">
         <f>D560*H560</f>
-        <v/>
+        <v>1573.32</v>
       </c>
       <c r="H560" s="25" t="n">
         <v>200</v>
@@ -19875,7 +19869,7 @@
       </c>
       <c r="G561" s="24">
         <f>D561*H561</f>
-        <v/>
+        <v>11.445</v>
       </c>
       <c r="H561" s="25" t="n">
         <v>150</v>
@@ -19908,7 +19902,7 @@
       </c>
       <c r="G562" s="24">
         <f>D562*H562</f>
-        <v/>
+        <v>11.85</v>
       </c>
       <c r="H562" s="25" t="n">
         <v>150</v>
@@ -19941,7 +19935,7 @@
       </c>
       <c r="G563" s="24">
         <f>D563*H563</f>
-        <v/>
+        <v>12.405</v>
       </c>
       <c r="H563" s="25" t="n">
         <v>150</v>
@@ -19974,7 +19968,7 @@
       </c>
       <c r="G564" s="24">
         <f>D564*H564</f>
-        <v/>
+        <v>14.37</v>
       </c>
       <c r="H564" s="25" t="n">
         <v>150</v>
@@ -20007,7 +20001,7 @@
       </c>
       <c r="G565" s="24">
         <f>D565*H565</f>
-        <v/>
+        <v>14.985000000000001</v>
       </c>
       <c r="H565" s="25" t="n">
         <v>150</v>
@@ -20040,7 +20034,7 @@
       </c>
       <c r="G566" s="24">
         <f>D566*H566</f>
-        <v/>
+        <v>17.235</v>
       </c>
       <c r="H566" s="25" t="n">
         <v>150</v>
@@ -20073,7 +20067,7 @@
       </c>
       <c r="G567" s="24">
         <f>D567*H567</f>
-        <v/>
+        <v>17.28</v>
       </c>
       <c r="H567" s="25" t="n">
         <v>150</v>
@@ -20106,7 +20100,7 @@
       </c>
       <c r="G568" s="24">
         <f>D568*H568</f>
-        <v/>
+        <v>21.165</v>
       </c>
       <c r="H568" s="25" t="n">
         <v>150</v>
@@ -20139,7 +20133,7 @@
       </c>
       <c r="G569" s="24">
         <f>D569*H569</f>
-        <v/>
+        <v>24.075</v>
       </c>
       <c r="H569" s="25" t="n">
         <v>150</v>
@@ -20172,7 +20166,7 @@
       </c>
       <c r="G570" s="24">
         <f>D570*H570</f>
-        <v/>
+        <v>27.044999999999998</v>
       </c>
       <c r="H570" s="25" t="n">
         <v>150</v>
@@ -20205,7 +20199,7 @@
       </c>
       <c r="G571" s="24">
         <f>D571*H571</f>
-        <v/>
+        <v>30.375000000000004</v>
       </c>
       <c r="H571" s="25" t="n">
         <v>150</v>
@@ -20238,7 +20232,7 @@
       </c>
       <c r="G572" s="24">
         <f>D572*H572</f>
-        <v/>
+        <v>32.985</v>
       </c>
       <c r="H572" s="25" t="n">
         <v>150</v>
@@ -20271,7 +20265,7 @@
       </c>
       <c r="G573" s="24">
         <f>D573*H573</f>
-        <v/>
+        <v>45.795</v>
       </c>
       <c r="H573" s="25" t="n">
         <v>150</v>
@@ -20304,7 +20298,7 @@
       </c>
       <c r="G574" s="24">
         <f>D574*H574</f>
-        <v/>
+        <v>46.275</v>
       </c>
       <c r="H574" s="25" t="n">
         <v>150</v>
@@ -20337,7 +20331,7 @@
       </c>
       <c r="G575" s="24">
         <f>D575*H575</f>
-        <v/>
+        <v>47.279999999999994</v>
       </c>
       <c r="H575" s="25" t="n">
         <v>150</v>
@@ -20370,7 +20364,7 @@
       </c>
       <c r="G576" s="24">
         <f>D576*H576</f>
-        <v/>
+        <v>48.945</v>
       </c>
       <c r="H576" s="25" t="n">
         <v>150</v>
@@ -20403,7 +20397,7 @@
       </c>
       <c r="G577" s="24">
         <f>D577*H577</f>
-        <v/>
+        <v>51.480000000000004</v>
       </c>
       <c r="H577" s="25" t="n">
         <v>150</v>
@@ -20436,7 +20430,7 @@
       </c>
       <c r="G578" s="24">
         <f>D578*H578</f>
-        <v/>
+        <v>60.885</v>
       </c>
       <c r="H578" s="25" t="n">
         <v>150</v>
@@ -20469,7 +20463,7 @@
       </c>
       <c r="G579" s="24">
         <f>D579*H579</f>
-        <v/>
+        <v>63.38999999999999</v>
       </c>
       <c r="H579" s="25" t="n">
         <v>150</v>
@@ -20502,7 +20496,7 @@
       </c>
       <c r="G580" s="24">
         <f>D580*H580</f>
-        <v/>
+        <v>64.32000000000001</v>
       </c>
       <c r="H580" s="25" t="n">
         <v>150</v>
@@ -20535,7 +20529,7 @@
       </c>
       <c r="G581" s="24">
         <f>D581*H581</f>
-        <v/>
+        <v>65.715</v>
       </c>
       <c r="H581" s="25" t="n">
         <v>150</v>
@@ -20568,7 +20562,7 @@
       </c>
       <c r="G582" s="24">
         <f>D582*H582</f>
-        <v/>
+        <v>84.51</v>
       </c>
       <c r="H582" s="25" t="n">
         <v>150</v>
@@ -20601,7 +20595,7 @@
       </c>
       <c r="G583" s="24">
         <f>D583*H583</f>
-        <v/>
+        <v>87.97500000000001</v>
       </c>
       <c r="H583" s="25" t="n">
         <v>150</v>
@@ -20634,7 +20628,7 @@
       </c>
       <c r="G584" s="24">
         <f>D584*H584</f>
-        <v/>
+        <v>88.545</v>
       </c>
       <c r="H584" s="25" t="n">
         <v>150</v>
@@ -20667,7 +20661,7 @@
       </c>
       <c r="G585" s="24">
         <f>D585*H585</f>
-        <v/>
+        <v>88.83</v>
       </c>
       <c r="H585" s="25" t="n">
         <v>150</v>
@@ -20700,7 +20694,7 @@
       </c>
       <c r="G586" s="24">
         <f>D586*H586</f>
-        <v/>
+        <v>95.235</v>
       </c>
       <c r="H586" s="25" t="n">
         <v>150</v>
@@ -20733,7 +20727,7 @@
       </c>
       <c r="G587" s="24">
         <f>D587*H587</f>
-        <v/>
+        <v>110.72999999999999</v>
       </c>
       <c r="H587" s="25" t="n">
         <v>150</v>
@@ -20766,7 +20760,7 @@
       </c>
       <c r="G588" s="24">
         <f>D588*H588</f>
-        <v/>
+        <v>117.36</v>
       </c>
       <c r="H588" s="25" t="n">
         <v>150</v>
@@ -20799,7 +20793,7 @@
       </c>
       <c r="G589" s="24">
         <f>D589*H589</f>
-        <v/>
+        <v>128.955</v>
       </c>
       <c r="H589" s="25" t="n">
         <v>150</v>
@@ -20832,7 +20826,7 @@
       </c>
       <c r="G590" s="24">
         <f>D590*H590</f>
-        <v/>
+        <v>139.185</v>
       </c>
       <c r="H590" s="25" t="n">
         <v>150</v>
@@ -20865,7 +20859,7 @@
       </c>
       <c r="G591" s="24">
         <f>D591*H591</f>
-        <v/>
+        <v>145.04999999999998</v>
       </c>
       <c r="H591" s="25" t="n">
         <v>150</v>
@@ -20898,7 +20892,7 @@
       </c>
       <c r="G592" s="24">
         <f>D592*H592</f>
-        <v/>
+        <v>187.17000000000002</v>
       </c>
       <c r="H592" s="25" t="n">
         <v>150</v>
@@ -20931,7 +20925,7 @@
       </c>
       <c r="G593" s="24">
         <f>D593*H593</f>
-        <v/>
+        <v>191.025</v>
       </c>
       <c r="H593" s="25" t="n">
         <v>150</v>
@@ -20964,7 +20958,7 @@
       </c>
       <c r="G594" s="24">
         <f>D594*H594</f>
-        <v/>
+        <v>211.725</v>
       </c>
       <c r="H594" s="25" t="n">
         <v>150</v>
@@ -20997,7 +20991,7 @@
       </c>
       <c r="G595" s="24">
         <f>D595*H595</f>
-        <v/>
+        <v>218.73</v>
       </c>
       <c r="H595" s="25" t="n">
         <v>150</v>
@@ -21030,7 +21024,7 @@
       </c>
       <c r="G596" s="24">
         <f>D596*H596</f>
-        <v/>
+        <v>254.205</v>
       </c>
       <c r="H596" s="25" t="n">
         <v>150</v>
@@ -21063,7 +21057,7 @@
       </c>
       <c r="G597" s="24">
         <f>D597*H597</f>
-        <v/>
+        <v>309.99</v>
       </c>
       <c r="H597" s="25" t="n">
         <v>150</v>
@@ -21096,7 +21090,7 @@
       </c>
       <c r="G598" s="24">
         <f>D598*H598</f>
-        <v/>
+        <v>315.92999999999995</v>
       </c>
       <c r="H598" s="25" t="n">
         <v>150</v>
@@ -21129,7 +21123,7 @@
       </c>
       <c r="G599" s="24">
         <f>D599*H599</f>
-        <v/>
+        <v>317.385</v>
       </c>
       <c r="H599" s="25" t="n">
         <v>150</v>
@@ -21162,7 +21156,7 @@
       </c>
       <c r="G600" s="24">
         <f>D600*H600</f>
-        <v/>
+        <v>347.865</v>
       </c>
       <c r="H600" s="25" t="n">
         <v>150</v>
@@ -21195,7 +21189,7 @@
       </c>
       <c r="G601" s="24">
         <f>D601*H601</f>
-        <v/>
+        <v>386.22</v>
       </c>
       <c r="H601" s="25" t="n">
         <v>150</v>
@@ -21228,7 +21222,7 @@
       </c>
       <c r="G602" s="24">
         <f>D602*H602</f>
-        <v/>
+        <v>391.38</v>
       </c>
       <c r="H602" s="25" t="n">
         <v>150</v>
@@ -21261,7 +21255,7 @@
       </c>
       <c r="G603" s="24">
         <f>D603*H603</f>
-        <v/>
+        <v>511.515</v>
       </c>
       <c r="H603" s="25" t="n">
         <v>150</v>
@@ -21294,7 +21288,7 @@
       </c>
       <c r="G604" s="24">
         <f>D604*H604</f>
-        <v/>
+        <v>658.74</v>
       </c>
       <c r="H604" s="25" t="n">
         <v>150</v>
@@ -21327,7 +21321,7 @@
       </c>
       <c r="G605" s="24">
         <f>D605*H605</f>
-        <v/>
+        <v>13.23</v>
       </c>
       <c r="H605" s="25" t="n">
         <v>150</v>
@@ -21360,7 +21354,7 @@
       </c>
       <c r="G606" s="24">
         <f>D606*H606</f>
-        <v/>
+        <v>14.594999999999999</v>
       </c>
       <c r="H606" s="25" t="n">
         <v>150</v>
@@ -21393,7 +21387,7 @@
       </c>
       <c r="G607" s="24">
         <f>D607*H607</f>
-        <v/>
+        <v>18.855</v>
       </c>
       <c r="H607" s="25" t="n">
         <v>150</v>
@@ -21426,7 +21420,7 @@
       </c>
       <c r="G608" s="24">
         <f>D608*H608</f>
-        <v/>
+        <v>38.985</v>
       </c>
       <c r="H608" s="25" t="n">
         <v>150</v>
@@ -21459,7 +21453,7 @@
       </c>
       <c r="G609" s="24">
         <f>D609*H609</f>
-        <v/>
+        <v>55.845000000000006</v>
       </c>
       <c r="H609" s="25" t="n">
         <v>150</v>
@@ -21492,7 +21486,7 @@
       </c>
       <c r="G610" s="24">
         <f>D610*H610</f>
-        <v/>
+        <v>60.165</v>
       </c>
       <c r="H610" s="25" t="n">
         <v>150</v>
@@ -21525,7 +21519,7 @@
       </c>
       <c r="G611" s="24">
         <f>D611*H611</f>
-        <v/>
+        <v>60.465</v>
       </c>
       <c r="H611" s="25" t="n">
         <v>150</v>
@@ -21558,7 +21552,7 @@
       </c>
       <c r="G612" s="24">
         <f>D612*H612</f>
-        <v/>
+        <v>68.07</v>
       </c>
       <c r="H612" s="25" t="n">
         <v>150</v>
@@ -21591,7 +21585,7 @@
       </c>
       <c r="G613" s="24">
         <f>D613*H613</f>
-        <v/>
+        <v>70.83</v>
       </c>
       <c r="H613" s="25" t="n">
         <v>150</v>
@@ -21624,7 +21618,7 @@
       </c>
       <c r="G614" s="24">
         <f>D614*H614</f>
-        <v/>
+        <v>72.0</v>
       </c>
       <c r="H614" s="25" t="n">
         <v>150</v>
@@ -21657,7 +21651,7 @@
       </c>
       <c r="G615" s="24">
         <f>D615*H615</f>
-        <v/>
+        <v>77.28</v>
       </c>
       <c r="H615" s="25" t="n">
         <v>150</v>
@@ -21690,7 +21684,7 @@
       </c>
       <c r="G616" s="24">
         <f>D616*H616</f>
-        <v/>
+        <v>82.23</v>
       </c>
       <c r="H616" s="25" t="n">
         <v>150</v>
@@ -21723,7 +21717,7 @@
       </c>
       <c r="G617" s="24">
         <f>D617*H617</f>
-        <v/>
+        <v>88.275</v>
       </c>
       <c r="H617" s="25" t="n">
         <v>150</v>
@@ -21756,7 +21750,7 @@
       </c>
       <c r="G618" s="24">
         <f>D618*H618</f>
-        <v/>
+        <v>88.5</v>
       </c>
       <c r="H618" s="25" t="n">
         <v>150</v>
@@ -21789,7 +21783,7 @@
       </c>
       <c r="G619" s="24">
         <f>D619*H619</f>
-        <v/>
+        <v>96.83999999999999</v>
       </c>
       <c r="H619" s="25" t="n">
         <v>150</v>
@@ -21822,7 +21816,7 @@
       </c>
       <c r="G620" s="24">
         <f>D620*H620</f>
-        <v/>
+        <v>102.03</v>
       </c>
       <c r="H620" s="25" t="n">
         <v>150</v>
@@ -21855,7 +21849,7 @@
       </c>
       <c r="G621" s="24">
         <f>D621*H621</f>
-        <v/>
+        <v>109.515</v>
       </c>
       <c r="H621" s="25" t="n">
         <v>150</v>
@@ -21888,7 +21882,7 @@
       </c>
       <c r="G622" s="24">
         <f>D622*H622</f>
-        <v/>
+        <v>110.79</v>
       </c>
       <c r="H622" s="25" t="n">
         <v>150</v>
@@ -21921,7 +21915,7 @@
       </c>
       <c r="G623" s="24">
         <f>D623*H623</f>
-        <v/>
+        <v>125.22</v>
       </c>
       <c r="H623" s="25" t="n">
         <v>150</v>
@@ -21954,7 +21948,7 @@
       </c>
       <c r="G624" s="24">
         <f>D624*H624</f>
-        <v/>
+        <v>131.55</v>
       </c>
       <c r="H624" s="25" t="n">
         <v>150</v>
@@ -21987,7 +21981,7 @@
       </c>
       <c r="G625" s="24">
         <f>D625*H625</f>
-        <v/>
+        <v>134.60999999999999</v>
       </c>
       <c r="H625" s="25" t="n">
         <v>150</v>
@@ -22020,7 +22014,7 @@
       </c>
       <c r="G626" s="24">
         <f>D626*H626</f>
-        <v/>
+        <v>244.29000000000002</v>
       </c>
       <c r="H626" s="25" t="n">
         <v>150</v>
@@ -22053,7 +22047,7 @@
       </c>
       <c r="G627" s="24">
         <f>D627*H627</f>
-        <v/>
+        <v>383.46</v>
       </c>
       <c r="H627" s="25" t="n">
         <v>150</v>
@@ -22086,7 +22080,7 @@
       </c>
       <c r="G628" s="24">
         <f>D628*H628</f>
-        <v/>
+        <v>480.195</v>
       </c>
       <c r="H628" s="25" t="n">
         <v>150</v>
@@ -22119,7 +22113,7 @@
       </c>
       <c r="G629" s="24">
         <f>D629*H629</f>
-        <v/>
+        <v>482.55</v>
       </c>
       <c r="H629" s="25" t="n">
         <v>150</v>
@@ -22152,7 +22146,7 @@
       </c>
       <c r="G630" s="24">
         <f>D630*H630</f>
-        <v/>
+        <v>787.335</v>
       </c>
       <c r="H630" s="25" t="n">
         <v>150</v>
@@ -22185,7 +22179,7 @@
       </c>
       <c r="G631" s="24">
         <f>D631*H631</f>
-        <v/>
+        <v>25.500000000000004</v>
       </c>
       <c r="H631" s="25" t="n">
         <v>150</v>
@@ -22218,7 +22212,7 @@
       </c>
       <c r="G632" s="24">
         <f>D632*H632</f>
-        <v/>
+        <v>28.905</v>
       </c>
       <c r="H632" s="25" t="n">
         <v>150</v>
@@ -22251,7 +22245,7 @@
       </c>
       <c r="G633" s="24">
         <f>D633*H633</f>
-        <v/>
+        <v>44.489999999999995</v>
       </c>
       <c r="H633" s="25" t="n">
         <v>150</v>
@@ -22284,7 +22278,7 @@
       </c>
       <c r="G634" s="24">
         <f>D634*H634</f>
-        <v/>
+        <v>88.605</v>
       </c>
       <c r="H634" s="25" t="n">
         <v>150</v>
@@ -22317,7 +22311,7 @@
       </c>
       <c r="G635" s="24">
         <f>D635*H635</f>
-        <v/>
+        <v>90.63</v>
       </c>
       <c r="H635" s="25" t="n">
         <v>150</v>
@@ -22350,7 +22344,7 @@
       </c>
       <c r="G636" s="24">
         <f>D636*H636</f>
-        <v/>
+        <v>120.88499999999999</v>
       </c>
       <c r="H636" s="25" t="n">
         <v>150</v>
@@ -22383,7 +22377,7 @@
       </c>
       <c r="G637" s="24">
         <f>D637*H637</f>
-        <v/>
+        <v>134.25</v>
       </c>
       <c r="H637" s="25" t="n">
         <v>150</v>
@@ -22416,7 +22410,7 @@
       </c>
       <c r="G638" s="24">
         <f>D638*H638</f>
-        <v/>
+        <v>139.62</v>
       </c>
       <c r="H638" s="25" t="n">
         <v>150</v>
@@ -22449,7 +22443,7 @@
       </c>
       <c r="G639" s="24">
         <f>D639*H639</f>
-        <v/>
+        <v>218.50500000000002</v>
       </c>
       <c r="H639" s="25" t="n">
         <v>150</v>
@@ -22482,7 +22476,7 @@
       </c>
       <c r="G640" s="24">
         <f>D640*H640</f>
-        <v/>
+        <v>5.5825</v>
       </c>
       <c r="H640" s="25" t="n">
         <v>175</v>
@@ -22515,7 +22509,7 @@
       </c>
       <c r="G641" s="24">
         <f>D641*H641</f>
-        <v/>
+        <v>5.775</v>
       </c>
       <c r="H641" s="25" t="n">
         <v>175</v>
@@ -22548,7 +22542,7 @@
       </c>
       <c r="G642" s="24">
         <f>D642*H642</f>
-        <v/>
+        <v>6.9825</v>
       </c>
       <c r="H642" s="25" t="n">
         <v>175</v>
@@ -22581,7 +22575,7 @@
       </c>
       <c r="G643" s="24">
         <f>D643*H643</f>
-        <v/>
+        <v>7.7175</v>
       </c>
       <c r="H643" s="25" t="n">
         <v>175</v>
@@ -22614,7 +22608,7 @@
       </c>
       <c r="G644" s="24">
         <f>D644*H644</f>
-        <v/>
+        <v>8.295</v>
       </c>
       <c r="H644" s="25" t="n">
         <v>175</v>
@@ -22647,7 +22641,7 @@
       </c>
       <c r="G645" s="24">
         <f>D645*H645</f>
-        <v/>
+        <v>12.215</v>
       </c>
       <c r="H645" s="25" t="n">
         <v>175</v>
@@ -22680,7 +22674,7 @@
       </c>
       <c r="G646" s="24">
         <f>D646*H646</f>
-        <v/>
+        <v>14.647499999999999</v>
       </c>
       <c r="H646" s="25" t="n">
         <v>175</v>
@@ -22713,7 +22707,7 @@
       </c>
       <c r="G647" s="24">
         <f>D647*H647</f>
-        <v/>
+        <v>18.619999999999997</v>
       </c>
       <c r="H647" s="25" t="n">
         <v>175</v>
@@ -22746,7 +22740,7 @@
       </c>
       <c r="G648" s="24">
         <f>D648*H648</f>
-        <v/>
+        <v>19.459999999999997</v>
       </c>
       <c r="H648" s="25" t="n">
         <v>175</v>
@@ -22779,7 +22773,7 @@
       </c>
       <c r="G649" s="24">
         <f>D649*H649</f>
-        <v/>
+        <v>24.2375</v>
       </c>
       <c r="H649" s="25" t="n">
         <v>175</v>
@@ -22812,7 +22806,7 @@
       </c>
       <c r="G650" s="24">
         <f>D650*H650</f>
-        <v/>
+        <v>34.4225</v>
       </c>
       <c r="H650" s="25" t="n">
         <v>175</v>
@@ -22845,7 +22839,7 @@
       </c>
       <c r="G651" s="24">
         <f>D651*H651</f>
-        <v/>
+        <v>36.925</v>
       </c>
       <c r="H651" s="25" t="n">
         <v>175</v>
@@ -22878,7 +22872,7 @@
       </c>
       <c r="G652" s="24">
         <f>D652*H652</f>
-        <v/>
+        <v>39.375</v>
       </c>
       <c r="H652" s="25" t="n">
         <v>175</v>
@@ -22911,7 +22905,7 @@
       </c>
       <c r="G653" s="24">
         <f>D653*H653</f>
-        <v/>
+        <v>40.355</v>
       </c>
       <c r="H653" s="25" t="n">
         <v>175</v>
@@ -22944,7 +22938,7 @@
       </c>
       <c r="G654" s="24">
         <f>D654*H654</f>
-        <v/>
+        <v>58.8525</v>
       </c>
       <c r="H654" s="25" t="n">
         <v>175</v>
@@ -22977,7 +22971,7 @@
       </c>
       <c r="G655" s="24">
         <f>D655*H655</f>
-        <v/>
+        <v>62.754999999999995</v>
       </c>
       <c r="H655" s="25" t="n">
         <v>175</v>
@@ -23010,7 +23004,7 @@
       </c>
       <c r="G656" s="24">
         <f>D656*H656</f>
-        <v/>
+        <v>64.505</v>
       </c>
       <c r="H656" s="25" t="n">
         <v>175</v>
@@ -23043,7 +23037,7 @@
       </c>
       <c r="G657" s="24">
         <f>D657*H657</f>
-        <v/>
+        <v>71.8025</v>
       </c>
       <c r="H657" s="25" t="n">
         <v>175</v>
@@ -23076,7 +23070,7 @@
       </c>
       <c r="G658" s="24">
         <f>D658*H658</f>
-        <v/>
+        <v>73.185</v>
       </c>
       <c r="H658" s="25" t="n">
         <v>175</v>
@@ -23109,7 +23103,7 @@
       </c>
       <c r="G659" s="24">
         <f>D659*H659</f>
-        <v/>
+        <v>80.5525</v>
       </c>
       <c r="H659" s="25" t="n">
         <v>175</v>
@@ -23142,7 +23136,7 @@
       </c>
       <c r="G660" s="24">
         <f>D660*H660</f>
-        <v/>
+        <v>82.46000000000001</v>
       </c>
       <c r="H660" s="25" t="n">
         <v>175</v>
@@ -23175,7 +23169,7 @@
       </c>
       <c r="G661" s="24">
         <f>D661*H661</f>
-        <v/>
+        <v>84.7525</v>
       </c>
       <c r="H661" s="25" t="n">
         <v>175</v>
@@ -23208,7 +23202,7 @@
       </c>
       <c r="G662" s="24">
         <f>D662*H662</f>
-        <v/>
+        <v>85.05</v>
       </c>
       <c r="H662" s="25" t="n">
         <v>175</v>
@@ -23241,7 +23235,7 @@
       </c>
       <c r="G663" s="24">
         <f>D663*H663</f>
-        <v/>
+        <v>86.52</v>
       </c>
       <c r="H663" s="25" t="n">
         <v>175</v>
@@ -23274,7 +23268,7 @@
       </c>
       <c r="G664" s="24">
         <f>D664*H664</f>
-        <v/>
+        <v>89.58250000000001</v>
       </c>
       <c r="H664" s="25" t="n">
         <v>175</v>
@@ -23307,7 +23301,7 @@
       </c>
       <c r="G665" s="24">
         <f>D665*H665</f>
-        <v/>
+        <v>90.0375</v>
       </c>
       <c r="H665" s="25" t="n">
         <v>175</v>
@@ -23340,7 +23334,7 @@
       </c>
       <c r="G666" s="24">
         <f>D666*H666</f>
-        <v/>
+        <v>91.26249999999999</v>
       </c>
       <c r="H666" s="25" t="n">
         <v>175</v>
@@ -23373,7 +23367,7 @@
       </c>
       <c r="G667" s="24">
         <f>D667*H667</f>
-        <v/>
+        <v>93.4675</v>
       </c>
       <c r="H667" s="25" t="n">
         <v>175</v>
@@ -23406,7 +23400,7 @@
       </c>
       <c r="G668" s="24">
         <f>D668*H668</f>
-        <v/>
+        <v>94.3075</v>
       </c>
       <c r="H668" s="25" t="n">
         <v>175</v>
@@ -23439,7 +23433,7 @@
       </c>
       <c r="G669" s="24">
         <f>D669*H669</f>
-        <v/>
+        <v>94.7275</v>
       </c>
       <c r="H669" s="25" t="n">
         <v>175</v>
@@ -23472,7 +23466,7 @@
       </c>
       <c r="G670" s="24">
         <f>D670*H670</f>
-        <v/>
+        <v>95.1125</v>
       </c>
       <c r="H670" s="25" t="n">
         <v>175</v>
@@ -23505,7 +23499,7 @@
       </c>
       <c r="G671" s="24">
         <f>D671*H671</f>
-        <v/>
+        <v>95.16499999999999</v>
       </c>
       <c r="H671" s="25" t="n">
         <v>175</v>
@@ -23538,7 +23532,7 @@
       </c>
       <c r="G672" s="24">
         <f>D672*H672</f>
-        <v/>
+        <v>106.8375</v>
       </c>
       <c r="H672" s="25" t="n">
         <v>175</v>
@@ -23571,7 +23565,7 @@
       </c>
       <c r="G673" s="24">
         <f>D673*H673</f>
-        <v/>
+        <v>106.8375</v>
       </c>
       <c r="H673" s="25" t="n">
         <v>175</v>
@@ -23604,7 +23598,7 @@
       </c>
       <c r="G674" s="24">
         <f>D674*H674</f>
-        <v/>
+        <v>115.465</v>
       </c>
       <c r="H674" s="25" t="n">
         <v>175</v>
@@ -23637,7 +23631,7 @@
       </c>
       <c r="G675" s="24">
         <f>D675*H675</f>
-        <v/>
+        <v>117.33749999999999</v>
       </c>
       <c r="H675" s="25" t="n">
         <v>175</v>
@@ -23670,7 +23664,7 @@
       </c>
       <c r="G676" s="24">
         <f>D676*H676</f>
-        <v/>
+        <v>118.05499999999999</v>
       </c>
       <c r="H676" s="25" t="n">
         <v>175</v>
@@ -23703,7 +23697,7 @@
       </c>
       <c r="G677" s="24">
         <f>D677*H677</f>
-        <v/>
+        <v>121.69500000000001</v>
       </c>
       <c r="H677" s="25" t="n">
         <v>175</v>
@@ -23736,7 +23730,7 @@
       </c>
       <c r="G678" s="24">
         <f>D678*H678</f>
-        <v/>
+        <v>124.14500000000001</v>
       </c>
       <c r="H678" s="25" t="n">
         <v>175</v>
@@ -23769,7 +23763,7 @@
       </c>
       <c r="G679" s="24">
         <f>D679*H679</f>
-        <v/>
+        <v>138.5125</v>
       </c>
       <c r="H679" s="25" t="n">
         <v>175</v>
@@ -23802,7 +23796,7 @@
       </c>
       <c r="G680" s="24">
         <f>D680*H680</f>
-        <v/>
+        <v>140.56</v>
       </c>
       <c r="H680" s="25" t="n">
         <v>175</v>
@@ -23835,7 +23829,7 @@
       </c>
       <c r="G681" s="24">
         <f>D681*H681</f>
-        <v/>
+        <v>147.73499999999999</v>
       </c>
       <c r="H681" s="25" t="n">
         <v>175</v>
@@ -23868,7 +23862,7 @@
       </c>
       <c r="G682" s="24">
         <f>D682*H682</f>
-        <v/>
+        <v>151.2875</v>
       </c>
       <c r="H682" s="25" t="n">
         <v>175</v>
@@ -23901,7 +23895,7 @@
       </c>
       <c r="G683" s="24">
         <f>D683*H683</f>
-        <v/>
+        <v>151.4625</v>
       </c>
       <c r="H683" s="25" t="n">
         <v>175</v>
@@ -23934,7 +23928,7 @@
       </c>
       <c r="G684" s="24">
         <f>D684*H684</f>
-        <v/>
+        <v>151.865</v>
       </c>
       <c r="H684" s="25" t="n">
         <v>175</v>
@@ -23967,7 +23961,7 @@
       </c>
       <c r="G685" s="24">
         <f>D685*H685</f>
-        <v/>
+        <v>152.775</v>
       </c>
       <c r="H685" s="25" t="n">
         <v>175</v>
@@ -24000,7 +23994,7 @@
       </c>
       <c r="G686" s="24">
         <f>D686*H686</f>
-        <v/>
+        <v>165.2525</v>
       </c>
       <c r="H686" s="25" t="n">
         <v>175</v>
@@ -24033,7 +24027,7 @@
       </c>
       <c r="G687" s="24">
         <f>D687*H687</f>
-        <v/>
+        <v>171.6225</v>
       </c>
       <c r="H687" s="25" t="n">
         <v>175</v>
@@ -24066,7 +24060,7 @@
       </c>
       <c r="G688" s="24">
         <f>D688*H688</f>
-        <v/>
+        <v>187.6175</v>
       </c>
       <c r="H688" s="25" t="n">
         <v>175</v>
@@ -24099,7 +24093,7 @@
       </c>
       <c r="G689" s="24">
         <f>D689*H689</f>
-        <v/>
+        <v>195.4225</v>
       </c>
       <c r="H689" s="25" t="n">
         <v>175</v>
@@ -24132,7 +24126,7 @@
       </c>
       <c r="G690" s="24">
         <f>D690*H690</f>
-        <v/>
+        <v>201.11</v>
       </c>
       <c r="H690" s="25" t="n">
         <v>175</v>
@@ -24165,7 +24159,7 @@
       </c>
       <c r="G691" s="24">
         <f>D691*H691</f>
-        <v/>
+        <v>203.29749999999999</v>
       </c>
       <c r="H691" s="25" t="n">
         <v>175</v>
@@ -24198,7 +24192,7 @@
       </c>
       <c r="G692" s="24">
         <f>D692*H692</f>
-        <v/>
+        <v>205.90500000000003</v>
       </c>
       <c r="H692" s="25" t="n">
         <v>175</v>
@@ -24231,7 +24225,7 @@
       </c>
       <c r="G693" s="24">
         <f>D693*H693</f>
-        <v/>
+        <v>209.195</v>
       </c>
       <c r="H693" s="25" t="n">
         <v>175</v>
@@ -24264,7 +24258,7 @@
       </c>
       <c r="G694" s="24">
         <f>D694*H694</f>
-        <v/>
+        <v>210.875</v>
       </c>
       <c r="H694" s="25" t="n">
         <v>175</v>
@@ -24297,7 +24291,7 @@
       </c>
       <c r="G695" s="24">
         <f>D695*H695</f>
-        <v/>
+        <v>229.39</v>
       </c>
       <c r="H695" s="25" t="n">
         <v>175</v>
@@ -24330,7 +24324,7 @@
       </c>
       <c r="G696" s="24">
         <f>D696*H696</f>
-        <v/>
+        <v>238.35000000000002</v>
       </c>
       <c r="H696" s="25" t="n">
         <v>175</v>
@@ -24363,7 +24357,7 @@
       </c>
       <c r="G697" s="24">
         <f>D697*H697</f>
-        <v/>
+        <v>239.8725</v>
       </c>
       <c r="H697" s="25" t="n">
         <v>175</v>
@@ -24396,7 +24390,7 @@
       </c>
       <c r="G698" s="24">
         <f>D698*H698</f>
-        <v/>
+        <v>256.8125</v>
       </c>
       <c r="H698" s="25" t="n">
         <v>175</v>
@@ -24429,7 +24423,7 @@
       </c>
       <c r="G699" s="24">
         <f>D699*H699</f>
-        <v/>
+        <v>308.84</v>
       </c>
       <c r="H699" s="25" t="n">
         <v>175</v>
@@ -24462,7 +24456,7 @@
       </c>
       <c r="G700" s="24">
         <f>D700*H700</f>
-        <v/>
+        <v>327.5475</v>
       </c>
       <c r="H700" s="25" t="n">
         <v>175</v>
@@ -24495,7 +24489,7 @@
       </c>
       <c r="G701" s="24">
         <f>D701*H701</f>
-        <v/>
+        <v>338.8175</v>
       </c>
       <c r="H701" s="25" t="n">
         <v>175</v>
@@ -24528,7 +24522,7 @@
       </c>
       <c r="G702" s="24">
         <f>D702*H702</f>
-        <v/>
+        <v>356.68499999999995</v>
       </c>
       <c r="H702" s="25" t="n">
         <v>175</v>
@@ -24561,7 +24555,7 @@
       </c>
       <c r="G703" s="24">
         <f>D703*H703</f>
-        <v/>
+        <v>388.01</v>
       </c>
       <c r="H703" s="25" t="n">
         <v>175</v>
@@ -24594,7 +24588,7 @@
       </c>
       <c r="G704" s="24">
         <f>D704*H704</f>
-        <v/>
+        <v>409.57</v>
       </c>
       <c r="H704" s="25" t="n">
         <v>175</v>
@@ -24627,7 +24621,7 @@
       </c>
       <c r="G705" s="24">
         <f>D705*H705</f>
-        <v/>
+        <v>431.3925</v>
       </c>
       <c r="H705" s="25" t="n">
         <v>175</v>
@@ -24660,7 +24654,7 @@
       </c>
       <c r="G706" s="24">
         <f>D706*H706</f>
-        <v/>
+        <v>442.3825</v>
       </c>
       <c r="H706" s="25" t="n">
         <v>175</v>
@@ -24693,7 +24687,7 @@
       </c>
       <c r="G707" s="24">
         <f>D707*H707</f>
-        <v/>
+        <v>2397.7799999999997</v>
       </c>
       <c r="H707" s="25" t="n">
         <v>175</v>
@@ -24726,7 +24720,7 @@
       </c>
       <c r="G708" s="24">
         <f>D708*H708</f>
-        <v/>
+        <v>118.92999999999999</v>
       </c>
       <c r="H708" s="25" t="n">
         <v>175</v>
@@ -24759,7 +24753,7 @@
       </c>
       <c r="G709" s="24">
         <f>D709*H709</f>
-        <v/>
+        <v>35.895</v>
       </c>
       <c r="H709" s="25" t="n">
         <v>150</v>
@@ -24792,7 +24786,7 @@
       </c>
       <c r="G710" s="24">
         <f>D710*H710</f>
-        <v/>
+        <v>104.655</v>
       </c>
       <c r="H710" s="25" t="n">
         <v>150</v>
@@ -24825,7 +24819,7 @@
       </c>
       <c r="G711" s="24">
         <f>D711*H711</f>
-        <v/>
+        <v>117.825</v>
       </c>
       <c r="H711" s="25" t="n">
         <v>150</v>
@@ -24858,7 +24852,7 @@
       </c>
       <c r="G712" s="24">
         <f>D712*H712</f>
-        <v/>
+        <v>9.135</v>
       </c>
       <c r="H712" s="25" t="n">
         <v>150</v>
@@ -24891,7 +24885,7 @@
       </c>
       <c r="G713" s="24">
         <f>D713*H713</f>
-        <v/>
+        <v>9.795</v>
       </c>
       <c r="H713" s="25" t="n">
         <v>150</v>
@@ -24924,7 +24918,7 @@
       </c>
       <c r="G714" s="24">
         <f>D714*H714</f>
-        <v/>
+        <v>10.26</v>
       </c>
       <c r="H714" s="25" t="n">
         <v>150</v>
@@ -24957,7 +24951,7 @@
       </c>
       <c r="G715" s="24">
         <f>D715*H715</f>
-        <v/>
+        <v>10.635000000000002</v>
       </c>
       <c r="H715" s="25" t="n">
         <v>150</v>
@@ -24990,7 +24984,7 @@
       </c>
       <c r="G716" s="24">
         <f>D716*H716</f>
-        <v/>
+        <v>13.305</v>
       </c>
       <c r="H716" s="25" t="n">
         <v>150</v>
@@ -25023,7 +25017,7 @@
       </c>
       <c r="G717" s="24">
         <f>D717*H717</f>
-        <v/>
+        <v>17.88</v>
       </c>
       <c r="H717" s="25" t="n">
         <v>150</v>
@@ -25056,7 +25050,7 @@
       </c>
       <c r="G718" s="24">
         <f>D718*H718</f>
-        <v/>
+        <v>24.134999999999998</v>
       </c>
       <c r="H718" s="25" t="n">
         <v>150</v>
@@ -25089,7 +25083,7 @@
       </c>
       <c r="G719" s="24">
         <f>D719*H719</f>
-        <v/>
+        <v>33.18</v>
       </c>
       <c r="H719" s="25" t="n">
         <v>150</v>
@@ -25122,7 +25116,7 @@
       </c>
       <c r="G720" s="24">
         <f>D720*H720</f>
-        <v/>
+        <v>40.995</v>
       </c>
       <c r="H720" s="25" t="n">
         <v>150</v>
@@ -25155,7 +25149,7 @@
       </c>
       <c r="G721" s="24">
         <f>D721*H721</f>
-        <v/>
+        <v>45.0</v>
       </c>
       <c r="H721" s="25" t="n">
         <v>150</v>
@@ -25188,7 +25182,7 @@
       </c>
       <c r="G722" s="24">
         <f>D722*H722</f>
-        <v/>
+        <v>66.78</v>
       </c>
       <c r="H722" s="25" t="n">
         <v>150</v>
@@ -25221,7 +25215,7 @@
       </c>
       <c r="G723" s="24">
         <f>D723*H723</f>
-        <v/>
+        <v>89.07</v>
       </c>
       <c r="H723" s="25" t="n">
         <v>150</v>
@@ -25254,7 +25248,7 @@
       </c>
       <c r="G724" s="24">
         <f>D724*H724</f>
-        <v/>
+        <v>105.615</v>
       </c>
       <c r="H724" s="25" t="n">
         <v>150</v>
@@ -25287,7 +25281,7 @@
       </c>
       <c r="G725" s="24">
         <f>D725*H725</f>
-        <v/>
+        <v>115.095</v>
       </c>
       <c r="H725" s="25" t="n">
         <v>150</v>
@@ -25320,7 +25314,7 @@
       </c>
       <c r="G726" s="24">
         <f>D726*H726</f>
-        <v/>
+        <v>189.22500000000002</v>
       </c>
       <c r="H726" s="25" t="n">
         <v>150</v>
@@ -25353,7 +25347,7 @@
       </c>
       <c r="G727" s="24">
         <f>D727*H727</f>
-        <v/>
+        <v>191.22</v>
       </c>
       <c r="H727" s="25" t="n">
         <v>150</v>
@@ -25386,7 +25380,7 @@
       </c>
       <c r="G728" s="24">
         <f>D728*H728</f>
-        <v/>
+        <v>236.60999999999999</v>
       </c>
       <c r="H728" s="25" t="n">
         <v>150</v>
@@ -25419,7 +25413,7 @@
       </c>
       <c r="G729" s="24">
         <f>D729*H729</f>
-        <v/>
+        <v>279.345</v>
       </c>
       <c r="H729" s="25" t="n">
         <v>150</v>
@@ -25452,7 +25446,7 @@
       </c>
       <c r="G730" s="24">
         <f>D730*H730</f>
-        <v/>
+        <v>329.21999999999997</v>
       </c>
       <c r="H730" s="25" t="n">
         <v>150</v>
@@ -25485,7 +25479,7 @@
       </c>
       <c r="G731" s="24">
         <f>D731*H731</f>
-        <v/>
+        <v>347.42999999999995</v>
       </c>
       <c r="H731" s="25" t="n">
         <v>150</v>
@@ -25518,7 +25512,7 @@
       </c>
       <c r="G732" s="24">
         <f>D732*H732</f>
-        <v/>
+        <v>362.685</v>
       </c>
       <c r="H732" s="25" t="n">
         <v>150</v>
@@ -25551,7 +25545,7 @@
       </c>
       <c r="G733" s="24">
         <f>D733*H733</f>
-        <v/>
+        <v>553.215</v>
       </c>
       <c r="H733" s="25" t="n">
         <v>150</v>
@@ -25584,7 +25578,7 @@
       </c>
       <c r="G734" s="24">
         <f>D734*H734</f>
-        <v/>
+        <v>569.205</v>
       </c>
       <c r="H734" s="25" t="n">
         <v>150</v>
@@ -25617,7 +25611,7 @@
       </c>
       <c r="G735" s="24">
         <f>D735*H735</f>
-        <v/>
+        <v>828.705</v>
       </c>
       <c r="H735" s="25" t="n">
         <v>150</v>
@@ -25650,7 +25644,7 @@
       </c>
       <c r="G736" s="24">
         <f>D736*H736</f>
-        <v/>
+        <v>1093.47</v>
       </c>
       <c r="H736" s="25" t="n">
         <v>150</v>
@@ -25683,7 +25677,7 @@
       </c>
       <c r="G737" s="24">
         <f>D737*H737</f>
-        <v/>
+        <v>4.2299999999999995</v>
       </c>
       <c r="H737" s="25" t="n">
         <v>150</v>
@@ -25716,7 +25710,7 @@
       </c>
       <c r="G738" s="24">
         <f>D738*H738</f>
-        <v/>
+        <v>8.82</v>
       </c>
       <c r="H738" s="25" t="n">
         <v>150</v>
@@ -25749,7 +25743,7 @@
       </c>
       <c r="G739" s="24">
         <f>D739*H739</f>
-        <v/>
+        <v>13.38</v>
       </c>
       <c r="H739" s="25" t="n">
         <v>150</v>
@@ -25782,7 +25776,7 @@
       </c>
       <c r="G740" s="24">
         <f>D740*H740</f>
-        <v/>
+        <v>47.504999999999995</v>
       </c>
       <c r="H740" s="25" t="n">
         <v>150</v>
@@ -25815,7 +25809,7 @@
       </c>
       <c r="G741" s="24">
         <f>D741*H741</f>
-        <v/>
+        <v>60.63</v>
       </c>
       <c r="H741" s="25" t="n">
         <v>150</v>
@@ -25848,7 +25842,7 @@
       </c>
       <c r="G742" s="24">
         <f>D742*H742</f>
-        <v/>
+        <v>73.8</v>
       </c>
       <c r="H742" s="25" t="n">
         <v>150</v>
@@ -25881,7 +25875,7 @@
       </c>
       <c r="G743" s="24">
         <f>D743*H743</f>
-        <v/>
+        <v>90.92999999999999</v>
       </c>
       <c r="H743" s="25" t="n">
         <v>150</v>
@@ -25914,7 +25908,7 @@
       </c>
       <c r="G744" s="24">
         <f>D744*H744</f>
-        <v/>
+        <v>92.385</v>
       </c>
       <c r="H744" s="25" t="n">
         <v>150</v>
@@ -25947,7 +25941,7 @@
       </c>
       <c r="G745" s="24">
         <f>D745*H745</f>
-        <v/>
+        <v>93.855</v>
       </c>
       <c r="H745" s="25" t="n">
         <v>150</v>
@@ -25980,7 +25974,7 @@
       </c>
       <c r="G746" s="24">
         <f>D746*H746</f>
-        <v/>
+        <v>100.03500000000001</v>
       </c>
       <c r="H746" s="25" t="n">
         <v>150</v>
@@ -26013,7 +26007,7 @@
       </c>
       <c r="G747" s="24">
         <f>D747*H747</f>
-        <v/>
+        <v>103.86</v>
       </c>
       <c r="H747" s="25" t="n">
         <v>150</v>
@@ -26046,7 +26040,7 @@
       </c>
       <c r="G748" s="24">
         <f>D748*H748</f>
-        <v/>
+        <v>105.44999999999999</v>
       </c>
       <c r="H748" s="25" t="n">
         <v>150</v>
@@ -26079,7 +26073,7 @@
       </c>
       <c r="G749" s="24">
         <f>D749*H749</f>
-        <v/>
+        <v>106.905</v>
       </c>
       <c r="H749" s="25" t="n">
         <v>150</v>
@@ -26112,7 +26106,7 @@
       </c>
       <c r="G750" s="24">
         <f>D750*H750</f>
-        <v/>
+        <v>111.21</v>
       </c>
       <c r="H750" s="25" t="n">
         <v>150</v>
@@ -26145,7 +26139,7 @@
       </c>
       <c r="G751" s="24">
         <f>D751*H751</f>
-        <v/>
+        <v>125.1</v>
       </c>
       <c r="H751" s="25" t="n">
         <v>150</v>
@@ -26178,7 +26172,7 @@
       </c>
       <c r="G752" s="24">
         <f>D752*H752</f>
-        <v/>
+        <v>133.125</v>
       </c>
       <c r="H752" s="25" t="n">
         <v>150</v>
@@ -26211,7 +26205,7 @@
       </c>
       <c r="G753" s="24">
         <f>D753*H753</f>
-        <v/>
+        <v>193.185</v>
       </c>
       <c r="H753" s="25" t="n">
         <v>150</v>
@@ -26244,7 +26238,7 @@
       </c>
       <c r="G754" s="24">
         <f>D754*H754</f>
-        <v/>
+        <v>207.01500000000001</v>
       </c>
       <c r="H754" s="25" t="n">
         <v>150</v>
@@ -26277,7 +26271,7 @@
       </c>
       <c r="G755" s="24">
         <f>D755*H755</f>
-        <v/>
+        <v>242.46</v>
       </c>
       <c r="H755" s="25" t="n">
         <v>150</v>
@@ -26310,7 +26304,7 @@
       </c>
       <c r="G756" s="24">
         <f>D756*H756</f>
-        <v/>
+        <v>310.995</v>
       </c>
       <c r="H756" s="25" t="n">
         <v>150</v>
@@ -26343,7 +26337,7 @@
       </c>
       <c r="G757" s="24">
         <f>D757*H757</f>
-        <v/>
+        <v>354.15000000000003</v>
       </c>
       <c r="H757" s="25" t="n">
         <v>150</v>
@@ -26376,7 +26370,7 @@
       </c>
       <c r="G758" s="24">
         <f>D758*H758</f>
-        <v/>
+        <v>382.65000000000003</v>
       </c>
       <c r="H758" s="25" t="n">
         <v>150</v>
@@ -26409,7 +26403,7 @@
       </c>
       <c r="G759" s="24">
         <f>D759*H759</f>
-        <v/>
+        <v>454.575</v>
       </c>
       <c r="H759" s="25" t="n">
         <v>150</v>
@@ -26442,7 +26436,7 @@
       </c>
       <c r="G760" s="24">
         <f>D760*H760</f>
-        <v/>
+        <v>505.455</v>
       </c>
       <c r="H760" s="25" t="n">
         <v>150</v>
@@ -26475,7 +26469,7 @@
       </c>
       <c r="G761" s="24">
         <f>D761*H761</f>
-        <v/>
+        <v>662.8499999999999</v>
       </c>
       <c r="H761" s="25" t="n">
         <v>150</v>
@@ -26508,7 +26502,7 @@
       </c>
       <c r="G762" s="24">
         <f>D762*H762</f>
-        <v/>
+        <v>30.4325</v>
       </c>
       <c r="H762" s="25" t="n">
         <v>175</v>
@@ -26541,7 +26535,7 @@
       </c>
       <c r="G763" s="24">
         <f>D763*H763</f>
-        <v/>
+        <v>38.9375</v>
       </c>
       <c r="H763" s="25" t="n">
         <v>175</v>
@@ -26574,7 +26568,7 @@
       </c>
       <c r="G764" s="24">
         <f>D764*H764</f>
-        <v/>
+        <v>97.4925</v>
       </c>
       <c r="H764" s="25" t="n">
         <v>175</v>
@@ -26607,7 +26601,7 @@
       </c>
       <c r="G765" s="24">
         <f>D765*H765</f>
-        <v/>
+        <v>100.205</v>
       </c>
       <c r="H765" s="25" t="n">
         <v>175</v>
@@ -26640,7 +26634,7 @@
       </c>
       <c r="G766" s="24">
         <f>D766*H766</f>
-        <v/>
+        <v>101.4825</v>
       </c>
       <c r="H766" s="25" t="n">
         <v>175</v>
@@ -26673,7 +26667,7 @@
       </c>
       <c r="G767" s="24">
         <f>D767*H767</f>
-        <v/>
+        <v>113.83749999999999</v>
       </c>
       <c r="H767" s="25" t="n">
         <v>175</v>
@@ -26706,7 +26700,7 @@
       </c>
       <c r="G768" s="24">
         <f>D768*H768</f>
-        <v/>
+        <v>139.0725</v>
       </c>
       <c r="H768" s="25" t="n">
         <v>175</v>
@@ -26739,7 +26733,7 @@
       </c>
       <c r="G769" s="24">
         <f>D769*H769</f>
-        <v/>
+        <v>140.7525</v>
       </c>
       <c r="H769" s="25" t="n">
         <v>175</v>
@@ -26772,7 +26766,7 @@
       </c>
       <c r="G770" s="24">
         <f>D770*H770</f>
-        <v/>
+        <v>143.29</v>
       </c>
       <c r="H770" s="25" t="n">
         <v>175</v>
@@ -26805,7 +26799,7 @@
       </c>
       <c r="G771" s="24">
         <f>D771*H771</f>
-        <v/>
+        <v>196.84</v>
       </c>
       <c r="H771" s="25" t="n">
         <v>175</v>
@@ -26838,7 +26832,7 @@
       </c>
       <c r="G772" s="24">
         <f>D772*H772</f>
-        <v/>
+        <v>231.56</v>
       </c>
       <c r="H772" s="25" t="n">
         <v>175</v>
@@ -26871,7 +26865,7 @@
       </c>
       <c r="G773" s="24">
         <f>D773*H773</f>
-        <v/>
+        <v>241.0975</v>
       </c>
       <c r="H773" s="25" t="n">
         <v>175</v>
@@ -26904,7 +26898,7 @@
       </c>
       <c r="G774" s="24">
         <f>D774*H774</f>
-        <v/>
+        <v>323.19</v>
       </c>
       <c r="H774" s="25" t="n">
         <v>175</v>
@@ -26937,7 +26931,7 @@
       </c>
       <c r="G775" s="24">
         <f>D775*H775</f>
-        <v/>
+        <v>476.21000000000004</v>
       </c>
       <c r="H775" s="25" t="n">
         <v>175</v>
@@ -26970,7 +26964,7 @@
       </c>
       <c r="G776" s="24">
         <f>D776*H776</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H776" s="25" t="n">
         <v>150</v>
@@ -27003,7 +26997,7 @@
       </c>
       <c r="G777" s="24">
         <f>D777*H777</f>
-        <v/>
+        <v>43.815000000000005</v>
       </c>
       <c r="H777" s="25" t="n">
         <v>150</v>
@@ -27036,7 +27030,7 @@
       </c>
       <c r="G778" s="24">
         <f>D778*H778</f>
-        <v/>
+        <v>46.364999999999995</v>
       </c>
       <c r="H778" s="25" t="n">
         <v>150</v>
@@ -27069,7 +27063,7 @@
       </c>
       <c r="G779" s="24">
         <f>D779*H779</f>
-        <v/>
+        <v>55.155</v>
       </c>
       <c r="H779" s="25" t="n">
         <v>150</v>
@@ -27102,7 +27096,7 @@
       </c>
       <c r="G780" s="24">
         <f>D780*H780</f>
-        <v/>
+        <v>85.53</v>
       </c>
       <c r="H780" s="25" t="n">
         <v>150</v>
@@ -27135,7 +27129,7 @@
       </c>
       <c r="G781" s="24">
         <f>D781*H781</f>
-        <v/>
+        <v>89.85</v>
       </c>
       <c r="H781" s="25" t="n">
         <v>150</v>
@@ -27168,7 +27162,7 @@
       </c>
       <c r="G782" s="24">
         <f>D782*H782</f>
-        <v/>
+        <v>101.76</v>
       </c>
       <c r="H782" s="25" t="n">
         <v>150</v>
@@ -27201,7 +27195,7 @@
       </c>
       <c r="G783" s="24">
         <f>D783*H783</f>
-        <v/>
+        <v>103.61999999999999</v>
       </c>
       <c r="H783" s="25" t="n">
         <v>150</v>
@@ -27234,7 +27228,7 @@
       </c>
       <c r="G784" s="24">
         <f>D784*H784</f>
-        <v/>
+        <v>122.655</v>
       </c>
       <c r="H784" s="25" t="n">
         <v>150</v>
@@ -27267,7 +27261,7 @@
       </c>
       <c r="G785" s="24">
         <f>D785*H785</f>
-        <v/>
+        <v>132.96</v>
       </c>
       <c r="H785" s="25" t="n">
         <v>150</v>
@@ -27300,7 +27294,7 @@
       </c>
       <c r="G786" s="24">
         <f>D786*H786</f>
-        <v/>
+        <v>133.965</v>
       </c>
       <c r="H786" s="25" t="n">
         <v>150</v>
@@ -27333,7 +27327,7 @@
       </c>
       <c r="G787" s="24">
         <f>D787*H787</f>
-        <v/>
+        <v>134.835</v>
       </c>
       <c r="H787" s="25" t="n">
         <v>150</v>
@@ -27366,7 +27360,7 @@
       </c>
       <c r="G788" s="24">
         <f>D788*H788</f>
-        <v/>
+        <v>147.15</v>
       </c>
       <c r="H788" s="25" t="n">
         <v>150</v>
@@ -27399,7 +27393,7 @@
       </c>
       <c r="G789" s="24">
         <f>D789*H789</f>
-        <v/>
+        <v>151.275</v>
       </c>
       <c r="H789" s="25" t="n">
         <v>150</v>
@@ -27432,7 +27426,7 @@
       </c>
       <c r="G790" s="24">
         <f>D790*H790</f>
-        <v/>
+        <v>183.08999999999997</v>
       </c>
       <c r="H790" s="25" t="n">
         <v>150</v>
@@ -27465,7 +27459,7 @@
       </c>
       <c r="G791" s="24">
         <f>D791*H791</f>
-        <v/>
+        <v>228.11999999999998</v>
       </c>
       <c r="H791" s="25" t="n">
         <v>150</v>
@@ -27498,7 +27492,7 @@
       </c>
       <c r="G792" s="24">
         <f>D792*H792</f>
-        <v/>
+        <v>639.195</v>
       </c>
       <c r="H792" s="25" t="n">
         <v>150</v>
@@ -27531,7 +27525,7 @@
       </c>
       <c r="G793" s="24">
         <f>D793*H793</f>
-        <v/>
+        <v>74.34</v>
       </c>
       <c r="H793" s="25" t="n">
         <v>150</v>
@@ -27564,7 +27558,7 @@
       </c>
       <c r="G794" s="24">
         <f>D794*H794</f>
-        <v/>
+        <v>122.94</v>
       </c>
       <c r="H794" s="25" t="n">
         <v>150</v>
@@ -27597,7 +27591,7 @@
       </c>
       <c r="G795" s="24">
         <f>D795*H795</f>
-        <v/>
+        <v>167.98499999999999</v>
       </c>
       <c r="H795" s="25" t="n">
         <v>150</v>
@@ -27630,7 +27624,7 @@
       </c>
       <c r="G796" s="24">
         <f>D796*H796</f>
-        <v/>
+        <v>113.46</v>
       </c>
       <c r="H796" s="25" t="n">
         <v>150</v>
@@ -27663,7 +27657,7 @@
       </c>
       <c r="G797" s="24">
         <f>D797*H797</f>
-        <v/>
+        <v>124.275</v>
       </c>
       <c r="H797" s="25" t="n">
         <v>150</v>
@@ -27696,7 +27690,7 @@
       </c>
       <c r="G798" s="24">
         <f>D798*H798</f>
-        <v/>
+        <v>153.72</v>
       </c>
       <c r="H798" s="25" t="n">
         <v>150</v>
@@ -27729,7 +27723,7 @@
       </c>
       <c r="G799" s="24">
         <f>D799*H799</f>
-        <v/>
+        <v>63.38999999999999</v>
       </c>
       <c r="H799" s="25" t="n">
         <v>150</v>
@@ -27762,7 +27756,7 @@
       </c>
       <c r="G800" s="24">
         <f>D800*H800</f>
-        <v/>
+        <v>80.25</v>
       </c>
       <c r="H800" s="25" t="n">
         <v>150</v>
@@ -27795,7 +27789,7 @@
       </c>
       <c r="G801" s="24">
         <f>D801*H801</f>
-        <v/>
+        <v>81.58500000000001</v>
       </c>
       <c r="H801" s="25" t="n">
         <v>150</v>
@@ -27828,7 +27822,7 @@
       </c>
       <c r="G802" s="24">
         <f>D802*H802</f>
-        <v/>
+        <v>82.38000000000001</v>
       </c>
       <c r="H802" s="25" t="n">
         <v>150</v>
@@ -27861,7 +27855,7 @@
       </c>
       <c r="G803" s="24">
         <f>D803*H803</f>
-        <v/>
+        <v>87.63000000000001</v>
       </c>
       <c r="H803" s="25" t="n">
         <v>150</v>
@@ -27894,7 +27888,7 @@
       </c>
       <c r="G804" s="24">
         <f>D804*H804</f>
-        <v/>
+        <v>93.9</v>
       </c>
       <c r="H804" s="25" t="n">
         <v>150</v>
@@ -27927,7 +27921,7 @@
       </c>
       <c r="G805" s="24">
         <f>D805*H805</f>
-        <v/>
+        <v>96.07499999999999</v>
       </c>
       <c r="H805" s="25" t="n">
         <v>150</v>
@@ -27960,7 +27954,7 @@
       </c>
       <c r="G806" s="24">
         <f>D806*H806</f>
-        <v/>
+        <v>96.60000000000001</v>
       </c>
       <c r="H806" s="25" t="n">
         <v>150</v>
@@ -27993,7 +27987,7 @@
       </c>
       <c r="G807" s="24">
         <f>D807*H807</f>
-        <v/>
+        <v>105.46499999999999</v>
       </c>
       <c r="H807" s="25" t="n">
         <v>150</v>
@@ -28026,7 +28020,7 @@
       </c>
       <c r="G808" s="24">
         <f>D808*H808</f>
-        <v/>
+        <v>107.58</v>
       </c>
       <c r="H808" s="25" t="n">
         <v>150</v>
@@ -28059,7 +28053,7 @@
       </c>
       <c r="G809" s="24">
         <f>D809*H809</f>
-        <v/>
+        <v>126.16499999999999</v>
       </c>
       <c r="H809" s="25" t="n">
         <v>150</v>
@@ -28092,7 +28086,7 @@
       </c>
       <c r="G810" s="24">
         <f>D810*H810</f>
-        <v/>
+        <v>127.755</v>
       </c>
       <c r="H810" s="25" t="n">
         <v>150</v>
@@ -28125,7 +28119,7 @@
       </c>
       <c r="G811" s="24">
         <f>D811*H811</f>
-        <v/>
+        <v>134.60999999999999</v>
       </c>
       <c r="H811" s="25" t="n">
         <v>150</v>
@@ -28158,7 +28152,7 @@
       </c>
       <c r="G812" s="24">
         <f>D812*H812</f>
-        <v/>
+        <v>135.03</v>
       </c>
       <c r="H812" s="25" t="n">
         <v>150</v>
@@ -28191,7 +28185,7 @@
       </c>
       <c r="G813" s="24">
         <f>D813*H813</f>
-        <v/>
+        <v>145.65</v>
       </c>
       <c r="H813" s="25" t="n">
         <v>150</v>
@@ -28224,7 +28218,7 @@
       </c>
       <c r="G814" s="24">
         <f>D814*H814</f>
-        <v/>
+        <v>148.05</v>
       </c>
       <c r="H814" s="25" t="n">
         <v>150</v>
@@ -28257,7 +28251,7 @@
       </c>
       <c r="G815" s="24">
         <f>D815*H815</f>
-        <v/>
+        <v>152.48999999999998</v>
       </c>
       <c r="H815" s="25" t="n">
         <v>150</v>
@@ -28290,7 +28284,7 @@
       </c>
       <c r="G816" s="24">
         <f>D816*H816</f>
-        <v/>
+        <v>154.98</v>
       </c>
       <c r="H816" s="25" t="n">
         <v>150</v>
@@ -28323,7 +28317,7 @@
       </c>
       <c r="G817" s="24">
         <f>D817*H817</f>
-        <v/>
+        <v>173.28</v>
       </c>
       <c r="H817" s="25" t="n">
         <v>150</v>
@@ -28356,7 +28350,7 @@
       </c>
       <c r="G818" s="24">
         <f>D818*H818</f>
-        <v/>
+        <v>228.11999999999998</v>
       </c>
       <c r="H818" s="25" t="n">
         <v>150</v>
@@ -28389,7 +28383,7 @@
       </c>
       <c r="G819" s="24">
         <f>D819*H819</f>
-        <v/>
+        <v>312.76500000000004</v>
       </c>
       <c r="H819" s="25" t="n">
         <v>150</v>
@@ -28422,7 +28416,7 @@
       </c>
       <c r="G820" s="24">
         <f>D820*H820</f>
-        <v/>
+        <v>28.910000000000004</v>
       </c>
       <c r="H820" s="25" t="n">
         <v>175</v>
@@ -28455,7 +28449,7 @@
       </c>
       <c r="G821" s="24">
         <f>D821*H821</f>
-        <v/>
+        <v>126.21</v>
       </c>
       <c r="H821" s="25" t="n">
         <v>175</v>
@@ -28488,7 +28482,7 @@
       </c>
       <c r="G822" s="24">
         <f>D822*H822</f>
-        <v/>
+        <v>147.7875</v>
       </c>
       <c r="H822" s="25" t="n">
         <v>175</v>
@@ -28521,7 +28515,7 @@
       </c>
       <c r="G823" s="24">
         <f>D823*H823</f>
-        <v/>
+        <v>156.73</v>
       </c>
       <c r="H823" s="25" t="n">
         <v>175</v>
@@ -28554,7 +28548,7 @@
       </c>
       <c r="G824" s="24">
         <f>D824*H824</f>
-        <v/>
+        <v>184.2225</v>
       </c>
       <c r="H824" s="25" t="n">
         <v>175</v>
@@ -28587,7 +28581,7 @@
       </c>
       <c r="G825" s="24">
         <f>D825*H825</f>
-        <v/>
+        <v>10.095</v>
       </c>
       <c r="H825" s="25" t="n">
         <v>150</v>
@@ -28620,7 +28614,7 @@
       </c>
       <c r="G826" s="24">
         <f>D826*H826</f>
-        <v/>
+        <v>14.655</v>
       </c>
       <c r="H826" s="25" t="n">
         <v>150</v>
@@ -28653,7 +28647,7 @@
       </c>
       <c r="G827" s="24">
         <f>D827*H827</f>
-        <v/>
+        <v>19.575</v>
       </c>
       <c r="H827" s="25" t="n">
         <v>150</v>
@@ -28686,7 +28680,7 @@
       </c>
       <c r="G828" s="24">
         <f>D828*H828</f>
-        <v/>
+        <v>34.62</v>
       </c>
       <c r="H828" s="25" t="n">
         <v>150</v>
@@ -28719,7 +28713,7 @@
       </c>
       <c r="G829" s="24">
         <f>D829*H829</f>
-        <v/>
+        <v>53.445</v>
       </c>
       <c r="H829" s="25" t="n">
         <v>150</v>
@@ -28752,7 +28746,7 @@
       </c>
       <c r="G830" s="24">
         <f>D830*H830</f>
-        <v/>
+        <v>62.985</v>
       </c>
       <c r="H830" s="25" t="n">
         <v>150</v>
@@ -28785,7 +28779,7 @@
       </c>
       <c r="G831" s="24">
         <f>D831*H831</f>
-        <v/>
+        <v>75.66</v>
       </c>
       <c r="H831" s="25" t="n">
         <v>150</v>
@@ -28818,7 +28812,7 @@
       </c>
       <c r="G832" s="24">
         <f>D832*H832</f>
-        <v/>
+        <v>78.21</v>
       </c>
       <c r="H832" s="25" t="n">
         <v>150</v>
@@ -28851,7 +28845,7 @@
       </c>
       <c r="G833" s="24">
         <f>D833*H833</f>
-        <v/>
+        <v>103.30499999999999</v>
       </c>
       <c r="H833" s="25" t="n">
         <v>150</v>
@@ -28884,7 +28878,7 @@
       </c>
       <c r="G834" s="24">
         <f>D834*H834</f>
-        <v/>
+        <v>120.85499999999999</v>
       </c>
       <c r="H834" s="25" t="n">
         <v>150</v>
@@ -28917,7 +28911,7 @@
       </c>
       <c r="G835" s="24">
         <f>D835*H835</f>
-        <v/>
+        <v>122.595</v>
       </c>
       <c r="H835" s="25" t="n">
         <v>150</v>
@@ -28950,7 +28944,7 @@
       </c>
       <c r="G836" s="24">
         <f>D836*H836</f>
-        <v/>
+        <v>128.16</v>
       </c>
       <c r="H836" s="25" t="n">
         <v>150</v>
@@ -28983,7 +28977,7 @@
       </c>
       <c r="G837" s="24">
         <f>D837*H837</f>
-        <v/>
+        <v>140.565</v>
       </c>
       <c r="H837" s="25" t="n">
         <v>150</v>
@@ -29016,7 +29010,7 @@
       </c>
       <c r="G838" s="24">
         <f>D838*H838</f>
-        <v/>
+        <v>146.73</v>
       </c>
       <c r="H838" s="25" t="n">
         <v>150</v>
@@ -29049,7 +29043,7 @@
       </c>
       <c r="G839" s="24">
         <f>D839*H839</f>
-        <v/>
+        <v>166.935</v>
       </c>
       <c r="H839" s="25" t="n">
         <v>150</v>
@@ -29082,7 +29076,7 @@
       </c>
       <c r="G840" s="24">
         <f>D840*H840</f>
-        <v/>
+        <v>182.52</v>
       </c>
       <c r="H840" s="25" t="n">
         <v>150</v>
@@ -29115,7 +29109,7 @@
       </c>
       <c r="G841" s="24">
         <f>D841*H841</f>
-        <v/>
+        <v>197.535</v>
       </c>
       <c r="H841" s="25" t="n">
         <v>150</v>
@@ -29148,7 +29142,7 @@
       </c>
       <c r="G842" s="24">
         <f>D842*H842</f>
-        <v/>
+        <v>221.98499999999999</v>
       </c>
       <c r="H842" s="25" t="n">
         <v>150</v>
@@ -29181,7 +29175,7 @@
       </c>
       <c r="G843" s="24">
         <f>D843*H843</f>
-        <v/>
+        <v>256.215</v>
       </c>
       <c r="H843" s="25" t="n">
         <v>150</v>
@@ -29214,7 +29208,7 @@
       </c>
       <c r="G844" s="24">
         <f>D844*H844</f>
-        <v/>
+        <v>337.20000000000005</v>
       </c>
       <c r="H844" s="25" t="n">
         <v>150</v>
@@ -29247,7 +29241,7 @@
       </c>
       <c r="G845" s="24">
         <f>D845*H845</f>
-        <v/>
+        <v>424.875</v>
       </c>
       <c r="H845" s="25" t="n">
         <v>150</v>
@@ -29280,7 +29274,7 @@
       </c>
       <c r="G846" s="24">
         <f>D846*H846</f>
-        <v/>
+        <v>564.615</v>
       </c>
       <c r="H846" s="25" t="n">
         <v>150</v>
@@ -29313,7 +29307,7 @@
       </c>
       <c r="G847" s="24">
         <f>D847*H847</f>
-        <v/>
+        <v>599.595</v>
       </c>
       <c r="H847" s="25" t="n">
         <v>150</v>
@@ -29346,7 +29340,7 @@
       </c>
       <c r="G848" s="24">
         <f>D848*H848</f>
-        <v/>
+        <v>150.405</v>
       </c>
       <c r="H848" s="25" t="n">
         <v>150</v>
@@ -29379,7 +29373,7 @@
       </c>
       <c r="G849" s="24">
         <f>D849*H849</f>
-        <v/>
+        <v>151.66500000000002</v>
       </c>
       <c r="H849" s="25" t="n">
         <v>150</v>
@@ -29412,7 +29406,7 @@
       </c>
       <c r="G850" s="24">
         <f>D850*H850</f>
-        <v/>
+        <v>69.87</v>
       </c>
       <c r="H850" s="25" t="n">
         <v>150</v>
@@ -29445,7 +29439,7 @@
       </c>
       <c r="G851" s="24">
         <f>D851*H851</f>
-        <v/>
+        <v>90.645</v>
       </c>
       <c r="H851" s="25" t="n">
         <v>150</v>
@@ -29478,7 +29472,7 @@
       </c>
       <c r="G852" s="24">
         <f>D852*H852</f>
-        <v/>
+        <v>93.72</v>
       </c>
       <c r="H852" s="25" t="n">
         <v>150</v>
@@ -29511,7 +29505,7 @@
       </c>
       <c r="G853" s="24">
         <f>D853*H853</f>
-        <v/>
+        <v>120.31500000000001</v>
       </c>
       <c r="H853" s="25" t="n">
         <v>150</v>
@@ -29544,7 +29538,7 @@
       </c>
       <c r="G854" s="24">
         <f>D854*H854</f>
-        <v/>
+        <v>136.45499999999998</v>
       </c>
       <c r="H854" s="25" t="n">
         <v>150</v>
@@ -29577,7 +29571,7 @@
       </c>
       <c r="G855" s="24">
         <f>D855*H855</f>
-        <v/>
+        <v>146.52</v>
       </c>
       <c r="H855" s="25" t="n">
         <v>150</v>
@@ -29610,7 +29604,7 @@
       </c>
       <c r="G856" s="24">
         <f>D856*H856</f>
-        <v/>
+        <v>154.09500000000003</v>
       </c>
       <c r="H856" s="25" t="n">
         <v>150</v>
@@ -29643,7 +29637,7 @@
       </c>
       <c r="G857" s="24">
         <f>D857*H857</f>
-        <v/>
+        <v>167.505</v>
       </c>
       <c r="H857" s="25" t="n">
         <v>150</v>
@@ -29676,7 +29670,7 @@
       </c>
       <c r="G858" s="24">
         <f>D858*H858</f>
-        <v/>
+        <v>260.055</v>
       </c>
       <c r="H858" s="25" t="n">
         <v>150</v>
@@ -29709,7 +29703,7 @@
       </c>
       <c r="G859" s="24">
         <f>D859*H859</f>
-        <v/>
+        <v>294.46500000000003</v>
       </c>
       <c r="H859" s="25" t="n">
         <v>150</v>
@@ -29742,7 +29736,7 @@
       </c>
       <c r="G860" s="24">
         <f>D860*H860</f>
-        <v/>
+        <v>334.875</v>
       </c>
       <c r="H860" s="25" t="n">
         <v>150</v>
@@ -29775,7 +29769,7 @@
       </c>
       <c r="G861" s="24">
         <f>D861*H861</f>
-        <v/>
+        <v>349.515</v>
       </c>
       <c r="H861" s="25" t="n">
         <v>150</v>
@@ -29808,7 +29802,7 @@
       </c>
       <c r="G862" s="24">
         <f>D862*H862</f>
-        <v/>
+        <v>360.34499999999997</v>
       </c>
       <c r="H862" s="25" t="n">
         <v>150</v>
@@ -29841,7 +29835,7 @@
       </c>
       <c r="G863" s="24">
         <f>D863*H863</f>
-        <v/>
+        <v>106.71000000000001</v>
       </c>
       <c r="H863" s="25" t="n">
         <v>150</v>
@@ -29874,7 +29868,7 @@
       </c>
       <c r="G864" s="24">
         <f>D864*H864</f>
-        <v/>
+        <v>205.57500000000002</v>
       </c>
       <c r="H864" s="25" t="n">
         <v>150</v>
@@ -29907,7 +29901,7 @@
       </c>
       <c r="G865" s="24">
         <f>D865*H865</f>
-        <v/>
+        <v>54.57</v>
       </c>
       <c r="H865" s="25" t="n">
         <v>150</v>
@@ -29940,7 +29934,7 @@
       </c>
       <c r="G866" s="24">
         <f>D866*H866</f>
-        <v/>
+        <v>78.435</v>
       </c>
       <c r="H866" s="25" t="n">
         <v>150</v>
@@ -29973,7 +29967,7 @@
       </c>
       <c r="G867" s="24">
         <f>D867*H867</f>
-        <v/>
+        <v>255.78</v>
       </c>
       <c r="H867" s="25" t="n">
         <v>150</v>
@@ -30006,7 +30000,7 @@
       </c>
       <c r="G868" s="24">
         <f>D868*H868</f>
-        <v/>
+        <v>339.53999999999996</v>
       </c>
       <c r="H868" s="25" t="n">
         <v>150</v>
@@ -30039,7 +30033,7 @@
       </c>
       <c r="G869" s="24">
         <f>D869*H869</f>
-        <v/>
+        <v>180.145</v>
       </c>
       <c r="H869" s="25" t="n">
         <v>175</v>
@@ -30072,7 +30066,7 @@
       </c>
       <c r="G870" s="24">
         <f>D870*H870</f>
-        <v/>
+        <v>214.4975</v>
       </c>
       <c r="H870" s="25" t="n">
         <v>175</v>
@@ -30105,7 +30099,7 @@
       </c>
       <c r="G871" s="24">
         <f>D871*H871</f>
-        <v/>
+        <v>195.36</v>
       </c>
       <c r="H871" s="25" t="n">
         <v>150</v>
@@ -30138,7 +30132,7 @@
       </c>
       <c r="G872" s="24">
         <f>D872*H872</f>
-        <v/>
+        <v>69.7375</v>
       </c>
       <c r="H872" s="25" t="n">
         <v>175</v>
@@ -30171,7 +30165,7 @@
       </c>
       <c r="G873" s="24">
         <f>D873*H873</f>
-        <v/>
+        <v>231.1925</v>
       </c>
       <c r="H873" s="25" t="n">
         <v>175</v>
@@ -30204,7 +30198,7 @@
       </c>
       <c r="G874" s="24">
         <f>D874*H874</f>
-        <v/>
+        <v>259.47249999999997</v>
       </c>
       <c r="H874" s="25" t="n">
         <v>175</v>
@@ -30237,7 +30231,7 @@
       </c>
       <c r="G875" s="24">
         <f>D875*H875</f>
-        <v/>
+        <v>111.16</v>
       </c>
       <c r="H875" s="25" t="n">
         <v>200</v>
@@ -30270,7 +30264,7 @@
       </c>
       <c r="G876" s="24">
         <f>D876*H876</f>
-        <v/>
+        <v>130.78</v>
       </c>
       <c r="H876" s="25" t="n">
         <v>200</v>
@@ -30303,7 +30297,7 @@
       </c>
       <c r="G877" s="24">
         <f>D877*H877</f>
-        <v/>
+        <v>145.6</v>
       </c>
       <c r="H877" s="25" t="n">
         <v>200</v>
@@ -30336,7 +30330,7 @@
       </c>
       <c r="G878" s="24">
         <f>D878*H878</f>
-        <v/>
+        <v>208.65999999999997</v>
       </c>
       <c r="H878" s="25" t="n">
         <v>200</v>
@@ -30369,7 +30363,7 @@
       </c>
       <c r="G879" s="24">
         <f>D879*H879</f>
-        <v/>
+        <v>221.06</v>
       </c>
       <c r="H879" s="25" t="n">
         <v>200</v>
@@ -30402,7 +30396,7 @@
       </c>
       <c r="G880" s="24">
         <f>D880*H880</f>
-        <v/>
+        <v>225.95999999999998</v>
       </c>
       <c r="H880" s="25" t="n">
         <v>200</v>
@@ -30435,7 +30429,7 @@
       </c>
       <c r="G881" s="24">
         <f>D881*H881</f>
-        <v/>
+        <v>279.3</v>
       </c>
       <c r="H881" s="25" t="n">
         <v>200</v>
@@ -30468,7 +30462,7 @@
       </c>
       <c r="G882" s="24">
         <f>D882*H882</f>
-        <v/>
+        <v>286.14000000000004</v>
       </c>
       <c r="H882" s="25" t="n">
         <v>200</v>
@@ -30501,7 +30495,7 @@
       </c>
       <c r="G883" s="24">
         <f>D883*H883</f>
-        <v/>
+        <v>300.91999999999996</v>
       </c>
       <c r="H883" s="25" t="n">
         <v>200</v>
@@ -30534,7 +30528,7 @@
       </c>
       <c r="G884" s="24">
         <f>D884*H884</f>
-        <v/>
+        <v>310.2</v>
       </c>
       <c r="H884" s="25" t="n">
         <v>200</v>
@@ -30567,7 +30561,7 @@
       </c>
       <c r="G885" s="24">
         <f>D885*H885</f>
-        <v/>
+        <v>326.82000000000005</v>
       </c>
       <c r="H885" s="25" t="n">
         <v>200</v>
@@ -30600,7 +30594,7 @@
       </c>
       <c r="G886" s="24">
         <f>D886*H886</f>
-        <v/>
+        <v>423.54</v>
       </c>
       <c r="H886" s="25" t="n">
         <v>200</v>
@@ -30633,7 +30627,7 @@
       </c>
       <c r="G887" s="24">
         <f>D887*H887</f>
-        <v/>
+        <v>996.96</v>
       </c>
       <c r="H887" s="25" t="n">
         <v>200</v>
@@ -30666,7 +30660,7 @@
       </c>
       <c r="G888" s="24">
         <f>D888*H888</f>
-        <v/>
+        <v>69.63</v>
       </c>
       <c r="H888" s="25" t="n">
         <v>150</v>
@@ -30699,7 +30693,7 @@
       </c>
       <c r="G889" s="24">
         <f>D889*H889</f>
-        <v/>
+        <v>112.635</v>
       </c>
       <c r="H889" s="25" t="n">
         <v>150</v>
@@ -30732,7 +30726,7 @@
       </c>
       <c r="G890" s="24">
         <f>D890*H890</f>
-        <v/>
+        <v>356.415</v>
       </c>
       <c r="H890" s="25" t="n">
         <v>150</v>
@@ -30765,7 +30759,7 @@
       </c>
       <c r="G891" s="24">
         <f>D891*H891</f>
-        <v/>
+        <v>636.4949999999999</v>
       </c>
       <c r="H891" s="25" t="n">
         <v>150</v>
@@ -30798,7 +30792,7 @@
       </c>
       <c r="G892" s="24">
         <f>D892*H892</f>
-        <v/>
+        <v>143.94</v>
       </c>
       <c r="H892" s="25" t="n">
         <v>150</v>
@@ -30831,7 +30825,7 @@
       </c>
       <c r="G893" s="24">
         <f>D893*H893</f>
-        <v/>
+        <v>334.5</v>
       </c>
       <c r="H893" s="25" t="n">
         <v>150</v>
@@ -30864,7 +30858,7 @@
       </c>
       <c r="G894" s="24">
         <f>D894*H894</f>
-        <v/>
+        <v>526.6800000000001</v>
       </c>
       <c r="H894" s="25" t="n">
         <v>150</v>
@@ -30897,7 +30891,7 @@
       </c>
       <c r="G895" s="24">
         <f>D895*H895</f>
-        <v/>
+        <v>40.44</v>
       </c>
       <c r="H895" s="25" t="n">
         <v>150</v>
@@ -30930,7 +30924,7 @@
       </c>
       <c r="G896" s="24">
         <f>D896*H896</f>
-        <v/>
+        <v>60.285</v>
       </c>
       <c r="H896" s="25" t="n">
         <v>150</v>
@@ -30963,7 +30957,7 @@
       </c>
       <c r="G897" s="24">
         <f>D897*H897</f>
-        <v/>
+        <v>1029.6</v>
       </c>
       <c r="H897" s="25" t="n">
         <v>150</v>
@@ -30996,7 +30990,7 @@
       </c>
       <c r="G898" s="24">
         <f>D898*H898</f>
-        <v/>
+        <v>1786.5149999999999</v>
       </c>
       <c r="H898" s="25" t="n">
         <v>150</v>
@@ -31029,7 +31023,7 @@
       </c>
       <c r="G899" s="24">
         <f>D899*H899</f>
-        <v/>
+        <v>606.345</v>
       </c>
       <c r="H899" s="25" t="n">
         <v>150</v>
@@ -31062,7 +31056,7 @@
       </c>
       <c r="G900" s="24">
         <f>D900*H900</f>
-        <v/>
+        <v>311.55</v>
       </c>
       <c r="H900" s="25" t="n">
         <v>150</v>
@@ -31095,7 +31089,7 @@
       </c>
       <c r="G901" s="24">
         <f>D901*H901</f>
-        <v/>
+        <v>687.72</v>
       </c>
       <c r="H901" s="25" t="n">
         <v>150</v>
@@ -31128,7 +31122,7 @@
       </c>
       <c r="G902" s="24">
         <f>D902*H902</f>
-        <v/>
+        <v>956.31</v>
       </c>
       <c r="H902" s="25" t="n">
         <v>150</v>
@@ -31161,7 +31155,7 @@
       </c>
       <c r="G903" s="24">
         <f>D903*H903</f>
-        <v/>
+        <v>1291.59</v>
       </c>
       <c r="H903" s="25" t="n">
         <v>150</v>
@@ -31267,18 +31261,18 @@
       </c>
       <c r="D6" s="26">
         <f>MEDIAN('Per-task detail'!$D$2:$D$2)</f>
-        <v/>
+        <v>0.1392</v>
       </c>
       <c r="E6" s="27">
         <f>COUNT('Per-task detail'!$D$2:$D$2)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F6" s="28" t="n">
         <v>5</v>
       </c>
       <c r="G6" s="29">
         <f>D6*'Per-task detail'!$H$2</f>
-        <v/>
+        <v>20.88</v>
       </c>
     </row>
     <row r="7">
@@ -31297,18 +31291,18 @@
       </c>
       <c r="D7" s="33">
         <f>MEDIAN('Per-task detail'!$D$3:$D$29)</f>
-        <v/>
+        <v>0.2227</v>
       </c>
       <c r="E7" s="34">
         <f>COUNT('Per-task detail'!$D$3:$D$29)</f>
-        <v/>
+        <v>27</v>
       </c>
       <c r="F7" s="35" t="n">
         <v>55.66</v>
       </c>
       <c r="G7" s="36">
         <f>D7*'Per-task detail'!$H$3</f>
-        <v/>
+        <v>33.405</v>
       </c>
     </row>
     <row r="8">
@@ -31327,18 +31321,18 @@
       </c>
       <c r="D8" s="33">
         <f>MEDIAN('Per-task detail'!$D$30:$D$71)</f>
-        <v/>
+        <v>0.24045</v>
       </c>
       <c r="E8" s="34">
         <f>COUNT('Per-task detail'!$D$30:$D$71)</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="F8" s="35" t="n">
         <v>71.87</v>
       </c>
       <c r="G8" s="36">
         <f>D8*'Per-task detail'!$H$30</f>
-        <v/>
+        <v>48.089999999999996</v>
       </c>
     </row>
     <row r="9">
@@ -31357,18 +31351,18 @@
       </c>
       <c r="D9" s="26">
         <f>MEDIAN('Per-task detail'!$D$72:$D$73)</f>
-        <v/>
+        <v>0.26575000000000004</v>
       </c>
       <c r="E9" s="27">
         <f>COUNT('Per-task detail'!$D$72:$D$73)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F9" s="28" t="n">
         <v>8.02</v>
       </c>
       <c r="G9" s="29">
         <f>D9*'Per-task detail'!$H$72</f>
-        <v/>
+        <v>39.862500000000004</v>
       </c>
     </row>
     <row r="10">
@@ -31387,18 +31381,18 @@
       </c>
       <c r="D10" s="33">
         <f>MEDIAN('Per-task detail'!$D$74:$D$104)</f>
-        <v/>
+        <v>0.3036</v>
       </c>
       <c r="E10" s="34">
         <f>COUNT('Per-task detail'!$D$74:$D$104)</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="F10" s="35" t="n">
         <v>76.17</v>
       </c>
       <c r="G10" s="36">
         <f>D10*'Per-task detail'!$H$74</f>
-        <v/>
+        <v>45.54</v>
       </c>
     </row>
     <row r="11">
@@ -31417,18 +31411,18 @@
       </c>
       <c r="D11" s="33">
         <f>MEDIAN('Per-task detail'!$D$105:$D$114)</f>
-        <v/>
+        <v>0.35209999999999997</v>
       </c>
       <c r="E11" s="34">
         <f>COUNT('Per-task detail'!$D$105:$D$114)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="F11" s="35" t="n">
         <v>9.140000000000001</v>
       </c>
       <c r="G11" s="36">
         <f>D11*'Per-task detail'!$H$105</f>
-        <v/>
+        <v>52.815</v>
       </c>
     </row>
     <row r="12">
@@ -31447,18 +31441,18 @@
       </c>
       <c r="D12" s="33">
         <f>MEDIAN('Per-task detail'!$D$115:$D$149)</f>
-        <v/>
+        <v>0.3712</v>
       </c>
       <c r="E12" s="34">
         <f>COUNT('Per-task detail'!$D$115:$D$149)</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="F12" s="35" t="n">
         <v>101.02</v>
       </c>
       <c r="G12" s="36">
         <f>D12*'Per-task detail'!$H$115</f>
-        <v/>
+        <v>55.67999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -31477,18 +31471,18 @@
       </c>
       <c r="D13" s="33">
         <f>MEDIAN('Per-task detail'!$D$150:$D$165)</f>
-        <v/>
+        <v>0.3774</v>
       </c>
       <c r="E13" s="34">
         <f>COUNT('Per-task detail'!$D$150:$D$165)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="F13" s="35" t="n">
         <v>26.75</v>
       </c>
       <c r="G13" s="36">
         <f>D13*'Per-task detail'!$H$150</f>
-        <v/>
+        <v>56.61</v>
       </c>
     </row>
     <row r="14">
@@ -31507,18 +31501,18 @@
       </c>
       <c r="D14" s="33">
         <f>MEDIAN('Per-task detail'!$D$166:$D$199)</f>
-        <v/>
+        <v>0.3823</v>
       </c>
       <c r="E14" s="34">
         <f>COUNT('Per-task detail'!$D$166:$D$199)</f>
-        <v/>
+        <v>34</v>
       </c>
       <c r="F14" s="35" t="n">
         <v>49.9</v>
       </c>
       <c r="G14" s="36">
         <f>D14*'Per-task detail'!$H$166</f>
-        <v/>
+        <v>57.345</v>
       </c>
     </row>
     <row r="15">
@@ -31537,18 +31531,18 @@
       </c>
       <c r="D15" s="26">
         <f>MEDIAN('Per-task detail'!$D$200:$D$207)</f>
-        <v/>
+        <v>0.38885000000000003</v>
       </c>
       <c r="E15" s="27">
         <f>COUNT('Per-task detail'!$D$200:$D$207)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="F15" s="28" t="n">
         <v>18.53</v>
       </c>
       <c r="G15" s="29">
         <f>D15*'Per-task detail'!$H$200</f>
-        <v/>
+        <v>58.32750000000001</v>
       </c>
     </row>
     <row r="16">
@@ -31567,18 +31561,18 @@
       </c>
       <c r="D16" s="33">
         <f>MEDIAN('Per-task detail'!$D$208:$D$302)</f>
-        <v/>
+        <v>0.4432</v>
       </c>
       <c r="E16" s="34">
         <f>COUNT('Per-task detail'!$D$208:$D$302)</f>
-        <v/>
+        <v>95</v>
       </c>
       <c r="F16" s="35" t="n">
         <v>88.14</v>
       </c>
       <c r="G16" s="36">
         <f>D16*'Per-task detail'!$H$208</f>
-        <v/>
+        <v>66.48</v>
       </c>
     </row>
     <row r="17">
@@ -31597,18 +31591,18 @@
       </c>
       <c r="D17" s="33">
         <f>MEDIAN('Per-task detail'!$D$303:$D$360)</f>
-        <v/>
+        <v>0.4682</v>
       </c>
       <c r="E17" s="34">
         <f>COUNT('Per-task detail'!$D$303:$D$360)</f>
-        <v/>
+        <v>58</v>
       </c>
       <c r="F17" s="35" t="n">
         <v>84.31</v>
       </c>
       <c r="G17" s="36">
         <f>D17*'Per-task detail'!$H$303</f>
-        <v/>
+        <v>70.23</v>
       </c>
     </row>
     <row r="18">
@@ -31627,18 +31621,18 @@
       </c>
       <c r="D18" s="33">
         <f>MEDIAN('Per-task detail'!$D$361:$D$386)</f>
-        <v/>
+        <v>0.47124999999999995</v>
       </c>
       <c r="E18" s="34">
         <f>COUNT('Per-task detail'!$D$361:$D$386)</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="F18" s="35" t="n">
         <v>20.76</v>
       </c>
       <c r="G18" s="36">
         <f>D18*'Per-task detail'!$H$361</f>
-        <v/>
+        <v>70.68749999999999</v>
       </c>
     </row>
     <row r="19">
@@ -31657,18 +31651,18 @@
       </c>
       <c r="D19" s="26">
         <f>MEDIAN('Per-task detail'!$D$387:$D$394)</f>
-        <v/>
+        <v>0.47505</v>
       </c>
       <c r="E19" s="27">
         <f>COUNT('Per-task detail'!$D$387:$D$394)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="F19" s="28" t="n">
         <v>13.52</v>
       </c>
       <c r="G19" s="29">
         <f>D19*'Per-task detail'!$H$387</f>
-        <v/>
+        <v>71.2575</v>
       </c>
     </row>
     <row r="20">
@@ -31687,18 +31681,18 @@
       </c>
       <c r="D20" s="33">
         <f>MEDIAN('Per-task detail'!$D$395:$D$471)</f>
-        <v/>
+        <v>0.4911</v>
       </c>
       <c r="E20" s="34">
         <f>COUNT('Per-task detail'!$D$395:$D$471)</f>
-        <v/>
+        <v>77</v>
       </c>
       <c r="F20" s="35" t="n">
         <v>100.1</v>
       </c>
       <c r="G20" s="36">
         <f>D20*'Per-task detail'!$H$395</f>
-        <v/>
+        <v>98.22</v>
       </c>
     </row>
     <row r="21">
@@ -31717,18 +31711,18 @@
       </c>
       <c r="D21" s="33">
         <f>MEDIAN('Per-task detail'!$D$472:$D$501)</f>
-        <v/>
+        <v>0.5086</v>
       </c>
       <c r="E21" s="34">
         <f>COUNT('Per-task detail'!$D$472:$D$501)</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="F21" s="35" t="n">
         <v>46.92</v>
       </c>
       <c r="G21" s="36">
         <f>D21*'Per-task detail'!$H$472</f>
-        <v/>
+        <v>101.72000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -31747,18 +31741,18 @@
       </c>
       <c r="D22" s="33">
         <f>MEDIAN('Per-task detail'!$D$502:$D$518)</f>
-        <v/>
+        <v>0.5492</v>
       </c>
       <c r="E22" s="34">
         <f>COUNT('Per-task detail'!$D$502:$D$518)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="F22" s="35" t="n">
         <v>66.64</v>
       </c>
       <c r="G22" s="36">
         <f>D22*'Per-task detail'!$H$502</f>
-        <v/>
+        <v>82.38000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -31777,18 +31771,18 @@
       </c>
       <c r="D23" s="33">
         <f>MEDIAN('Per-task detail'!$D$519:$D$560)</f>
-        <v/>
+        <v>0.5647500000000001</v>
       </c>
       <c r="E23" s="34">
         <f>COUNT('Per-task detail'!$D$519:$D$560)</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="F23" s="35" t="n">
         <v>40.18</v>
       </c>
       <c r="G23" s="36">
         <f>D23*'Per-task detail'!$H$519</f>
-        <v/>
+        <v>112.95000000000002</v>
       </c>
     </row>
     <row r="24">
@@ -31807,18 +31801,18 @@
       </c>
       <c r="D24" s="33">
         <f>MEDIAN('Per-task detail'!$D$561:$D$604)</f>
-        <v/>
+        <v>0.5749500000000001</v>
       </c>
       <c r="E24" s="34">
         <f>COUNT('Per-task detail'!$D$561:$D$604)</f>
-        <v/>
+        <v>44</v>
       </c>
       <c r="F24" s="35" t="n">
         <v>72.26000000000001</v>
       </c>
       <c r="G24" s="36">
         <f>D24*'Per-task detail'!$H$561</f>
-        <v/>
+        <v>86.2425</v>
       </c>
     </row>
     <row r="25">
@@ -31837,18 +31831,18 @@
       </c>
       <c r="D25" s="33">
         <f>MEDIAN('Per-task detail'!$D$605:$D$630)</f>
-        <v/>
+        <v>0.58925</v>
       </c>
       <c r="E25" s="34">
         <f>COUNT('Per-task detail'!$D$605:$D$630)</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="F25" s="35" t="n">
         <v>38.19</v>
       </c>
       <c r="G25" s="36">
         <f>D25*'Per-task detail'!$H$605</f>
-        <v/>
+        <v>88.3875</v>
       </c>
     </row>
     <row r="26">
@@ -31867,18 +31861,18 @@
       </c>
       <c r="D26" s="26">
         <f>MEDIAN('Per-task detail'!$D$631:$D$639)</f>
-        <v/>
+        <v>0.6042</v>
       </c>
       <c r="E26" s="27">
         <f>COUNT('Per-task detail'!$D$631:$D$639)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="F26" s="28" t="n">
         <v>13.15</v>
       </c>
       <c r="G26" s="29">
         <f>D26*'Per-task detail'!$H$631</f>
-        <v/>
+        <v>90.63</v>
       </c>
     </row>
     <row r="27">
@@ -31897,18 +31891,18 @@
       </c>
       <c r="D27" s="33">
         <f>MEDIAN('Per-task detail'!$D$640:$D$707)</f>
-        <v/>
+        <v>0.6351500000000001</v>
       </c>
       <c r="E27" s="34">
         <f>COUNT('Per-task detail'!$D$640:$D$707)</f>
-        <v/>
+        <v>68</v>
       </c>
       <c r="F27" s="35" t="n">
         <v>110.14</v>
       </c>
       <c r="G27" s="36">
         <f>D27*'Per-task detail'!$H$640</f>
-        <v/>
+        <v>111.15125000000002</v>
       </c>
     </row>
     <row r="28">
@@ -31927,18 +31921,18 @@
       </c>
       <c r="D28" s="26">
         <f>MEDIAN('Per-task detail'!$D$708:$D$708)</f>
-        <v/>
+        <v>0.6796</v>
       </c>
       <c r="E28" s="27">
         <f>COUNT('Per-task detail'!$D$708:$D$708)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F28" s="28" t="n">
         <v>2.94</v>
       </c>
       <c r="G28" s="29">
         <f>D28*'Per-task detail'!$H$708</f>
-        <v/>
+        <v>118.92999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -31957,18 +31951,18 @@
       </c>
       <c r="D29" s="26">
         <f>MEDIAN('Per-task detail'!$D$709:$D$711)</f>
-        <v/>
+        <v>0.6977</v>
       </c>
       <c r="E29" s="27">
         <f>COUNT('Per-task detail'!$D$709:$D$711)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F29" s="28" t="n">
         <v>3.22</v>
       </c>
       <c r="G29" s="29">
         <f>D29*'Per-task detail'!$H$709</f>
-        <v/>
+        <v>104.655</v>
       </c>
     </row>
     <row r="30">
@@ -31987,18 +31981,18 @@
       </c>
       <c r="D30" s="33">
         <f>MEDIAN('Per-task detail'!$D$712:$D$736)</f>
-        <v/>
+        <v>0.7041</v>
       </c>
       <c r="E30" s="34">
         <f>COUNT('Per-task detail'!$D$712:$D$736)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="F30" s="35" t="n">
         <v>41.55</v>
       </c>
       <c r="G30" s="36">
         <f>D30*'Per-task detail'!$H$712</f>
-        <v/>
+        <v>105.615</v>
       </c>
     </row>
     <row r="31">
@@ -32017,18 +32011,18 @@
       </c>
       <c r="D31" s="33">
         <f>MEDIAN('Per-task detail'!$D$737:$D$761)</f>
-        <v/>
+        <v>0.7127</v>
       </c>
       <c r="E31" s="34">
         <f>COUNT('Per-task detail'!$D$737:$D$761)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="F31" s="35" t="n">
         <v>104.25</v>
       </c>
       <c r="G31" s="36">
         <f>D31*'Per-task detail'!$H$737</f>
-        <v/>
+        <v>106.905</v>
       </c>
     </row>
     <row r="32">
@@ -32047,18 +32041,18 @@
       </c>
       <c r="D32" s="33">
         <f>MEDIAN('Per-task detail'!$D$762:$D$775)</f>
-        <v/>
+        <v>0.7995</v>
       </c>
       <c r="E32" s="34">
         <f>COUNT('Per-task detail'!$D$762:$D$775)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="F32" s="35" t="n">
         <v>29.34</v>
       </c>
       <c r="G32" s="36">
         <f>D32*'Per-task detail'!$H$762</f>
-        <v/>
+        <v>139.9125</v>
       </c>
     </row>
     <row r="33">
@@ -32077,18 +32071,18 @@
       </c>
       <c r="D33" s="33">
         <f>MEDIAN('Per-task detail'!$D$776:$D$792)</f>
-        <v/>
+        <v>0.8177</v>
       </c>
       <c r="E33" s="34">
         <f>COUNT('Per-task detail'!$D$776:$D$792)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="F33" s="35" t="n">
         <v>33</v>
       </c>
       <c r="G33" s="36">
         <f>D33*'Per-task detail'!$H$776</f>
-        <v/>
+        <v>122.655</v>
       </c>
     </row>
     <row r="34">
@@ -32107,18 +32101,18 @@
       </c>
       <c r="D34" s="26">
         <f>MEDIAN('Per-task detail'!$D$793:$D$795)</f>
-        <v/>
+        <v>0.8196</v>
       </c>
       <c r="E34" s="27">
         <f>COUNT('Per-task detail'!$D$793:$D$795)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F34" s="28" t="n">
         <v>6.83</v>
       </c>
       <c r="G34" s="29">
         <f>D34*'Per-task detail'!$H$793</f>
-        <v/>
+        <v>122.94</v>
       </c>
     </row>
     <row r="35">
@@ -32137,18 +32131,18 @@
       </c>
       <c r="D35" s="26">
         <f>MEDIAN('Per-task detail'!$D$796:$D$798)</f>
-        <v/>
+        <v>0.8285</v>
       </c>
       <c r="E35" s="27">
         <f>COUNT('Per-task detail'!$D$796:$D$798)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F35" s="28" t="n">
         <v>5.05</v>
       </c>
       <c r="G35" s="29">
         <f>D35*'Per-task detail'!$H$796</f>
-        <v/>
+        <v>124.275</v>
       </c>
     </row>
     <row r="36">
@@ -32167,18 +32161,18 @@
       </c>
       <c r="D36" s="33">
         <f>MEDIAN('Per-task detail'!$D$799:$D$819)</f>
-        <v/>
+        <v>0.8411</v>
       </c>
       <c r="E36" s="34">
         <f>COUNT('Per-task detail'!$D$799:$D$819)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="F36" s="35" t="n">
         <v>46.06</v>
       </c>
       <c r="G36" s="36">
         <f>D36*'Per-task detail'!$H$799</f>
-        <v/>
+        <v>126.16499999999999</v>
       </c>
     </row>
     <row r="37">
@@ -32197,18 +32191,18 @@
       </c>
       <c r="D37" s="26">
         <f>MEDIAN('Per-task detail'!$D$820:$D$824)</f>
-        <v/>
+        <v>0.8445</v>
       </c>
       <c r="E37" s="27">
         <f>COUNT('Per-task detail'!$D$820:$D$824)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="F37" s="28" t="n">
         <v>11.33</v>
       </c>
       <c r="G37" s="29">
         <f>D37*'Per-task detail'!$H$820</f>
-        <v/>
+        <v>147.7875</v>
       </c>
     </row>
     <row r="38">
@@ -32227,18 +32221,18 @@
       </c>
       <c r="D38" s="33">
         <f>MEDIAN('Per-task detail'!$D$825:$D$847)</f>
-        <v/>
+        <v>0.8544</v>
       </c>
       <c r="E38" s="34">
         <f>COUNT('Per-task detail'!$D$825:$D$847)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="F38" s="35" t="n">
         <v>47.59</v>
       </c>
       <c r="G38" s="36">
         <f>D38*'Per-task detail'!$H$825</f>
-        <v/>
+        <v>128.16</v>
       </c>
     </row>
     <row r="39">
@@ -32257,18 +32251,18 @@
       </c>
       <c r="D39" s="26">
         <f>MEDIAN('Per-task detail'!$D$848:$D$849)</f>
-        <v/>
+        <v>1.0069</v>
       </c>
       <c r="E39" s="27">
         <f>COUNT('Per-task detail'!$D$848:$D$849)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F39" s="28" t="n">
         <v>2.18</v>
       </c>
       <c r="G39" s="29">
         <f>D39*'Per-task detail'!$H$848</f>
-        <v/>
+        <v>151.035</v>
       </c>
     </row>
     <row r="40">
@@ -32287,18 +32281,18 @@
       </c>
       <c r="D40" s="33">
         <f>MEDIAN('Per-task detail'!$D$850:$D$862)</f>
-        <v/>
+        <v>1.0273</v>
       </c>
       <c r="E40" s="34">
         <f>COUNT('Per-task detail'!$D$850:$D$862)</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="F40" s="35" t="n">
         <v>24.05</v>
       </c>
       <c r="G40" s="36">
         <f>D40*'Per-task detail'!$H$850</f>
-        <v/>
+        <v>154.09500000000003</v>
       </c>
     </row>
     <row r="41">
@@ -32317,18 +32311,18 @@
       </c>
       <c r="D41" s="26">
         <f>MEDIAN('Per-task detail'!$D$863:$D$864)</f>
-        <v/>
+        <v>1.04095</v>
       </c>
       <c r="E41" s="27">
         <f>COUNT('Per-task detail'!$D$863:$D$864)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F41" s="28" t="n">
         <v>2.93</v>
       </c>
       <c r="G41" s="29">
         <f>D41*'Per-task detail'!$H$863</f>
-        <v/>
+        <v>156.1425</v>
       </c>
     </row>
     <row r="42">
@@ -32347,18 +32341,18 @@
       </c>
       <c r="D42" s="26">
         <f>MEDIAN('Per-task detail'!$D$865:$D$868)</f>
-        <v/>
+        <v>1.11405</v>
       </c>
       <c r="E42" s="27">
         <f>COUNT('Per-task detail'!$D$865:$D$868)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F42" s="28" t="n">
         <v>25.78</v>
       </c>
       <c r="G42" s="29">
         <f>D42*'Per-task detail'!$H$865</f>
-        <v/>
+        <v>167.1075</v>
       </c>
     </row>
     <row r="43">
@@ -32377,18 +32371,18 @@
       </c>
       <c r="D43" s="26">
         <f>MEDIAN('Per-task detail'!$D$869:$D$870)</f>
-        <v/>
+        <v>1.12755</v>
       </c>
       <c r="E43" s="27">
         <f>COUNT('Per-task detail'!$D$869:$D$870)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F43" s="28" t="n">
         <v>3.16</v>
       </c>
       <c r="G43" s="29">
         <f>D43*'Per-task detail'!$H$869</f>
-        <v/>
+        <v>197.32125000000002</v>
       </c>
     </row>
     <row r="44">
@@ -32407,18 +32401,18 @@
       </c>
       <c r="D44" s="26">
         <f>MEDIAN('Per-task detail'!$D$871:$D$871)</f>
-        <v/>
+        <v>1.3024</v>
       </c>
       <c r="E44" s="27">
         <f>COUNT('Per-task detail'!$D$871:$D$871)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F44" s="28" t="n">
         <v>4.31</v>
       </c>
       <c r="G44" s="29">
         <f>D44*'Per-task detail'!$H$871</f>
-        <v/>
+        <v>195.36</v>
       </c>
     </row>
     <row r="45">
@@ -32437,18 +32431,18 @@
       </c>
       <c r="D45" s="26">
         <f>MEDIAN('Per-task detail'!$D$872:$D$874)</f>
-        <v/>
+        <v>1.3211</v>
       </c>
       <c r="E45" s="27">
         <f>COUNT('Per-task detail'!$D$872:$D$874)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F45" s="28" t="n">
         <v>10.58</v>
       </c>
       <c r="G45" s="29">
         <f>D45*'Per-task detail'!$H$872</f>
-        <v/>
+        <v>231.1925</v>
       </c>
     </row>
     <row r="46">
@@ -32467,18 +32461,18 @@
       </c>
       <c r="D46" s="33">
         <f>MEDIAN('Per-task detail'!$D$875:$D$887)</f>
-        <v/>
+        <v>1.3965</v>
       </c>
       <c r="E46" s="34">
         <f>COUNT('Per-task detail'!$D$875:$D$887)</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="F46" s="35" t="n">
         <v>127.55</v>
       </c>
       <c r="G46" s="36">
         <f>D46*'Per-task detail'!$H$875</f>
-        <v/>
+        <v>279.3</v>
       </c>
     </row>
     <row r="47">
@@ -32497,18 +32491,18 @@
       </c>
       <c r="D47" s="26">
         <f>MEDIAN('Per-task detail'!$D$888:$D$891)</f>
-        <v/>
+        <v>1.5635000000000001</v>
       </c>
       <c r="E47" s="27">
         <f>COUNT('Per-task detail'!$D$888:$D$891)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F47" s="28" t="n">
         <v>26.32</v>
       </c>
       <c r="G47" s="29">
         <f>D47*'Per-task detail'!$H$888</f>
-        <v/>
+        <v>234.525</v>
       </c>
     </row>
     <row r="48">
@@ -32527,18 +32521,18 @@
       </c>
       <c r="D48" s="26">
         <f>MEDIAN('Per-task detail'!$D$892:$D$893)</f>
-        <v/>
+        <v>1.5948</v>
       </c>
       <c r="E48" s="27">
         <f>COUNT('Per-task detail'!$D$892:$D$893)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F48" s="28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="G48" s="29">
         <f>D48*'Per-task detail'!$H$892</f>
-        <v/>
+        <v>239.22</v>
       </c>
     </row>
     <row r="49">
@@ -32557,18 +32551,18 @@
       </c>
       <c r="D49" s="26">
         <f>MEDIAN('Per-task detail'!$D$894:$D$894)</f>
-        <v/>
+        <v>3.5112</v>
       </c>
       <c r="E49" s="27">
         <f>COUNT('Per-task detail'!$D$894:$D$894)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F49" s="28" t="n">
         <v>6.04</v>
       </c>
       <c r="G49" s="29">
         <f>D49*'Per-task detail'!$H$894</f>
-        <v/>
+        <v>526.6800000000001</v>
       </c>
     </row>
     <row r="50">
@@ -32587,18 +32581,18 @@
       </c>
       <c r="D50" s="26">
         <f>MEDIAN('Per-task detail'!$D$895:$D$898)</f>
-        <v/>
+        <v>3.63295</v>
       </c>
       <c r="E50" s="27">
         <f>COUNT('Per-task detail'!$D$895:$D$898)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F50" s="28" t="n">
         <v>10.74</v>
       </c>
       <c r="G50" s="29">
         <f>D50*'Per-task detail'!$H$895</f>
-        <v/>
+        <v>544.9425</v>
       </c>
     </row>
     <row r="51">
@@ -32617,18 +32611,18 @@
       </c>
       <c r="D51" s="26">
         <f>MEDIAN('Per-task detail'!$D$899:$D$899)</f>
-        <v/>
+        <v>4.0423</v>
       </c>
       <c r="E51" s="27">
         <f>COUNT('Per-task detail'!$D$899:$D$899)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F51" s="28" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="29">
         <f>D51*'Per-task detail'!$H$899</f>
-        <v/>
+        <v>606.345</v>
       </c>
     </row>
     <row r="52">
@@ -32647,18 +32641,18 @@
       </c>
       <c r="D52" s="26">
         <f>MEDIAN('Per-task detail'!$D$900:$D$902)</f>
-        <v/>
+        <v>4.5848</v>
       </c>
       <c r="E52" s="27">
         <f>COUNT('Per-task detail'!$D$900:$D$902)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F52" s="28" t="n">
         <v>17.48</v>
       </c>
       <c r="G52" s="29">
         <f>D52*'Per-task detail'!$H$900</f>
-        <v/>
+        <v>687.72</v>
       </c>
     </row>
     <row r="53">
@@ -32677,18 +32671,18 @@
       </c>
       <c r="D53" s="26">
         <f>MEDIAN('Per-task detail'!$D$903:$D$903)</f>
-        <v/>
+        <v>8.6106</v>
       </c>
       <c r="E53" s="27">
         <f>COUNT('Per-task detail'!$D$903:$D$903)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F53" s="28" t="n">
         <v>9.31</v>
       </c>
       <c r="G53" s="29">
         <f>D53*'Per-task detail'!$H$903</f>
-        <v/>
+        <v>1291.59</v>
       </c>
     </row>
     <row r="54">
@@ -33009,19 +33003,17 @@
       <c r="C65" s="39" t="n"/>
       <c r="D65" s="41">
         <f>MEDIAN('Per-task detail'!$D$2:$D$903)</f>
-        <v/>
       </c>
       <c r="E65" s="42">
         <f>SUM(E6:E64)</f>
-        <v/>
+        <v>902</v>
       </c>
       <c r="F65" s="43">
         <f>SUM(F6:F64)</f>
-        <v/>
       </c>
       <c r="G65" s="44">
         <f>D65*Assumptions!$C$10</f>
-        <v/>
+        <v>84.48750000000001</v>
       </c>
     </row>
     <row r="67">
@@ -33557,10 +33549,10 @@
       </c>
       <c r="C6" s="49">
         <f>COUNT('Per-task detail'!$D$2:$D$903)</f>
-        <v/>
+        <v>902</v>
       </c>
       <c r="D6" s="50" t="n">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
@@ -33576,7 +33568,7 @@
       </c>
       <c r="C7" s="51">
         <f>AVERAGE('Per-task detail'!$D$2:$D$903)</f>
-        <v/>
+        <v>0.8888159645232816</v>
       </c>
       <c r="D7" s="52" t="n">
         <v>0.89</v>
@@ -33595,7 +33587,7 @@
       </c>
       <c r="C8" s="51">
         <f>MEDIAN('Per-task detail'!$D$2:$D$903)</f>
-        <v/>
+        <v>0.56325</v>
       </c>
       <c r="D8" s="52" t="n">
         <v>0.5600000000000001</v>
@@ -33614,7 +33606,7 @@
       </c>
       <c r="C9" s="53">
         <f>SUM('Per-task detail'!$D$2:$D$903)</f>
-        <v/>
+        <v>801.7120000000003</v>
       </c>
       <c r="D9" s="28" t="n">
         <v>801.7</v>
@@ -33651,7 +33643,7 @@
       </c>
       <c r="C11" s="55">
         <f>C9/C10</f>
-        <v/>
+        <v>0.4531170519414458</v>
       </c>
       <c r="D11" s="56" t="n">
         <v>0.453</v>
@@ -33670,7 +33662,7 @@
       </c>
       <c r="C12" s="49">
         <f>COUNTA('AHT by contributor'!$B$6:$B$64)</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="D12" s="50" t="n">
         <v>59</v>
@@ -33707,7 +33699,7 @@
       </c>
       <c r="C14" s="59">
         <f>C13/C10</f>
-        <v/>
+        <v>163.31939184988414</v>
       </c>
       <c r="D14" s="60" t="n">
         <v>163.33</v>
